--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2166"/>
+  <dimension ref="A1:G2167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63506,6 +63506,35 @@
         </is>
       </c>
     </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>テストステロンを上げる食事
+・赤肉
+・全卵5個
+・サーモン、サバ
+・キウイ
+・野菜＜肉
+・脂質を体重×1g
+・タンパク体重×2g~身長×1g
+・炭水化物は増量、減量に合わせ調整
+細かい栄養素をチマチマ気にするより、
+肉、卵、魚をベースにして、
+あとは炭水化物で体重を調整する。
+これが男の食事。</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2163"/>
+  <dimension ref="A1:G2162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56010,33 +56010,10 @@
     <row r="1903">
       <c r="A1903" t="inlineStr">
         <is>
-          <t>2026-06-05 09:46:28</t>
+          <t>2026-06-05 09:54:00</t>
         </is>
       </c>
       <c r="B1903" t="inlineStr">
-        <is>
-          <t>もちろん「自然＝幸福」は自然主義的誤謬であるが、原始時代には幸福になるヒントがある。</t>
-        </is>
-      </c>
-      <c r="C1903" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1903" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1903" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1904">
-      <c r="A1904" t="inlineStr">
-        <is>
-          <t>2026-06-05 09:54:00</t>
-        </is>
-      </c>
-      <c r="B1904" t="inlineStr">
         <is>
           <t>スマホ中毒を抜け出すためにやったこと 
 ・朝に触らない 
@@ -56050,25 +56027,25 @@
 簡単に言ったら、物理的に隔離して他の事に没頭する。 ただそれだけ。</t>
         </is>
       </c>
-      <c r="C1904" t="n">
+      <c r="C1903" t="n">
         <v>33</v>
       </c>
-      <c r="D1904" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1904" t="inlineStr">
+      <c r="D1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1903" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1905">
-      <c r="A1905" t="inlineStr">
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
         <is>
           <t>2026-06-05 10:04:00</t>
         </is>
       </c>
-      <c r="B1905" t="inlineStr">
+      <c r="B1904" t="inlineStr">
         <is>
           <t>「20代童貞率42%」は間違ってる。  
 あれは”未婚男性"のみデータ。  
@@ -56076,25 +56053,25 @@
 20代童貞は負け組と言っても過言ではない。</t>
         </is>
       </c>
-      <c r="C1905" t="n">
+      <c r="C1904" t="n">
         <v>604</v>
       </c>
-      <c r="D1905" t="n">
+      <c r="D1904" t="n">
         <v>28</v>
       </c>
-      <c r="E1905" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1906">
-      <c r="A1906" t="inlineStr">
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
         <is>
           <t>2026-06-05 10:20:27</t>
         </is>
       </c>
-      <c r="B1906" t="inlineStr">
+      <c r="B1905" t="inlineStr">
         <is>
           <t>恋愛はギャルゲーじゃない。
 「ホテルに誘う最強フレーズ」とか「モテるでしょ？の最適回答」みたいなポストは全部電子ゴミ。
@@ -56102,48 +56079,48 @@
 逆に生理的に無理な奴がどんな神フレーズ吐いてもヤれない。</t>
         </is>
       </c>
+      <c r="C1905" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-06-05 10:32:00</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>体重は絶対に同じ条件で測ろう。 なぜなら、水分と胃の中に食べ物が入ってるかで、1~2kgは誤差が出るから。 おすすめは朝一番にションベンした後。 増量でも減量でも、バラバラの時間に測った体重の増減で一喜一憂するのは良くない。</t>
+        </is>
+      </c>
       <c r="C1906" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D1906" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1906" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="1907">
       <c r="A1907" t="inlineStr">
         <is>
-          <t>2026-06-05 10:32:00</t>
+          <t>2026-06-05 10:57:46</t>
         </is>
       </c>
       <c r="B1907" t="inlineStr">
-        <is>
-          <t>体重は絶対に同じ条件で測ろう。 なぜなら、水分と胃の中に食べ物が入ってるかで、1~2kgは誤差が出るから。 おすすめは朝一番にションベンした後。 増量でも減量でも、バラバラの時間に測った体重の増減で一喜一憂するのは良くない。</t>
-        </is>
-      </c>
-      <c r="C1907" t="n">
-        <v>17</v>
-      </c>
-      <c r="D1907" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1907" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="1908">
-      <c r="A1908" t="inlineStr">
-        <is>
-          <t>2026-06-05 10:57:46</t>
-        </is>
-      </c>
-      <c r="B1908" t="inlineStr">
         <is>
           <t>スマホ中毒は時間が奪われるだけでなく
 ・集中力の低下
@@ -56155,25 +56132,25 @@
 「時間の無駄」で済む話じゃない。脳が劣化していく。</t>
         </is>
       </c>
-      <c r="C1908" t="n">
+      <c r="C1907" t="n">
         <v>37</v>
       </c>
-      <c r="D1908" t="n">
+      <c r="D1907" t="n">
         <v>2</v>
       </c>
-      <c r="E1908" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1909">
-      <c r="A1909" t="inlineStr">
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
         <is>
           <t>2026-06-05 11:00:01</t>
         </is>
       </c>
-      <c r="B1909" t="inlineStr">
+      <c r="B1908" t="inlineStr">
         <is>
           <t>「男」は神からのギフトなんよ。 
 ・論理的思考 
@@ -56185,25 +56162,25 @@
 「女っていいよな」は自分を磨かない男の戯言。</t>
         </is>
       </c>
-      <c r="C1909" t="n">
+      <c r="C1908" t="n">
         <v>177</v>
       </c>
-      <c r="D1909" t="n">
+      <c r="D1908" t="n">
         <v>19</v>
       </c>
-      <c r="E1909" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1910">
-      <c r="A1910" t="inlineStr">
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
         <is>
           <t>2026-06-05 11:33:00</t>
         </is>
       </c>
-      <c r="B1910" t="inlineStr">
+      <c r="B1909" t="inlineStr">
         <is>
           <t>堕落している人は「5分で出来る事」を軽視している。
 「あと5分しかないし…この短時間で何もできないよな」でスマホに逃げてしまうクセをやめて
@@ -56213,48 +56190,48 @@
 をやっておけば明日の朝が楽になる。</t>
         </is>
       </c>
+      <c r="C1909" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:46:28</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby一重低身長元チー牛顔が解説https://t.co/MBG8mm5jV3</t>
+        </is>
+      </c>
       <c r="C1910" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D1910" t="n">
         <v>0</v>
       </c>
       <c r="E1910" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1911">
       <c r="A1911" t="inlineStr">
         <is>
-          <t>2026-06-05 11:46:28</t>
+          <t>2026-06-05 13:00:01</t>
         </is>
       </c>
       <c r="B1911" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby一重低身長元チー牛顔が解説https://t.co/MBG8mm5jV3</t>
-        </is>
-      </c>
-      <c r="C1911" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1911" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1911" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1912">
-      <c r="A1912" t="inlineStr">
-        <is>
-          <t>2026-06-05 13:00:01</t>
-        </is>
-      </c>
-      <c r="B1912" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・寝る1時間前の食事 
@@ -56266,25 +56243,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C1912" t="n">
+      <c r="C1911" t="n">
         <v>16</v>
       </c>
-      <c r="D1912" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1912" t="inlineStr">
+      <c r="D1911" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1911" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1913">
-      <c r="A1913" t="inlineStr">
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
         <is>
           <t>2026-06-05 22:03:00</t>
         </is>
       </c>
-      <c r="B1913" t="inlineStr">
+      <c r="B1912" t="inlineStr">
         <is>
           <t>コーヒーで気持ち悪くなる人へ。 
 ・空腹で飲まない 
@@ -56297,25 +56274,25 @@
 これを試してみて。</t>
         </is>
       </c>
-      <c r="C1913" t="n">
+      <c r="C1912" t="n">
         <v>18</v>
       </c>
-      <c r="D1913" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1913" t="inlineStr">
+      <c r="D1912" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1912" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1914">
-      <c r="A1914" t="inlineStr">
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
         <is>
           <t>2026-06-05 22:30:00</t>
         </is>
       </c>
-      <c r="B1914" t="inlineStr">
+      <c r="B1913" t="inlineStr">
         <is>
           <t>コーヒーは神が人類に与えたドーピング。 
 ・集中力UP 
@@ -56327,25 +56304,25 @@
 プレを買う前にまずはコーヒーを飲もう。</t>
         </is>
       </c>
-      <c r="C1914" t="n">
+      <c r="C1913" t="n">
         <v>70</v>
       </c>
-      <c r="D1914" t="n">
+      <c r="D1913" t="n">
         <v>4</v>
       </c>
-      <c r="E1914" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1915">
-      <c r="A1915" t="inlineStr">
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
         <is>
           <t>2026-06-05 23:06:00</t>
         </is>
       </c>
-      <c r="B1915" t="inlineStr">
+      <c r="B1914" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・朝1時間のディープワーク 
@@ -56357,25 +56334,25 @@
 俺は目覚ましを時計に変えてから全部変わった。</t>
         </is>
       </c>
-      <c r="C1915" t="n">
+      <c r="C1914" t="n">
         <v>22</v>
       </c>
-      <c r="D1915" t="n">
+      <c r="D1914" t="n">
         <v>1</v>
       </c>
-      <c r="E1915" t="inlineStr">
+      <c r="E1914" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1916">
-      <c r="A1916" t="inlineStr">
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
         <is>
           <t>2026-06-06 08:12:50</t>
         </is>
       </c>
-      <c r="B1916" t="inlineStr">
+      <c r="B1915" t="inlineStr">
         <is>
           <t>食事を変えて起きた変化 
 ・体臭が減った 
@@ -56387,25 +56364,25 @@
 当たり前のことを今一度見直そう。</t>
         </is>
       </c>
-      <c r="C1916" t="n">
+      <c r="C1915" t="n">
         <v>21</v>
       </c>
-      <c r="D1916" t="n">
+      <c r="D1915" t="n">
         <v>1</v>
       </c>
-      <c r="E1916" t="inlineStr">
+      <c r="E1915" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1917">
-      <c r="A1917" t="inlineStr">
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
         <is>
           <t>2026-06-06 08:20:28</t>
         </is>
       </c>
-      <c r="B1917" t="inlineStr">
+      <c r="B1916" t="inlineStr">
         <is>
           <t>童貞でもマインドはヤ〇チンであれ。 
 ・女をいじる 
@@ -56419,25 +56396,25 @@
 のけぞりながら女に「つけろよ」って言っとけばいい。</t>
         </is>
       </c>
-      <c r="C1917" t="n">
+      <c r="C1916" t="n">
         <v>108</v>
       </c>
-      <c r="D1917" t="n">
+      <c r="D1916" t="n">
         <v>10</v>
       </c>
-      <c r="E1917" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1918">
-      <c r="A1918" t="inlineStr">
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
         <is>
           <t>2026-06-06 09:00:01</t>
         </is>
       </c>
-      <c r="B1918" t="inlineStr">
+      <c r="B1917" t="inlineStr">
         <is>
           <t>ポルノとセ〇クスは全く違う。  
 ポルノで刺激されるのは
@@ -56450,25 +56427,25 @@
 ＋セロトニン（充足）</t>
         </is>
       </c>
-      <c r="C1918" t="n">
+      <c r="C1917" t="n">
         <v>27</v>
       </c>
-      <c r="D1918" t="n">
+      <c r="D1917" t="n">
         <v>1</v>
       </c>
-      <c r="E1918" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1919">
-      <c r="A1919" t="inlineStr">
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
         <is>
           <t>2026-06-06 09:03:13</t>
         </is>
       </c>
-      <c r="B1919" t="inlineStr">
+      <c r="B1918" t="inlineStr">
         <is>
           <t>スマホ中毒の本当の恐ろしさは、中毒がデフォルトになりすぎて誰も中毒だと気づかないところにある。
 電車、育児、歩行中、インフラ。
@@ -56476,25 +56453,25 @@
 その状態で脱スマホ中毒を語ると「反テクノロジーですか？」「スピってますか？」でレッテルを貼られて終わる。</t>
         </is>
       </c>
-      <c r="C1919" t="n">
+      <c r="C1918" t="n">
         <v>18</v>
       </c>
-      <c r="D1919" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1919" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1920">
-      <c r="A1920" t="inlineStr">
+      <c r="D1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
         <is>
           <t>2026-06-06 09:35:00</t>
         </is>
       </c>
-      <c r="B1920" t="inlineStr">
+      <c r="B1919" t="inlineStr">
         <is>
           <t>男磨き初心者のミス  
 ・「女性のアドバイスこそが正義や」 
@@ -56507,25 +56484,25 @@
  →受け身が許されるのはTOP1％のみ</t>
         </is>
       </c>
-      <c r="C1920" t="n">
+      <c r="C1919" t="n">
         <v>32</v>
       </c>
-      <c r="D1920" t="n">
+      <c r="D1919" t="n">
         <v>1</v>
       </c>
-      <c r="E1920" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1921">
-      <c r="A1921" t="inlineStr">
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
         <is>
           <t>2026-06-06 09:35:09</t>
         </is>
       </c>
-      <c r="B1921" t="inlineStr">
+      <c r="B1920" t="inlineStr">
         <is>
           <t>ヒョロガリはドカ食いをするのではなく、
 毎日の食事に1品だけ追加してみて。
@@ -56534,8 +56511,31 @@
 250kcalは米半合で達成できる。</t>
         </is>
       </c>
+      <c r="C1920" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:38:45</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>ナイスです👍 https://t.co/w9tiD0Ejoe</t>
+        </is>
+      </c>
       <c r="C1921" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1921" t="n">
         <v>0</v>
@@ -56549,33 +56549,10 @@
     <row r="1922">
       <c r="A1922" t="inlineStr">
         <is>
-          <t>2026-06-06 09:38:45</t>
+          <t>2026-06-06 11:01:00</t>
         </is>
       </c>
       <c r="B1922" t="inlineStr">
-        <is>
-          <t>ナイスです👍 https://t.co/w9tiD0Ejoe</t>
-        </is>
-      </c>
-      <c r="C1922" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1922" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1922" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1923">
-      <c r="A1923" t="inlineStr">
-        <is>
-          <t>2026-06-06 11:01:00</t>
-        </is>
-      </c>
-      <c r="B1923" t="inlineStr">
         <is>
           <t>スマホを減らしたら手に入ったもの 
 ・時間 
@@ -56588,49 +56565,49 @@
 失ったものは何もない。</t>
         </is>
       </c>
+      <c r="C1922" t="n">
+        <v>32</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-06-06 11:26:28</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>スマホ中毒をやめる方法9選 | byスマホ中毒で高校中退した廃人
+https://t.co/IJPAZYRO6b</t>
+        </is>
+      </c>
       <c r="C1923" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D1923" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1923" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1924">
       <c r="A1924" t="inlineStr">
         <is>
-          <t>2026-06-06 11:26:28</t>
+          <t>2026-06-06 22:10:00</t>
         </is>
       </c>
       <c r="B1924" t="inlineStr">
-        <is>
-          <t>スマホ中毒をやめる方法9選 | byスマホ中毒で高校中退した廃人
-https://t.co/IJPAZYRO6b</t>
-        </is>
-      </c>
-      <c r="C1924" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1924" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1924" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1925">
-      <c r="A1925" t="inlineStr">
-        <is>
-          <t>2026-06-06 22:10:00</t>
-        </is>
-      </c>
-      <c r="B1925" t="inlineStr">
         <is>
           <t>朝に勝つ奴が1日に勝つ 
 ・5時台に起きる 
@@ -56645,25 +56622,25 @@
 俺は朝を変えて人生変わった。</t>
         </is>
       </c>
-      <c r="C1925" t="n">
+      <c r="C1924" t="n">
         <v>75</v>
       </c>
-      <c r="D1925" t="n">
+      <c r="D1924" t="n">
         <v>7</v>
       </c>
-      <c r="E1925" t="inlineStr">
+      <c r="E1924" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1926">
-      <c r="A1926" t="inlineStr">
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
         <is>
           <t>2026-06-07 05:16:39</t>
         </is>
       </c>
-      <c r="B1926" t="inlineStr">
+      <c r="B1925" t="inlineStr">
         <is>
           <t>継続のコツは頑張らないこと 
 ・100点→3日で挫折 
@@ -56671,25 +56648,25 @@
 続けることが全て。</t>
         </is>
       </c>
-      <c r="C1926" t="n">
+      <c r="C1925" t="n">
         <v>27</v>
       </c>
-      <c r="D1926" t="n">
+      <c r="D1925" t="n">
         <v>1</v>
       </c>
-      <c r="E1926" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1927">
-      <c r="A1927" t="inlineStr">
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
         <is>
           <t>2026-06-07 08:09:56</t>
         </is>
       </c>
-      <c r="B1927" t="inlineStr">
+      <c r="B1926" t="inlineStr">
         <is>
           <t>やる気が落ちた時の儀式を持っておくといい。
 俺は最近、作業で疲れたらヤドーム（タイのお土産）を吸引することにしています。
@@ -56699,25 +56676,25 @@
 もいいかもです。 https://t.co/DDk9fQcuka https://t.co/JVZTWTYvgs</t>
         </is>
       </c>
-      <c r="C1927" t="n">
+      <c r="C1926" t="n">
         <v>18</v>
       </c>
-      <c r="D1927" t="n">
+      <c r="D1926" t="n">
         <v>1</v>
       </c>
-      <c r="E1927" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1928">
-      <c r="A1928" t="inlineStr">
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
         <is>
           <t>2026-06-07 08:18:38</t>
         </is>
       </c>
-      <c r="B1928" t="inlineStr">
+      <c r="B1927" t="inlineStr">
         <is>
           <t>モテることが簡単になった理由。
 ・インターネットポルノの普及
@@ -56729,50 +56706,50 @@
 私の発信を長く見ている人は有利。</t>
         </is>
       </c>
-      <c r="C1928" t="n">
+      <c r="C1927" t="n">
         <v>84</v>
       </c>
-      <c r="D1928" t="n">
+      <c r="D1927" t="n">
         <v>9</v>
       </c>
-      <c r="E1928" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1929">
-      <c r="A1929" t="inlineStr">
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
         <is>
           <t>2026-06-07 08:22:53</t>
         </is>
       </c>
-      <c r="B1929" t="inlineStr">
+      <c r="B1928" t="inlineStr">
         <is>
           <t>「筋トレしてない男はゲイ」「童貞は生物として終わり」くらいの雰囲気があった方が社会にとって良いと思う。
 多様性を謳う系のリベラルは害悪。
 でも、これに洗脳されている男が多いから、俺らだけが良い思いできるんだけどね。 https://t.co/Y7rLnPvKEM</t>
         </is>
       </c>
-      <c r="C1929" t="n">
+      <c r="C1928" t="n">
         <v>45</v>
       </c>
-      <c r="D1929" t="n">
+      <c r="D1928" t="n">
         <v>1</v>
       </c>
-      <c r="E1929" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1930">
-      <c r="A1930" t="inlineStr">
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
         <is>
           <t>2026-06-07 09:06:12</t>
         </is>
       </c>
-      <c r="B1930" t="inlineStr">
+      <c r="B1929" t="inlineStr">
         <is>
           <t>毎日、行動してくださる方が現れてとても嬉しいです。
 数年前まで私は「クラスで一言も喋らない自閉症のチー牛」でした。
@@ -56780,25 +56757,25 @@
 これを見たあなたは今後人生で女や金、憂鬱な人生に困ることはないです。… https://t.co/16wOk9Tj8f</t>
         </is>
       </c>
-      <c r="C1930" t="n">
+      <c r="C1929" t="n">
         <v>4</v>
       </c>
-      <c r="D1930" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1930" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1931">
-      <c r="A1931" t="inlineStr">
+      <c r="D1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
         <is>
           <t>2026-06-07 09:20:00</t>
         </is>
       </c>
-      <c r="B1931" t="inlineStr">
+      <c r="B1930" t="inlineStr">
         <is>
           <t>あなたが時間貧乏である理由 
 ①汚部屋 
@@ -56813,25 +56790,25 @@
 要領がいい人は、これの逆を行きます。</t>
         </is>
       </c>
-      <c r="C1931" t="n">
+      <c r="C1930" t="n">
         <v>123</v>
       </c>
-      <c r="D1931" t="n">
+      <c r="D1930" t="n">
         <v>14</v>
       </c>
-      <c r="E1931" t="inlineStr">
+      <c r="E1930" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1932">
-      <c r="A1932" t="inlineStr">
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
         <is>
           <t>2026-06-07 09:41:00</t>
         </is>
       </c>
-      <c r="B1932" t="inlineStr">
+      <c r="B1931" t="inlineStr">
         <is>
           <t>清潔感を出すためにやること 
 ・眉毛を整える 
@@ -56844,11 +56821,34 @@
 やって当たり前のこと。</t>
         </is>
       </c>
+      <c r="C1931" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-06-07 09:47:57</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1932" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D1932" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1932" t="inlineStr">
         <is>
@@ -56859,33 +56859,10 @@
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>2026-06-07 09:47:57</t>
+          <t>2026-06-07 10:45:00</t>
         </is>
       </c>
       <c r="B1933" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1933" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1933" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1933" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1934">
-      <c r="A1934" t="inlineStr">
-        <is>
-          <t>2026-06-07 10:45:00</t>
-        </is>
-      </c>
-      <c r="B1934" t="inlineStr">
         <is>
           <t>大学デビュー失敗した陰キャたちへ 
 結論、挽回は無理。 
@@ -56900,25 +56877,25 @@
 種まきの期間だと思え。</t>
         </is>
       </c>
-      <c r="C1934" t="n">
+      <c r="C1933" t="n">
         <v>165</v>
       </c>
-      <c r="D1934" t="n">
+      <c r="D1933" t="n">
         <v>9</v>
       </c>
-      <c r="E1934" t="inlineStr">
+      <c r="E1933" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
     </row>
-    <row r="1935">
-      <c r="A1935" t="inlineStr">
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
         <is>
           <t>2026-06-07 10:57:46</t>
         </is>
       </c>
-      <c r="B1935" t="inlineStr">
+      <c r="B1934" t="inlineStr">
         <is>
           <t>私はスポーツ観戦大好きで、ニート時代は深夜にプレミアリーグ見まくっていたサカ豚。
 でも、間違いなく人の応援をしている場合じゃなかった。
@@ -56926,48 +56903,48 @@
 スポーツ観戦はすでにやることを終えた上級国民の娯楽。 https://t.co/0yTrug56kv</t>
         </is>
       </c>
+      <c r="C1934" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-06-07 11:20:26</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1935" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D1935" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1935" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>2026-06-07 11:20:26</t>
+          <t>2026-06-07 11:47:00</t>
         </is>
       </c>
       <c r="B1936" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1936" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1936" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1936" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1937">
-      <c r="A1937" t="inlineStr">
-        <is>
-          <t>2026-06-07 11:47:00</t>
-        </is>
-      </c>
-      <c r="B1937" t="inlineStr">
         <is>
           <t>早起きできない奴の特徴 
 ・寝る時間が遅い 
@@ -56983,25 +56960,25 @@
 ・8~9時間確保する</t>
         </is>
       </c>
-      <c r="C1937" t="n">
+      <c r="C1936" t="n">
         <v>44</v>
       </c>
-      <c r="D1937" t="n">
+      <c r="D1936" t="n">
         <v>6</v>
       </c>
-      <c r="E1937" t="inlineStr">
+      <c r="E1936" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1938">
-      <c r="A1938" t="inlineStr">
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
         <is>
           <t>2026-06-07 21:59:00</t>
         </is>
       </c>
-      <c r="B1938" t="inlineStr">
+      <c r="B1937" t="inlineStr">
         <is>
           <t>朝コーヒーがあなたにもたらすもの 
 ・集中力の爆上がり 
@@ -57015,48 +56992,48 @@
 俺はブラックコーヒー飲んで爆速でポストを量産している。</t>
         </is>
       </c>
+      <c r="C1937" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:45:52</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
+        </is>
+      </c>
       <c r="C1938" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D1938" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1938" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1939">
       <c r="A1939" t="inlineStr">
         <is>
-          <t>2026-06-08 02:45:52</t>
+          <t>2026-06-08 03:03:37</t>
         </is>
       </c>
       <c r="B1939" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
-        </is>
-      </c>
-      <c r="C1939" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1939" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1939" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1940">
-      <c r="A1940" t="inlineStr">
-        <is>
-          <t>2026-06-08 03:03:37</t>
-        </is>
-      </c>
-      <c r="B1940" t="inlineStr">
         <is>
           <t>地味にQOLを上げる方法
 ・歯ブラシ
@@ -57067,25 +57044,25 @@
 いつも使う物に少し金払うだけで、QOLは上がる。</t>
         </is>
       </c>
-      <c r="C1940" t="n">
+      <c r="C1939" t="n">
         <v>66</v>
       </c>
-      <c r="D1940" t="n">
+      <c r="D1939" t="n">
         <v>5</v>
       </c>
-      <c r="E1940" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1941">
-      <c r="A1941" t="inlineStr">
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
         <is>
           <t>2026-06-08 07:49:00</t>
         </is>
       </c>
-      <c r="B1941" t="inlineStr">
+      <c r="B1940" t="inlineStr">
         <is>
           <t>睡眠不足で筋トレしても意味ない 
 ・筋肉は寝てる間に成長する 
@@ -57095,25 +57072,25 @@
 まずは寝ろ。</t>
         </is>
       </c>
-      <c r="C1941" t="n">
+      <c r="C1940" t="n">
         <v>33</v>
       </c>
-      <c r="D1941" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1941" t="inlineStr">
+      <c r="D1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1940" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1942">
-      <c r="A1942" t="inlineStr">
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
         <is>
           <t>2026-06-08 08:43:00</t>
         </is>
       </c>
-      <c r="B1942" t="inlineStr">
+      <c r="B1941" t="inlineStr">
         <is>
           <t>”極振り”が人生を変える。
 女攻略したいなら
@@ -57125,25 +57102,25 @@
 俺はこの極振りでコンプを克服してきた。</t>
         </is>
       </c>
-      <c r="C1942" t="n">
+      <c r="C1941" t="n">
         <v>113</v>
       </c>
-      <c r="D1942" t="n">
+      <c r="D1941" t="n">
         <v>10</v>
       </c>
-      <c r="E1942" t="inlineStr">
+      <c r="E1941" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1943">
-      <c r="A1943" t="inlineStr">
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
         <is>
           <t>2026-06-08 09:14:00</t>
         </is>
       </c>
-      <c r="B1943" t="inlineStr">
+      <c r="B1942" t="inlineStr">
         <is>
           <t>童貞は
 ・身長10cm盛る
@@ -57154,25 +57131,25 @@
 「俺のち〇こを必要としている人はいる」という自信にはなる。</t>
         </is>
       </c>
-      <c r="C1943" t="n">
+      <c r="C1942" t="n">
         <v>158</v>
       </c>
-      <c r="D1943" t="n">
+      <c r="D1942" t="n">
         <v>6</v>
       </c>
-      <c r="E1943" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1944">
-      <c r="A1944" t="inlineStr">
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
         <is>
           <t>2026-06-08 10:00:01</t>
         </is>
       </c>
-      <c r="B1944" t="inlineStr">
+      <c r="B1943" t="inlineStr">
         <is>
           <t>「チー牛家庭」の問題点。
 ・食事から教育方針まで、すべて母親が決める 
@@ -57183,25 +57160,25 @@
 はしごを外され、決断力を育ててこなかった</t>
         </is>
       </c>
-      <c r="C1944" t="n">
+      <c r="C1943" t="n">
         <v>32</v>
       </c>
-      <c r="D1944" t="n">
+      <c r="D1943" t="n">
         <v>1</v>
       </c>
-      <c r="E1944" t="inlineStr">
+      <c r="E1943" t="inlineStr">
         <is>
           <t>exam</t>
         </is>
       </c>
     </row>
-    <row r="1945">
-      <c r="A1945" t="inlineStr">
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
         <is>
           <t>2026-06-08 10:41:00</t>
         </is>
       </c>
-      <c r="B1945" t="inlineStr">
+      <c r="B1944" t="inlineStr">
         <is>
           <t>正直、学生時代に”イジメすらもされないような陰キャ”だった方がSNSやマチアプで人気者になるのは厳しい。 
 これらはあくまで拡声器。 
@@ -57209,25 +57186,25 @@
 やることは自己啓発陰キャになり、自分本体をひたすら磨くこと。</t>
         </is>
       </c>
-      <c r="C1945" t="n">
+      <c r="C1944" t="n">
         <v>53</v>
       </c>
-      <c r="D1945" t="n">
+      <c r="D1944" t="n">
         <v>4</v>
       </c>
-      <c r="E1945" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1946">
-      <c r="A1946" t="inlineStr">
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
         <is>
           <t>2026-06-08 11:09:00</t>
         </is>
       </c>
-      <c r="B1946" t="inlineStr">
+      <c r="B1945" t="inlineStr">
         <is>
           <t>スマホ中毒がデフォルトの時代。 
 そこを脱して「静寂」を手に入れた人間は、
@@ -57235,8 +57212,31 @@
 周りが耽溺している間に、あなたは淡々とリアルな成果を積み上げる側へ回れ。</t>
         </is>
       </c>
+      <c r="C1945" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:14:05</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1946" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D1946" t="n">
         <v>1</v>
@@ -57250,33 +57250,10 @@
     <row r="1947">
       <c r="A1947" t="inlineStr">
         <is>
-          <t>2026-06-08 11:14:05</t>
+          <t>2026-06-08 12:00:01</t>
         </is>
       </c>
       <c r="B1947" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1947" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1947" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1947" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1948">
-      <c r="A1948" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:00:01</t>
-        </is>
-      </c>
-      <c r="B1948" t="inlineStr">
         <is>
           <t>睡眠を削ると時間が減る。
 判断力低下
@@ -57289,25 +57266,25 @@
 睡眠を削るのは「ここぞ」という時だけでいい。</t>
         </is>
       </c>
-      <c r="C1948" t="n">
+      <c r="C1947" t="n">
         <v>29</v>
       </c>
-      <c r="D1948" t="n">
+      <c r="D1947" t="n">
         <v>1</v>
       </c>
-      <c r="E1948" t="inlineStr">
+      <c r="E1947" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1949">
-      <c r="A1949" t="inlineStr">
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
         <is>
           <t>2026-06-09 07:28:00</t>
         </is>
       </c>
-      <c r="B1949" t="inlineStr">
+      <c r="B1948" t="inlineStr">
         <is>
           <t>モテる男は周りから固めていく。
 まず本命の友達から評価を得てクチコミを広める。
@@ -57315,25 +57292,25 @@
 逆に非モテはガンギマリで女にピンポイントで、くそきもアプローチだけする。</t>
         </is>
       </c>
-      <c r="C1949" t="n">
+      <c r="C1948" t="n">
         <v>23</v>
       </c>
-      <c r="D1949" t="n">
+      <c r="D1948" t="n">
         <v>2</v>
       </c>
-      <c r="E1949" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1950">
-      <c r="A1950" t="inlineStr">
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
         <is>
           <t>2026-06-09 08:06:00</t>
         </is>
       </c>
-      <c r="B1950" t="inlineStr">
+      <c r="B1949" t="inlineStr">
         <is>
           <t>3日坊主の奴はSNSを見すぎ。
 他人の投稿ばかり見て、隣の芝生が青く見えるがゆえ、やることがブレている。
@@ -57342,25 +57319,25 @@
 フォローは厳選している。</t>
         </is>
       </c>
-      <c r="C1950" t="n">
+      <c r="C1949" t="n">
         <v>22</v>
       </c>
-      <c r="D1950" t="n">
+      <c r="D1949" t="n">
         <v>1</v>
       </c>
-      <c r="E1950" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1951">
-      <c r="A1951" t="inlineStr">
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
         <is>
           <t>2026-06-09 08:50:00</t>
         </is>
       </c>
-      <c r="B1951" t="inlineStr">
+      <c r="B1950" t="inlineStr">
         <is>
           <t>テストステロンを1日で取り戻す方法 
 ・8時間睡眠 
@@ -57376,25 +57353,25 @@
 翌日には余裕で回復してる。</t>
         </is>
       </c>
-      <c r="C1951" t="n">
+      <c r="C1950" t="n">
         <v>953</v>
       </c>
-      <c r="D1951" t="n">
+      <c r="D1950" t="n">
         <v>66</v>
       </c>
-      <c r="E1951" t="inlineStr">
+      <c r="E1950" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1952">
-      <c r="A1952" t="inlineStr">
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
         <is>
           <t>2026-06-09 09:30:00</t>
         </is>
       </c>
-      <c r="B1952" t="inlineStr">
+      <c r="B1951" t="inlineStr">
         <is>
           <t>・「ヒョロガリがフリーウェイト使うのは申し訳ない。」 
 ・「インターバル3分も取るのは気まずい。」 
@@ -57404,8 +57381,31 @@
 そして、あなたも他の会員と同じ額の会費を払ってます。</t>
         </is>
       </c>
+      <c r="C1951" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:43:01</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
+        </is>
+      </c>
       <c r="C1952" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D1952" t="n">
         <v>0</v>
@@ -57419,12 +57419,12 @@
     <row r="1953">
       <c r="A1953" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:01</t>
+          <t>2026-06-09 09:43:52</t>
         </is>
       </c>
       <c r="B1953" t="inlineStr">
         <is>
-          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C1953" t="n">
@@ -57442,33 +57442,10 @@
     <row r="1954">
       <c r="A1954" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:52</t>
+          <t>2026-06-09 10:06:00</t>
         </is>
       </c>
       <c r="B1954" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1954" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1954" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1954" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1955">
-      <c r="A1955" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:06:00</t>
-        </is>
-      </c>
-      <c r="B1955" t="inlineStr">
         <is>
           <t>受け身な男の脳内  
 小学生時代 
@@ -57483,50 +57460,50 @@
 「出世出来たら結婚出来るんだろうなぁ」</t>
         </is>
       </c>
-      <c r="C1955" t="n">
+      <c r="C1954" t="n">
         <v>84</v>
       </c>
-      <c r="D1955" t="n">
+      <c r="D1954" t="n">
         <v>6</v>
       </c>
-      <c r="E1955" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1956">
-      <c r="A1956" t="inlineStr">
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
         <is>
           <t>2026-06-09 10:12:00</t>
         </is>
       </c>
-      <c r="B1956" t="inlineStr">
+      <c r="B1955" t="inlineStr">
         <is>
           <t>スマホ中毒者は自分だけの「対策ノウハウ」を作っていけ。
 確かにタイムロック、瞑想等は効果はあるが単なるテクニック論に過ぎない。
 自分の癖を見つけて、ピンポイントで対策する方が効果的。</t>
         </is>
       </c>
-      <c r="C1956" t="n">
+      <c r="C1955" t="n">
         <v>19</v>
       </c>
-      <c r="D1956" t="n">
+      <c r="D1955" t="n">
         <v>2</v>
       </c>
-      <c r="E1956" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1957">
-      <c r="A1957" t="inlineStr">
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
         <is>
           <t>2026-06-09 10:48:00</t>
         </is>
       </c>
-      <c r="B1957" t="inlineStr">
+      <c r="B1956" t="inlineStr">
         <is>
           <t>非モテのコミュニケーション悪癖 
 ・名前を呼べない 
@@ -57541,25 +57518,25 @@
 2つ以上当てはまれば、キモがれらている可能性大。</t>
         </is>
       </c>
-      <c r="C1957" t="n">
+      <c r="C1956" t="n">
         <v>54</v>
       </c>
-      <c r="D1957" t="n">
+      <c r="D1956" t="n">
         <v>6</v>
       </c>
-      <c r="E1957" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1958">
-      <c r="A1958" t="inlineStr">
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
         <is>
           <t>2026-06-09 11:20:00</t>
         </is>
       </c>
-      <c r="B1958" t="inlineStr">
+      <c r="B1957" t="inlineStr">
         <is>
           <t>モテテクは結果論。 
 ・返信を遅らせる 
@@ -57569,49 +57546,49 @@
 確かに非モテのモテテク武装は大事。 だから無意味ではないが、 結果論であることを理解した上で使った方がいい。</t>
         </is>
       </c>
+      <c r="C1957" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1957" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:30:00</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>筋トレをやらない理由はない。 
+毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
+        </is>
+      </c>
       <c r="C1958" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1958" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1958" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="1959">
       <c r="A1959" t="inlineStr">
         <is>
-          <t>2026-06-09 11:30:00</t>
+          <t>2026-06-10 07:40:00</t>
         </is>
       </c>
       <c r="B1959" t="inlineStr">
-        <is>
-          <t>筋トレをやらない理由はない。 
-毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
-        </is>
-      </c>
-      <c r="C1959" t="n">
-        <v>22</v>
-      </c>
-      <c r="D1959" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1959" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="1960">
-      <c r="A1960" t="inlineStr">
-        <is>
-          <t>2026-06-10 07:40:00</t>
-        </is>
-      </c>
-      <c r="B1960" t="inlineStr">
         <is>
           <t>スマホが近くにあるだけで頭が悪くなる。
 脳が「スマホを無視しろ」とコマンドを送るのにリソースを割くからです。
@@ -57620,25 +57597,25 @@
 物理的な距離だけがあなたの脳を解放します。</t>
         </is>
       </c>
-      <c r="C1960" t="n">
+      <c r="C1959" t="n">
         <v>15</v>
       </c>
-      <c r="D1960" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1960" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1961">
-      <c r="A1961" t="inlineStr">
+      <c r="D1959" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
         <is>
           <t>2026-06-10 08:23:00</t>
         </is>
       </c>
-      <c r="B1961" t="inlineStr">
+      <c r="B1960" t="inlineStr">
         <is>
           <t>一番、結果が出るのはコンフォートゾーンでガチガチにハメ技決めてる時。
 ・毎日、同じ食事を摂る
@@ -57648,25 +57625,25 @@
 「つまらない」と感じると思うが、いちいち新しいことを始める必要はない。君の努力は正しい。</t>
         </is>
       </c>
-      <c r="C1961" t="n">
+      <c r="C1960" t="n">
         <v>45</v>
       </c>
-      <c r="D1961" t="n">
+      <c r="D1960" t="n">
         <v>5</v>
       </c>
-      <c r="E1961" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1962">
-      <c r="A1962" t="inlineStr">
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
         <is>
           <t>2026-06-10 08:42:00</t>
         </is>
       </c>
-      <c r="B1962" t="inlineStr">
+      <c r="B1961" t="inlineStr">
         <is>
           <t>ストイックには2種類ある。  
 ・サボらない努力マシーン 
@@ -57676,25 +57653,25 @@
 そして、翌日には何事もなかったようにルーティンに戻る。</t>
         </is>
       </c>
-      <c r="C1962" t="n">
+      <c r="C1961" t="n">
         <v>31</v>
       </c>
-      <c r="D1962" t="n">
+      <c r="D1961" t="n">
         <v>5</v>
       </c>
-      <c r="E1962" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1963">
-      <c r="A1963" t="inlineStr">
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
         <is>
           <t>2026-06-10 09:20:00</t>
         </is>
       </c>
-      <c r="B1963" t="inlineStr">
+      <c r="B1962" t="inlineStr">
         <is>
           <t>筋トレで得たもの 
 ・自信 
@@ -57709,25 +57686,25 @@
 やらない理由がない。</t>
         </is>
       </c>
-      <c r="C1963" t="n">
+      <c r="C1962" t="n">
         <v>59</v>
       </c>
-      <c r="D1963" t="n">
+      <c r="D1962" t="n">
         <v>4</v>
       </c>
-      <c r="E1963" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1964">
-      <c r="A1964" t="inlineStr">
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
         <is>
           <t>2026-06-10 09:36:00</t>
         </is>
       </c>
-      <c r="B1964" t="inlineStr">
+      <c r="B1963" t="inlineStr">
         <is>
           <t>ヒョロガリのマインド
 「ハイTな食事🤓（2300kcal）」
@@ -57739,25 +57716,25 @@
 黙って食え。</t>
         </is>
       </c>
-      <c r="C1964" t="n">
+      <c r="C1963" t="n">
         <v>47</v>
       </c>
-      <c r="D1964" t="n">
+      <c r="D1963" t="n">
         <v>1</v>
       </c>
-      <c r="E1964" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1965">
-      <c r="A1965" t="inlineStr">
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
         <is>
           <t>2026-06-10 10:00:00</t>
         </is>
       </c>
-      <c r="B1965" t="inlineStr">
+      <c r="B1964" t="inlineStr">
         <is>
           <t>自信がない奴の特徴 
 ・姿勢が悪い 
@@ -57774,25 +57751,25 @@
 俺は筋トレで体を変えてから自信がついた。</t>
         </is>
       </c>
-      <c r="C1965" t="n">
+      <c r="C1964" t="n">
         <v>58</v>
       </c>
-      <c r="D1965" t="n">
+      <c r="D1964" t="n">
         <v>5</v>
       </c>
-      <c r="E1965" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1966">
-      <c r="A1966" t="inlineStr">
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
         <is>
           <t>2026-06-10 10:45:00</t>
         </is>
       </c>
-      <c r="B1966" t="inlineStr">
+      <c r="B1965" t="inlineStr">
         <is>
           <t>スマホ中毒の唯一の基準は
 「目標達成を妨げているか否か」。
@@ -57803,11 +57780,34 @@
 スクリーンタイムよりも使い方を見直せ。</t>
         </is>
       </c>
+      <c r="C1965" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1965" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:49:46</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
+        </is>
+      </c>
       <c r="C1966" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D1966" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1966" t="inlineStr">
         <is>
@@ -57818,33 +57818,10 @@
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>2026-06-10 10:49:46</t>
+          <t>2026-06-10 11:00:03</t>
         </is>
       </c>
       <c r="B1967" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
-        </is>
-      </c>
-      <c r="C1967" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1967" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1967" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1968">
-      <c r="A1968" t="inlineStr">
-        <is>
-          <t>2026-06-10 11:00:03</t>
-        </is>
-      </c>
-      <c r="B1968" t="inlineStr">
         <is>
           <t>男磨きしている人が陥りがちな失敗は「禁欲の目的化」。
 確かにオナ禁、コールドシャワー、瞑想といった習慣はスピではなく、科学的根拠がある。
@@ -57852,25 +57829,25 @@
 あくまで廃人が自己管理能力を上げる手段でしかない。</t>
         </is>
       </c>
-      <c r="C1968" t="n">
+      <c r="C1967" t="n">
         <v>46</v>
       </c>
-      <c r="D1968" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1968" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1969">
-      <c r="A1969" t="inlineStr">
+      <c r="D1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
         <is>
           <t>2026-06-10 11:29:00</t>
         </is>
       </c>
-      <c r="B1969" t="inlineStr">
+      <c r="B1968" t="inlineStr">
         <is>
           <t>一般的な弱者男性の日常。
 平日は経営者のために働き、上司と得意先に頭を下げる。帰宅後は推しの配信で時間を潰す。 
@@ -57880,25 +57857,25 @@
 哲学的ゾンビとはこのこと。</t>
         </is>
       </c>
-      <c r="C1969" t="n">
+      <c r="C1968" t="n">
         <v>44</v>
       </c>
-      <c r="D1969" t="n">
+      <c r="D1968" t="n">
         <v>6</v>
       </c>
-      <c r="E1969" t="inlineStr">
+      <c r="E1968" t="inlineStr">
         <is>
           <t>sunday</t>
         </is>
       </c>
     </row>
-    <row r="1970">
-      <c r="A1970" t="inlineStr">
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
         <is>
           <t>2026-06-10 12:06:00</t>
         </is>
       </c>
-      <c r="B1970" t="inlineStr">
+      <c r="B1969" t="inlineStr">
         <is>
           <t>睡眠を30分削ると、 
 ・テストステロン低下 
@@ -57911,25 +57888,25 @@
 そして、翌朝はアラーム無しで起きる奴こそが強者。</t>
         </is>
       </c>
-      <c r="C1970" t="n">
+      <c r="C1969" t="n">
         <v>27</v>
       </c>
-      <c r="D1970" t="n">
+      <c r="D1969" t="n">
         <v>4</v>
       </c>
-      <c r="E1970" t="inlineStr">
+      <c r="E1969" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1971">
-      <c r="A1971" t="inlineStr">
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
         <is>
           <t>2026-06-11 06:18:00</t>
         </is>
       </c>
-      <c r="B1971" t="inlineStr">
+      <c r="B1970" t="inlineStr">
         <is>
           <t>弱者男性の先天的欠点
 ・短足
@@ -57945,25 +57922,25 @@
 複数当てはまると、結構人生ハードモード。</t>
         </is>
       </c>
-      <c r="C1971" t="n">
+      <c r="C1970" t="n">
         <v>38</v>
       </c>
-      <c r="D1971" t="n">
+      <c r="D1970" t="n">
         <v>2</v>
       </c>
-      <c r="E1971" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1972">
-      <c r="A1972" t="inlineStr">
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
         <is>
           <t>2026-06-11 06:29:00</t>
         </is>
       </c>
-      <c r="B1972" t="inlineStr">
+      <c r="B1971" t="inlineStr">
         <is>
           <t>ヒョロガリは週3回、BIG3をそれぞれやるだけで十分全身を鍛えられる。
 5分割で2時間は多分、続かない。
@@ -57971,25 +57948,25 @@
 週3は忙しくても行ける。</t>
         </is>
       </c>
-      <c r="C1972" t="n">
+      <c r="C1971" t="n">
         <v>36</v>
       </c>
-      <c r="D1972" t="n">
+      <c r="D1971" t="n">
         <v>1</v>
       </c>
-      <c r="E1972" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1973">
-      <c r="A1973" t="inlineStr">
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
         <is>
           <t>2026-06-11 08:44:00</t>
         </is>
       </c>
-      <c r="B1973" t="inlineStr">
+      <c r="B1972" t="inlineStr">
         <is>
           <t>俺が童貞(20歳)に戻ったらやること 
 ・ ジム入会 
@@ -58003,11 +57980,34 @@
 ・ブスでもBBAでも片っ端からアプローチ</t>
         </is>
       </c>
+      <c r="C1972" t="n">
+        <v>261</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:11:09</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1973" t="n">
-        <v>261</v>
+        <v>6</v>
       </c>
       <c r="D1973" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E1973" t="inlineStr">
         <is>
@@ -58018,16 +58018,16 @@
     <row r="1974">
       <c r="A1974" t="inlineStr">
         <is>
-          <t>2026-06-11 09:11:09</t>
+          <t>2026-06-11 09:12:47</t>
         </is>
       </c>
       <c r="B1974" t="inlineStr">
         <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
         </is>
       </c>
       <c r="C1974" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D1974" t="n">
         <v>0</v>
@@ -58041,33 +58041,10 @@
     <row r="1975">
       <c r="A1975" t="inlineStr">
         <is>
-          <t>2026-06-11 09:12:47</t>
+          <t>2026-06-11 09:13:00</t>
         </is>
       </c>
       <c r="B1975" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
-        </is>
-      </c>
-      <c r="C1975" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1975" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1975" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1976">
-      <c r="A1976" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:13:00</t>
-        </is>
-      </c>
-      <c r="B1976" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。 環境を変える努力をしろ。 
@@ -58081,11 +58058,34 @@
 ・やるか死ぬかの状況</t>
         </is>
       </c>
+      <c r="C1975" t="n">
+        <v>54</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:15:26</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1976" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D1976" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E1976" t="inlineStr">
         <is>
@@ -58096,33 +58096,10 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>2026-06-11 09:15:26</t>
+          <t>2026-06-11 09:45:00</t>
         </is>
       </c>
       <c r="B1977" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1977" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1977" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1977" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1978">
-      <c r="A1978" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:45:00</t>
-        </is>
-      </c>
-      <c r="B1978" t="inlineStr">
         <is>
           <t>あなたがチー牛顔である理由 
 ・一重 
@@ -58136,48 +58113,48 @@
 ・体脂肪率20%以上</t>
         </is>
       </c>
+      <c r="C1977" t="n">
+        <v>280</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:48:30</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
+        </is>
+      </c>
       <c r="C1978" t="n">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="D1978" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E1978" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lunch</t>
         </is>
       </c>
     </row>
     <row r="1979">
       <c r="A1979" t="inlineStr">
         <is>
-          <t>2026-06-11 09:48:30</t>
+          <t>2026-06-11 10:10:00</t>
         </is>
       </c>
       <c r="B1979" t="inlineStr">
-        <is>
-          <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
-        </is>
-      </c>
-      <c r="C1979" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1979" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1979" t="inlineStr">
-        <is>
-          <t>lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1980">
-      <c r="A1980" t="inlineStr">
-        <is>
-          <t>2026-06-11 10:10:00</t>
-        </is>
-      </c>
-      <c r="B1980" t="inlineStr">
         <is>
           <t>孤独でもメンタルを安定させる方法 
 男磨きは孤独との戦いになるので実践してほしい。
@@ -58191,25 +58168,25 @@
 むしろ人生はいい方向に進む。</t>
         </is>
       </c>
-      <c r="C1980" t="n">
+      <c r="C1979" t="n">
         <v>81</v>
       </c>
-      <c r="D1980" t="n">
+      <c r="D1979" t="n">
         <v>7</v>
       </c>
-      <c r="E1980" t="inlineStr">
+      <c r="E1979" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1981">
-      <c r="A1981" t="inlineStr">
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
         <is>
           <t>2026-06-11 10:37:00</t>
         </is>
       </c>
-      <c r="B1981" t="inlineStr">
+      <c r="B1980" t="inlineStr">
         <is>
           <t>スマホ断ちがあなたに与えるもの 
 ・思考力 
@@ -58223,59 +58200,82 @@
 SNSを受動的に見ることは百害あって一利なし。</t>
         </is>
       </c>
+      <c r="C1980" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-06-11 10:45:10</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1981" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D1981" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1981" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>2026-06-11 10:45:10</t>
+          <t>2026-06-11 11:26:00</t>
         </is>
       </c>
       <c r="B1982" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1982" t="n">
-        <v>3</v>
-      </c>
-      <c r="D1982" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1982" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1983">
-      <c r="A1983" t="inlineStr">
-        <is>
-          <t>2026-06-11 11:26:00</t>
-        </is>
-      </c>
-      <c r="B1983" t="inlineStr">
         <is>
           <t>男磨きのゴールは「俺は一生、セ◯クスに困らない」という自信を作ること。 
 この自信がモテ以外の人生の楽しみに集中させてくれる。 そして、余裕を生みさらにモテを生んでくれる。 
 だから、俺は「ブスでもBBAでもいいから片っ端からいけ」と言ってるのよ。</t>
         </is>
       </c>
+      <c r="C1982" t="n">
+        <v>70</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:30:28</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1983" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D1983" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1983" t="inlineStr">
         <is>
@@ -58286,33 +58286,10 @@
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>2026-06-11 11:30:28</t>
+          <t>2026-06-12 08:50:00</t>
         </is>
       </c>
       <c r="B1984" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1984" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1984" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
-        <is>
-          <t>2026-06-12 08:50:00</t>
-        </is>
-      </c>
-      <c r="B1985" t="inlineStr">
         <is>
           <t>奥手な童貞の脳内  
 小学生時代 
@@ -58327,25 +58304,25 @@
 「昇進して女を見返すやで！」</t>
         </is>
       </c>
-      <c r="C1985" t="n">
+      <c r="C1984" t="n">
         <v>274</v>
       </c>
-      <c r="D1985" t="n">
+      <c r="D1984" t="n">
         <v>9</v>
       </c>
-      <c r="E1985" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1986">
-      <c r="A1986" t="inlineStr">
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
         <is>
           <t>2026-06-12 09:20:00</t>
         </is>
       </c>
-      <c r="B1986" t="inlineStr">
+      <c r="B1985" t="inlineStr">
         <is>
           <t>退化を促すドーパミン 
 ・悪口 
@@ -58363,11 +58340,34 @@
 ドーパミンを得る対象を変えるだけで、人生は変わる。</t>
         </is>
       </c>
+      <c r="C1985" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:41:33</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1986" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D1986" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1986" t="inlineStr">
         <is>
@@ -58378,33 +58378,10 @@
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>2026-06-12 09:41:33</t>
+          <t>2026-06-12 10:00:02</t>
         </is>
       </c>
       <c r="B1987" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1987" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:00:02</t>
-        </is>
-      </c>
-      <c r="B1988" t="inlineStr">
         <is>
           <t>非モテはいきなり本命に行くな。
 あなたが「俺でもイケるかも」と思っている女にさえ、チキってアプローチできない時点で無理です。 
@@ -58413,25 +58390,25 @@
 まずは男磨きをし、ブスとBBAを口説くことから始めてください。</t>
         </is>
       </c>
-      <c r="C1988" t="n">
+      <c r="C1987" t="n">
         <v>14</v>
       </c>
-      <c r="D1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1988" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
+      <c r="D1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
         <is>
           <t>2026-06-12 10:28:00</t>
         </is>
       </c>
-      <c r="B1989" t="inlineStr">
+      <c r="B1988" t="inlineStr">
         <is>
           <t>負け犬の遠吠え集 
 ・「独身貴族」 
@@ -58445,11 +58422,34 @@
 逆に素直に「うらやましい」「悔しい」が言える男は強い。</t>
         </is>
       </c>
+      <c r="C1988" t="n">
+        <v>28</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:40:53</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
+        </is>
+      </c>
       <c r="C1989" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D1989" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E1989" t="inlineStr">
         <is>
@@ -58460,16 +58460,16 @@
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>2026-06-12 10:40:53</t>
+          <t>2026-06-12 10:49:07</t>
         </is>
       </c>
       <c r="B1990" t="inlineStr">
         <is>
-          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
       <c r="C1990" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1990" t="n">
         <v>0</v>
@@ -58483,33 +58483,10 @@
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>2026-06-12 10:49:07</t>
+          <t>2026-06-12 10:53:00</t>
         </is>
       </c>
       <c r="B1991" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1991" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1991" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1991" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:53:00</t>
-        </is>
-      </c>
-      <c r="B1992" t="inlineStr">
         <is>
           <t>決定疲れを減らす方法 
 ・デスクの整理 
@@ -58521,36 +58498,60 @@
 これで大事なタスクへの火力が爆上がりします。</t>
         </is>
       </c>
-      <c r="C1992" t="n">
+      <c r="C1991" t="n">
         <v>15</v>
       </c>
-      <c r="D1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1992" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+      <c r="D1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-12 11:17:04</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>男の人生はシンプル。
 唸るほど金を持ち、ジムに行き、女行き倒す。
 他の事はどうでもいい。 https://t.co/9LrSQYOjXd</t>
         </is>
       </c>
+      <c r="C1992" t="n">
+        <v>77</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:46:23</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
+無料で空気を吸った方がコスパいい。</t>
+        </is>
+      </c>
       <c r="C1993" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="D1993" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1993" t="inlineStr">
         <is>
@@ -58561,34 +58562,10 @@
     <row r="1994">
       <c r="A1994" t="inlineStr">
         <is>
-          <t>2026-06-12 11:46:23</t>
+          <t>2026-06-12 12:00:00</t>
         </is>
       </c>
       <c r="B1994" t="inlineStr">
-        <is>
-          <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
-無料で空気を吸った方がコスパいい。</t>
-        </is>
-      </c>
-      <c r="C1994" t="n">
-        <v>19</v>
-      </c>
-      <c r="D1994" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1994" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
-        <is>
-          <t>2026-06-12 12:00:00</t>
-        </is>
-      </c>
-      <c r="B1995" t="inlineStr">
         <is>
           <t>疲れているのに眠れない原因 
 ①反芻思考 
@@ -58600,50 +58577,50 @@
 まずは原因を分析するところから始めよう。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
+      <c r="C1994" t="n">
         <v>11</v>
       </c>
-      <c r="D1995" t="n">
+      <c r="D1994" t="n">
         <v>1</v>
       </c>
-      <c r="E1995" t="inlineStr">
+      <c r="E1994" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-12 12:32:00</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>睡眠の質を測るために、昔はスマートウォッチつけて寝てたけどやめちゃったな。
 理由はゴツゴツしてて睡眠の邪魔になっていたのと、別に計測したからといって質が上がるわけではないから。
 ”翌日のパフォーマンスが向上しているか”という体感こそがエビデンスだと思っています。</t>
         </is>
       </c>
-      <c r="C1996" t="n">
+      <c r="C1995" t="n">
         <v>7</v>
       </c>
-      <c r="D1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1996" t="inlineStr">
+      <c r="D1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1995" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-12 21:47:00</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>朝の水分補給は、ただの真水では睡眠中に失った電解質は取り戻せない。 
 また、電解質が入っていないと飲んだ水が身体に行き届きにくくなる。 
@@ -58651,25 +58628,25 @@
 もしこれが不味くて飲めないなら、「みそ汁」「コーンスープ」「電解質パウダー」でもOK</t>
         </is>
       </c>
-      <c r="C1997" t="n">
+      <c r="C1996" t="n">
         <v>21</v>
       </c>
-      <c r="D1997" t="n">
+      <c r="D1996" t="n">
         <v>2</v>
       </c>
-      <c r="E1997" t="inlineStr">
+      <c r="E1996" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-13 07:32:34</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>スマホ依存症を治すために私がやったこと 
 ・スマホなし1時間散歩 
@@ -58682,25 +58659,25 @@
 そして、SNSを全部PCに移せば、スマホを使う理由は少なくなる。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
+      <c r="C1997" t="n">
         <v>82</v>
       </c>
-      <c r="D1998" t="n">
+      <c r="D1997" t="n">
         <v>4</v>
       </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-13 08:27:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>非モテがチン騎士になる理由。  
 結論、それ以外の関わり方を知らないから。 
@@ -58709,25 +58686,25 @@
 優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
+      <c r="C1998" t="n">
         <v>57</v>
       </c>
-      <c r="D1999" t="n">
+      <c r="D1998" t="n">
         <v>1</v>
       </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-13 09:00:01</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>スマホ依存症の症状 
 ・起きた瞬間にチェック 
@@ -58743,25 +58720,25 @@
 ・21時以降は見ない</t>
         </is>
       </c>
-      <c r="C2000" t="n">
+      <c r="C1999" t="n">
         <v>16</v>
       </c>
-      <c r="D2000" t="n">
+      <c r="D1999" t="n">
         <v>2</v>
       </c>
-      <c r="E2000" t="inlineStr">
+      <c r="E1999" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-13 09:21:45</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>自己満男磨き(笑)と呼ばれている習慣を擁護します。  
 【オナ禁】
@@ -58792,25 +58769,25 @@
 正しく評価して自分に落とし込むことが重要。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
+      <c r="C2000" t="n">
         <v>10</v>
       </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-13 09:28:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>口呼吸が習慣化している人の特徴 
 ①舌が白い 
@@ -58821,25 +58798,25 @@
 高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
+      <c r="C2001" t="n">
         <v>26</v>
       </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-13 10:06:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58853,11 +58830,34 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
+      <c r="C2002" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:00:02</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+        </is>
+      </c>
       <c r="C2003" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D2003" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2003" t="inlineStr">
         <is>
@@ -58868,19 +58868,19 @@
     <row r="2004">
       <c r="A2004" t="inlineStr">
         <is>
-          <t>2026-06-13 11:00:02</t>
+          <t>2026-06-13 11:17:03</t>
         </is>
       </c>
       <c r="B2004" t="inlineStr">
         <is>
-          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C2004" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D2004" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2004" t="inlineStr">
         <is>
@@ -58891,33 +58891,10 @@
     <row r="2005">
       <c r="A2005" t="inlineStr">
         <is>
-          <t>2026-06-13 11:17:03</t>
+          <t>2026-06-13 12:26:00</t>
         </is>
       </c>
       <c r="B2005" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C2005" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
-        <is>
-          <t>2026-06-13 12:26:00</t>
-        </is>
-      </c>
-      <c r="B2006" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58929,25 +58906,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
+      <c r="C2005" t="n">
         <v>16</v>
       </c>
-      <c r="D2006" t="n">
+      <c r="D2005" t="n">
         <v>1</v>
       </c>
-      <c r="E2006" t="inlineStr">
+      <c r="E2005" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58958,25 +58935,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
+      <c r="C2006" t="n">
         <v>19</v>
       </c>
-      <c r="D2007" t="n">
+      <c r="D2006" t="n">
         <v>2</v>
       </c>
-      <c r="E2007" t="inlineStr">
+      <c r="E2006" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58988,25 +58965,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C2008" t="n">
+      <c r="C2007" t="n">
         <v>19</v>
       </c>
-      <c r="D2008" t="n">
+      <c r="D2007" t="n">
         <v>2</v>
       </c>
-      <c r="E2008" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -59023,25 +59000,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
+      <c r="C2008" t="n">
         <v>22</v>
       </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -59057,25 +59034,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
+      <c r="C2009" t="n">
         <v>17</v>
       </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -59088,8 +59065,31 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
+      <c r="C2010" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:07:02</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
+        </is>
+      </c>
       <c r="C2011" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2011" t="n">
         <v>0</v>
@@ -59103,33 +59103,10 @@
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>2026-06-14 09:07:02</t>
+          <t>2026-06-14 09:31:00</t>
         </is>
       </c>
       <c r="B2012" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
-        </is>
-      </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
-        <is>
-          <t>2026-06-14 09:31:00</t>
-        </is>
-      </c>
-      <c r="B2013" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -59145,25 +59122,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -59173,25 +59150,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -59203,25 +59180,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -59233,25 +59210,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -59265,25 +59242,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -59300,25 +59277,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -59328,25 +59305,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -59360,25 +59337,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -59388,25 +59365,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -59417,25 +59394,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -59448,25 +59425,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59476,25 +59453,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59503,25 +59480,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59529,6 +59506,30 @@
 地味なライフハック。</t>
         </is>
       </c>
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:41:41</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>起床3秒後のEAA❌
+起床3秒後の歯磨き⭕</t>
+        </is>
+      </c>
       <c r="C2026" t="n">
         <v>0</v>
       </c>
@@ -59544,34 +59545,10 @@
     <row r="2027">
       <c r="A2027" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-21 07:01:00</t>
         </is>
       </c>
       <c r="B2027" t="inlineStr">
-        <is>
-          <t>起床3秒後のEAA❌
-起床3秒後の歯磨き⭕</t>
-        </is>
-      </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:01:00</t>
-        </is>
-      </c>
-      <c r="B2028" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59584,25 +59561,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59612,6 +59589,29 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:03:13</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+        </is>
+      </c>
       <c r="C2029" t="n">
         <v>0</v>
       </c>
@@ -59627,12 +59627,13 @@
     <row r="2030">
       <c r="A2030" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-19 19:34:04</t>
         </is>
       </c>
       <c r="B2030" t="inlineStr">
         <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
       <c r="C2030" t="n">
@@ -59650,34 +59651,10 @@
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B2031" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B2032" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59685,31 +59662,54 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:46</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
+        </is>
+      </c>
       <c r="C2033" t="n">
         <v>0</v>
       </c>
@@ -59725,33 +59725,10 @@
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>2026-06-16 18:11:46</t>
+          <t>2026-06-16 06:56:00</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
-        <is>
-          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
-        </is>
-      </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:56:00</t>
-        </is>
-      </c>
-      <c r="B2035" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59766,25 +59743,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59795,25 +59772,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59821,25 +59798,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59854,25 +59831,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59883,25 +59860,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59913,25 +59890,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59941,25 +59918,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59967,25 +59944,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59996,25 +59973,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -60027,25 +60004,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -60053,25 +60030,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -60083,25 +60060,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -60109,25 +60086,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -60142,25 +60119,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -60171,25 +60148,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="C2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -60206,25 +60183,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="C2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -60240,6 +60217,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2050" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2051" t="n">
         <v>0</v>
       </c>
@@ -60249,45 +60255,16 @@
       <c r="E2051" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2051" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2052">
       <c r="A2052" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2052" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2053" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -60315,25 +60292,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="C2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -60345,25 +60322,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="C2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -60376,25 +60353,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="C2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -60405,25 +60382,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="C2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -60431,25 +60408,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="C2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -60459,30 +60436,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2058" t="inlineStr">
+      <c r="C2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2057" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60493,30 +60470,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2059" t="inlineStr">
+      <c r="C2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2058" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60526,30 +60503,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2060" t="inlineStr">
+      <c r="C2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2059" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60562,30 +60539,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2061" t="inlineStr">
+      <c r="C2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2060" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60596,55 +60573,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2063" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2062" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60657,25 +60634,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60686,25 +60663,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60715,25 +60692,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60742,19 +60719,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60771,19 +60748,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60796,19 +60773,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60820,19 +60797,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60841,19 +60818,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60866,19 +60843,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60889,19 +60866,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60913,19 +60890,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60934,19 +60911,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60965,24 +60942,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2076" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2075" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60994,19 +60971,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -61021,19 +60998,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -61047,19 +61024,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -61070,19 +61047,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -61092,38 +61069,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -61132,19 +61109,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -61156,19 +61133,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-07-24 12:00:00</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>マチアプはあなたの恋愛市場価値を測るための試金石。
 【上位1%】
@@ -61190,25 +61167,25 @@
 俺が変われたのは、チー牛時代にマチアプで惨敗して現実を知ったから。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -61218,19 +61195,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -61244,19 +61221,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -61274,24 +61251,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2088" t="inlineStr">
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2087" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -61302,24 +61279,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2089" t="inlineStr">
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2088" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -61329,24 +61306,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2090" t="inlineStr">
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2089" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -61355,19 +61332,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -61381,19 +61358,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -61406,19 +61383,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -61431,19 +61408,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61457,19 +61434,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61490,19 +61467,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61510,19 +61487,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61530,19 +61507,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61552,19 +61529,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61573,19 +61550,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61599,25 +61576,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61631,30 +61608,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2102" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2101" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61667,25 +61644,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61700,25 +61677,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61731,25 +61708,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61759,25 +61736,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61791,25 +61768,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61832,25 +61809,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61859,25 +61836,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61892,25 +61869,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61927,25 +61904,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61956,25 +61933,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61992,25 +61969,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -62023,25 +62000,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -62052,6 +62029,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2115" t="n">
         <v>0</v>
       </c>
@@ -62071,29 +62071,6 @@
         </is>
       </c>
       <c r="B2116" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2117" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -62112,25 +62089,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="C2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -62146,25 +62123,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="C2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -62176,25 +62153,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="C2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -62204,25 +62181,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="C2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -62234,25 +62211,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="C2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -62262,25 +62239,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="C2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -62302,25 +62279,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="C2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -62334,30 +62311,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2124" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2123" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -62369,25 +62346,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -62398,25 +62375,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62452,25 +62429,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62482,25 +62459,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="C2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62516,25 +62493,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="C2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62546,25 +62523,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="C2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62593,50 +62570,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="C2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="C2131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62651,25 +62628,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="C2132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62680,25 +62657,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="C2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62716,19 +62693,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62749,19 +62726,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62773,19 +62750,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62797,19 +62774,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62820,19 +62797,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62846,19 +62823,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62870,19 +62847,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62895,19 +62872,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62923,19 +62900,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62953,19 +62930,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62979,19 +62956,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -63003,19 +62980,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -63028,19 +63005,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -63051,19 +63028,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2148" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -63072,19 +63049,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2149" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2149" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -63094,19 +63071,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2150" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2151">
-      <c r="A2151" t="inlineStr">
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2150" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -63118,19 +63095,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2151" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2152">
-      <c r="A2152" t="inlineStr">
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2152" t="inlineStr">
+      <c r="B2151" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -63145,19 +63122,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2152" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2153">
-      <c r="A2153" t="inlineStr">
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2152" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -63170,19 +63147,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2153" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2154">
-      <c r="A2154" t="inlineStr">
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2153" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -63195,19 +63172,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2154" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2155">
-      <c r="A2155" t="inlineStr">
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2154" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -63223,19 +63200,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2155" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2156">
-      <c r="A2156" t="inlineStr">
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2155" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -63252,19 +63229,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2156" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2157">
-      <c r="A2157" t="inlineStr">
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2157" t="inlineStr">
+      <c r="B2156" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -63277,19 +63254,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2157" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2158">
-      <c r="A2158" t="inlineStr">
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2157" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -63299,19 +63276,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2158" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2159">
-      <c r="A2159" t="inlineStr">
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2159" t="inlineStr">
+      <c r="B2158" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -63322,19 +63299,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2159" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2160">
-      <c r="A2160" t="inlineStr">
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2160" t="inlineStr">
+      <c r="B2159" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -63347,19 +63324,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2160" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2161">
-      <c r="A2161" t="inlineStr">
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2161" t="inlineStr">
+      <c r="B2160" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -63375,19 +63352,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2161" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2162">
-      <c r="A2162" t="inlineStr">
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2162" t="inlineStr">
+      <c r="B2161" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -63402,19 +63379,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2162" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2163">
-      <c r="A2163" t="inlineStr">
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2163" t="inlineStr">
+      <c r="B2162" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -63431,7 +63408,7 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2163" t="inlineStr">
+      <c r="E2162" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -56424,7 +56424,8 @@
 分泌されるホルモンも違う。  
 ポルノ＝ドーパミンのみ（空虚）  
 セ〇クス＝ドーパミン＋オキシトシン
-＋セロトニン（充足）</t>
+＋セロトニン（充足）  
+「女はコスパ悪い」とか抜かしてたら、一生埋まらないものを抱えながら生きる最悪な人生になるよ。</t>
         </is>
       </c>
       <c r="C1917" t="n">
@@ -56450,7 +56451,9 @@
           <t>スマホ中毒の本当の恐ろしさは、中毒がデフォルトになりすぎて誰も中毒だと気づかないところにある。
 電車、育児、歩行中、インフラ。
 あらゆる隙間にスマホが入ってきた。
-その状態で脱スマホ中毒を語ると「反テクノロジーですか？」「スピってますか？」でレッテルを貼られて終わる。</t>
+その状態で脱スマホ中毒を語ると「反テクノロジーですか？」「スピってますか？」でレッテルを貼られて終わる。
+実際に注意持続時間の低下、睡眠の質の悪化、幸福度低下等の実害は証明されており、宗教でも倫理でもない話をしているのに陰謀論者扱いされる。
+これにはディストピア的な恐怖を感じる。</t>
         </is>
       </c>
       <c r="C1918" t="n">
@@ -56481,7 +56484,8 @@
 ・「オナ禁してテストステロン爆上げ」 
 →筋トレもしろ  
 ・「自分を磨けば女性から来てくれる」
- →受け身が許されるのはTOP1％のみ</t>
+ →受け身が許されるのはTOP1％のみ  
+すべて俺が通ってきた道。</t>
         </is>
       </c>
       <c r="C1919" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2162"/>
+  <dimension ref="A1:G2160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56530,33 +56530,10 @@
     <row r="1921">
       <c r="A1921" t="inlineStr">
         <is>
-          <t>2026-06-06 09:38:45</t>
+          <t>2026-06-06 11:01:00</t>
         </is>
       </c>
       <c r="B1921" t="inlineStr">
-        <is>
-          <t>ナイスです👍 https://t.co/w9tiD0Ejoe</t>
-        </is>
-      </c>
-      <c r="C1921" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1921" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1921" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1922">
-      <c r="A1922" t="inlineStr">
-        <is>
-          <t>2026-06-06 11:01:00</t>
-        </is>
-      </c>
-      <c r="B1922" t="inlineStr">
         <is>
           <t>スマホを減らしたら手に入ったもの 
 ・時間 
@@ -56569,49 +56546,25 @@
 失ったものは何もない。</t>
         </is>
       </c>
-      <c r="C1922" t="n">
+      <c r="C1921" t="n">
         <v>32</v>
       </c>
-      <c r="D1922" t="n">
+      <c r="D1921" t="n">
         <v>3</v>
       </c>
-      <c r="E1922" t="inlineStr">
+      <c r="E1921" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1923">
-      <c r="A1923" t="inlineStr">
-        <is>
-          <t>2026-06-06 11:26:28</t>
-        </is>
-      </c>
-      <c r="B1923" t="inlineStr">
-        <is>
-          <t>スマホ中毒をやめる方法9選 | byスマホ中毒で高校中退した廃人
-https://t.co/IJPAZYRO6b</t>
-        </is>
-      </c>
-      <c r="C1923" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1923" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1923" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1924">
-      <c r="A1924" t="inlineStr">
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
         <is>
           <t>2026-06-06 22:10:00</t>
         </is>
       </c>
-      <c r="B1924" t="inlineStr">
+      <c r="B1922" t="inlineStr">
         <is>
           <t>朝に勝つ奴が1日に勝つ 
 ・5時台に起きる 
@@ -56626,25 +56579,25 @@
 俺は朝を変えて人生変わった。</t>
         </is>
       </c>
-      <c r="C1924" t="n">
+      <c r="C1922" t="n">
         <v>75</v>
       </c>
-      <c r="D1924" t="n">
+      <c r="D1922" t="n">
         <v>7</v>
       </c>
-      <c r="E1924" t="inlineStr">
+      <c r="E1922" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1925">
-      <c r="A1925" t="inlineStr">
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
         <is>
           <t>2026-06-07 05:16:39</t>
         </is>
       </c>
-      <c r="B1925" t="inlineStr">
+      <c r="B1923" t="inlineStr">
         <is>
           <t>継続のコツは頑張らないこと 
 ・100点→3日で挫折 
@@ -56652,25 +56605,25 @@
 続けることが全て。</t>
         </is>
       </c>
-      <c r="C1925" t="n">
+      <c r="C1923" t="n">
         <v>27</v>
       </c>
-      <c r="D1925" t="n">
+      <c r="D1923" t="n">
         <v>1</v>
       </c>
-      <c r="E1925" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1926">
-      <c r="A1926" t="inlineStr">
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
         <is>
           <t>2026-06-07 08:09:56</t>
         </is>
       </c>
-      <c r="B1926" t="inlineStr">
+      <c r="B1924" t="inlineStr">
         <is>
           <t>やる気が落ちた時の儀式を持っておくといい。
 俺は最近、作業で疲れたらヤドーム（タイのお土産）を吸引することにしています。
@@ -56680,25 +56633,25 @@
 もいいかもです。 https://t.co/DDk9fQcuka https://t.co/JVZTWTYvgs</t>
         </is>
       </c>
-      <c r="C1926" t="n">
+      <c r="C1924" t="n">
         <v>18</v>
       </c>
-      <c r="D1926" t="n">
+      <c r="D1924" t="n">
         <v>1</v>
       </c>
-      <c r="E1926" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1927">
-      <c r="A1927" t="inlineStr">
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
         <is>
           <t>2026-06-07 08:18:38</t>
         </is>
       </c>
-      <c r="B1927" t="inlineStr">
+      <c r="B1925" t="inlineStr">
         <is>
           <t>モテることが簡単になった理由。
 ・インターネットポルノの普及
@@ -56710,50 +56663,50 @@
 私の発信を長く見ている人は有利。</t>
         </is>
       </c>
-      <c r="C1927" t="n">
+      <c r="C1925" t="n">
         <v>84</v>
       </c>
-      <c r="D1927" t="n">
+      <c r="D1925" t="n">
         <v>9</v>
       </c>
-      <c r="E1927" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1928">
-      <c r="A1928" t="inlineStr">
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
         <is>
           <t>2026-06-07 08:22:53</t>
         </is>
       </c>
-      <c r="B1928" t="inlineStr">
+      <c r="B1926" t="inlineStr">
         <is>
           <t>「筋トレしてない男はゲイ」「童貞は生物として終わり」くらいの雰囲気があった方が社会にとって良いと思う。
 多様性を謳う系のリベラルは害悪。
 でも、これに洗脳されている男が多いから、俺らだけが良い思いできるんだけどね。 https://t.co/Y7rLnPvKEM</t>
         </is>
       </c>
-      <c r="C1928" t="n">
+      <c r="C1926" t="n">
         <v>45</v>
       </c>
-      <c r="D1928" t="n">
+      <c r="D1926" t="n">
         <v>1</v>
       </c>
-      <c r="E1928" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1929">
-      <c r="A1929" t="inlineStr">
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
         <is>
           <t>2026-06-07 09:06:12</t>
         </is>
       </c>
-      <c r="B1929" t="inlineStr">
+      <c r="B1927" t="inlineStr">
         <is>
           <t>毎日、行動してくださる方が現れてとても嬉しいです。
 数年前まで私は「クラスで一言も喋らない自閉症のチー牛」でした。
@@ -56761,25 +56714,25 @@
 これを見たあなたは今後人生で女や金、憂鬱な人生に困ることはないです。… https://t.co/16wOk9Tj8f</t>
         </is>
       </c>
-      <c r="C1929" t="n">
+      <c r="C1927" t="n">
         <v>4</v>
       </c>
-      <c r="D1929" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1929" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1930">
-      <c r="A1930" t="inlineStr">
+      <c r="D1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
         <is>
           <t>2026-06-07 09:20:00</t>
         </is>
       </c>
-      <c r="B1930" t="inlineStr">
+      <c r="B1928" t="inlineStr">
         <is>
           <t>あなたが時間貧乏である理由 
 ①汚部屋 
@@ -56794,25 +56747,25 @@
 要領がいい人は、これの逆を行きます。</t>
         </is>
       </c>
-      <c r="C1930" t="n">
+      <c r="C1928" t="n">
         <v>123</v>
       </c>
-      <c r="D1930" t="n">
+      <c r="D1928" t="n">
         <v>14</v>
       </c>
-      <c r="E1930" t="inlineStr">
+      <c r="E1928" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1931">
-      <c r="A1931" t="inlineStr">
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
         <is>
           <t>2026-06-07 09:41:00</t>
         </is>
       </c>
-      <c r="B1931" t="inlineStr">
+      <c r="B1929" t="inlineStr">
         <is>
           <t>清潔感を出すためにやること 
 ・眉毛を整える 
@@ -56825,48 +56778,48 @@
 やって当たり前のこと。</t>
         </is>
       </c>
-      <c r="C1931" t="n">
+      <c r="C1929" t="n">
         <v>49</v>
       </c>
-      <c r="D1931" t="n">
+      <c r="D1929" t="n">
         <v>4</v>
       </c>
-      <c r="E1931" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1932">
-      <c r="A1932" t="inlineStr">
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
         <is>
           <t>2026-06-07 09:47:57</t>
         </is>
       </c>
-      <c r="B1932" t="inlineStr">
+      <c r="B1930" t="inlineStr">
         <is>
           <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
-      <c r="C1932" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1932" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1932" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1933">
-      <c r="A1933" t="inlineStr">
+      <c r="C1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
         <is>
           <t>2026-06-07 10:45:00</t>
         </is>
       </c>
-      <c r="B1933" t="inlineStr">
+      <c r="B1931" t="inlineStr">
         <is>
           <t>大学デビュー失敗した陰キャたちへ 
 結論、挽回は無理。 
@@ -56881,25 +56834,25 @@
 種まきの期間だと思え。</t>
         </is>
       </c>
-      <c r="C1933" t="n">
+      <c r="C1931" t="n">
         <v>165</v>
       </c>
-      <c r="D1933" t="n">
+      <c r="D1931" t="n">
         <v>9</v>
       </c>
-      <c r="E1933" t="inlineStr">
+      <c r="E1931" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
     </row>
-    <row r="1934">
-      <c r="A1934" t="inlineStr">
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
         <is>
           <t>2026-06-07 10:57:46</t>
         </is>
       </c>
-      <c r="B1934" t="inlineStr">
+      <c r="B1932" t="inlineStr">
         <is>
           <t>私はスポーツ観戦大好きで、ニート時代は深夜にプレミアリーグ見まくっていたサカ豚。
 でも、間違いなく人の応援をしている場合じゃなかった。
@@ -56907,48 +56860,48 @@
 スポーツ観戦はすでにやることを終えた上級国民の娯楽。 https://t.co/0yTrug56kv</t>
         </is>
       </c>
-      <c r="C1934" t="n">
+      <c r="C1932" t="n">
         <v>23</v>
       </c>
-      <c r="D1934" t="n">
+      <c r="D1932" t="n">
         <v>2</v>
       </c>
-      <c r="E1934" t="inlineStr">
+      <c r="E1932" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1935">
-      <c r="A1935" t="inlineStr">
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
         <is>
           <t>2026-06-07 11:20:26</t>
         </is>
       </c>
-      <c r="B1935" t="inlineStr">
+      <c r="B1933" t="inlineStr">
         <is>
           <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
-      <c r="C1935" t="n">
+      <c r="C1933" t="n">
         <v>1</v>
       </c>
-      <c r="D1935" t="n">
+      <c r="D1933" t="n">
         <v>1</v>
       </c>
-      <c r="E1935" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1936">
-      <c r="A1936" t="inlineStr">
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
         <is>
           <t>2026-06-07 11:47:00</t>
         </is>
       </c>
-      <c r="B1936" t="inlineStr">
+      <c r="B1934" t="inlineStr">
         <is>
           <t>早起きできない奴の特徴 
 ・寝る時間が遅い 
@@ -56964,25 +56917,25 @@
 ・8~9時間確保する</t>
         </is>
       </c>
-      <c r="C1936" t="n">
+      <c r="C1934" t="n">
         <v>44</v>
       </c>
-      <c r="D1936" t="n">
+      <c r="D1934" t="n">
         <v>6</v>
       </c>
-      <c r="E1936" t="inlineStr">
+      <c r="E1934" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1937">
-      <c r="A1937" t="inlineStr">
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
         <is>
           <t>2026-06-07 21:59:00</t>
         </is>
       </c>
-      <c r="B1937" t="inlineStr">
+      <c r="B1935" t="inlineStr">
         <is>
           <t>朝コーヒーがあなたにもたらすもの 
 ・集中力の爆上がり 
@@ -56996,48 +56949,48 @@
 俺はブラックコーヒー飲んで爆速でポストを量産している。</t>
         </is>
       </c>
-      <c r="C1937" t="n">
+      <c r="C1935" t="n">
         <v>52</v>
       </c>
-      <c r="D1937" t="n">
+      <c r="D1935" t="n">
         <v>4</v>
       </c>
-      <c r="E1937" t="inlineStr">
+      <c r="E1935" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1938">
-      <c r="A1938" t="inlineStr">
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
         <is>
           <t>2026-06-08 02:45:52</t>
         </is>
       </c>
-      <c r="B1938" t="inlineStr">
+      <c r="B1936" t="inlineStr">
         <is>
           <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
         </is>
       </c>
-      <c r="C1938" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1938" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1938" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1939">
-      <c r="A1939" t="inlineStr">
+      <c r="C1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
         <is>
           <t>2026-06-08 03:03:37</t>
         </is>
       </c>
-      <c r="B1939" t="inlineStr">
+      <c r="B1937" t="inlineStr">
         <is>
           <t>地味にQOLを上げる方法
 ・歯ブラシ
@@ -57048,25 +57001,25 @@
 いつも使う物に少し金払うだけで、QOLは上がる。</t>
         </is>
       </c>
-      <c r="C1939" t="n">
+      <c r="C1937" t="n">
         <v>66</v>
       </c>
-      <c r="D1939" t="n">
+      <c r="D1937" t="n">
         <v>5</v>
       </c>
-      <c r="E1939" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1940">
-      <c r="A1940" t="inlineStr">
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
         <is>
           <t>2026-06-08 07:49:00</t>
         </is>
       </c>
-      <c r="B1940" t="inlineStr">
+      <c r="B1938" t="inlineStr">
         <is>
           <t>睡眠不足で筋トレしても意味ない 
 ・筋肉は寝てる間に成長する 
@@ -57076,25 +57029,25 @@
 まずは寝ろ。</t>
         </is>
       </c>
-      <c r="C1940" t="n">
+      <c r="C1938" t="n">
         <v>33</v>
       </c>
-      <c r="D1940" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1940" t="inlineStr">
+      <c r="D1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1938" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1941">
-      <c r="A1941" t="inlineStr">
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
         <is>
           <t>2026-06-08 08:43:00</t>
         </is>
       </c>
-      <c r="B1941" t="inlineStr">
+      <c r="B1939" t="inlineStr">
         <is>
           <t>”極振り”が人生を変える。
 女攻略したいなら
@@ -57106,25 +57059,25 @@
 俺はこの極振りでコンプを克服してきた。</t>
         </is>
       </c>
-      <c r="C1941" t="n">
+      <c r="C1939" t="n">
         <v>113</v>
       </c>
-      <c r="D1941" t="n">
+      <c r="D1939" t="n">
         <v>10</v>
       </c>
-      <c r="E1941" t="inlineStr">
+      <c r="E1939" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1942">
-      <c r="A1942" t="inlineStr">
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
         <is>
           <t>2026-06-08 09:14:00</t>
         </is>
       </c>
-      <c r="B1942" t="inlineStr">
+      <c r="B1940" t="inlineStr">
         <is>
           <t>童貞は
 ・身長10cm盛る
@@ -57135,25 +57088,25 @@
 「俺のち〇こを必要としている人はいる」という自信にはなる。</t>
         </is>
       </c>
-      <c r="C1942" t="n">
+      <c r="C1940" t="n">
         <v>158</v>
       </c>
-      <c r="D1942" t="n">
+      <c r="D1940" t="n">
         <v>6</v>
       </c>
-      <c r="E1942" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1943">
-      <c r="A1943" t="inlineStr">
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
         <is>
           <t>2026-06-08 10:00:01</t>
         </is>
       </c>
-      <c r="B1943" t="inlineStr">
+      <c r="B1941" t="inlineStr">
         <is>
           <t>「チー牛家庭」の問題点。
 ・食事から教育方針まで、すべて母親が決める 
@@ -57164,25 +57117,25 @@
 はしごを外され、決断力を育ててこなかった</t>
         </is>
       </c>
-      <c r="C1943" t="n">
+      <c r="C1941" t="n">
         <v>32</v>
       </c>
-      <c r="D1943" t="n">
+      <c r="D1941" t="n">
         <v>1</v>
       </c>
-      <c r="E1943" t="inlineStr">
+      <c r="E1941" t="inlineStr">
         <is>
           <t>exam</t>
         </is>
       </c>
     </row>
-    <row r="1944">
-      <c r="A1944" t="inlineStr">
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
         <is>
           <t>2026-06-08 10:41:00</t>
         </is>
       </c>
-      <c r="B1944" t="inlineStr">
+      <c r="B1942" t="inlineStr">
         <is>
           <t>正直、学生時代に”イジメすらもされないような陰キャ”だった方がSNSやマチアプで人気者になるのは厳しい。 
 これらはあくまで拡声器。 
@@ -57190,25 +57143,25 @@
 やることは自己啓発陰キャになり、自分本体をひたすら磨くこと。</t>
         </is>
       </c>
-      <c r="C1944" t="n">
+      <c r="C1942" t="n">
         <v>53</v>
       </c>
-      <c r="D1944" t="n">
+      <c r="D1942" t="n">
         <v>4</v>
       </c>
-      <c r="E1944" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1945">
-      <c r="A1945" t="inlineStr">
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
         <is>
           <t>2026-06-08 11:09:00</t>
         </is>
       </c>
-      <c r="B1945" t="inlineStr">
+      <c r="B1943" t="inlineStr">
         <is>
           <t>スマホ中毒がデフォルトの時代。 
 そこを脱して「静寂」を手に入れた人間は、
@@ -57216,48 +57169,48 @@
 周りが耽溺している間に、あなたは淡々とリアルな成果を積み上げる側へ回れ。</t>
         </is>
       </c>
-      <c r="C1945" t="n">
+      <c r="C1943" t="n">
         <v>46</v>
       </c>
-      <c r="D1945" t="n">
+      <c r="D1943" t="n">
         <v>1</v>
       </c>
-      <c r="E1945" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1946">
-      <c r="A1946" t="inlineStr">
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
         <is>
           <t>2026-06-08 11:14:05</t>
         </is>
       </c>
-      <c r="B1946" t="inlineStr">
+      <c r="B1944" t="inlineStr">
         <is>
           <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
-      <c r="C1946" t="n">
+      <c r="C1944" t="n">
         <v>2</v>
       </c>
-      <c r="D1946" t="n">
+      <c r="D1944" t="n">
         <v>1</v>
       </c>
-      <c r="E1946" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1947">
-      <c r="A1947" t="inlineStr">
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
         <is>
           <t>2026-06-08 12:00:01</t>
         </is>
       </c>
-      <c r="B1947" t="inlineStr">
+      <c r="B1945" t="inlineStr">
         <is>
           <t>睡眠を削ると時間が減る。
 判断力低下
@@ -57270,25 +57223,25 @@
 睡眠を削るのは「ここぞ」という時だけでいい。</t>
         </is>
       </c>
-      <c r="C1947" t="n">
+      <c r="C1945" t="n">
         <v>29</v>
       </c>
-      <c r="D1947" t="n">
+      <c r="D1945" t="n">
         <v>1</v>
       </c>
-      <c r="E1947" t="inlineStr">
+      <c r="E1945" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1948">
-      <c r="A1948" t="inlineStr">
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
         <is>
           <t>2026-06-09 07:28:00</t>
         </is>
       </c>
-      <c r="B1948" t="inlineStr">
+      <c r="B1946" t="inlineStr">
         <is>
           <t>モテる男は周りから固めていく。
 まず本命の友達から評価を得てクチコミを広める。
@@ -57296,25 +57249,25 @@
 逆に非モテはガンギマリで女にピンポイントで、くそきもアプローチだけする。</t>
         </is>
       </c>
-      <c r="C1948" t="n">
+      <c r="C1946" t="n">
         <v>23</v>
       </c>
-      <c r="D1948" t="n">
+      <c r="D1946" t="n">
         <v>2</v>
       </c>
-      <c r="E1948" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1949">
-      <c r="A1949" t="inlineStr">
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
         <is>
           <t>2026-06-09 08:06:00</t>
         </is>
       </c>
-      <c r="B1949" t="inlineStr">
+      <c r="B1947" t="inlineStr">
         <is>
           <t>3日坊主の奴はSNSを見すぎ。
 他人の投稿ばかり見て、隣の芝生が青く見えるがゆえ、やることがブレている。
@@ -57323,25 +57276,25 @@
 フォローは厳選している。</t>
         </is>
       </c>
-      <c r="C1949" t="n">
+      <c r="C1947" t="n">
         <v>22</v>
       </c>
-      <c r="D1949" t="n">
+      <c r="D1947" t="n">
         <v>1</v>
       </c>
-      <c r="E1949" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1950">
-      <c r="A1950" t="inlineStr">
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
         <is>
           <t>2026-06-09 08:50:00</t>
         </is>
       </c>
-      <c r="B1950" t="inlineStr">
+      <c r="B1948" t="inlineStr">
         <is>
           <t>テストステロンを1日で取り戻す方法 
 ・8時間睡眠 
@@ -57357,25 +57310,25 @@
 翌日には余裕で回復してる。</t>
         </is>
       </c>
-      <c r="C1950" t="n">
+      <c r="C1948" t="n">
         <v>953</v>
       </c>
-      <c r="D1950" t="n">
+      <c r="D1948" t="n">
         <v>66</v>
       </c>
-      <c r="E1950" t="inlineStr">
+      <c r="E1948" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1951">
-      <c r="A1951" t="inlineStr">
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
         <is>
           <t>2026-06-09 09:30:00</t>
         </is>
       </c>
-      <c r="B1951" t="inlineStr">
+      <c r="B1949" t="inlineStr">
         <is>
           <t>・「ヒョロガリがフリーウェイト使うのは申し訳ない。」 
 ・「インターバル3分も取るのは気まずい。」 
@@ -57385,8 +57338,54 @@
 そして、あなたも他の会員と同じ額の会費を払ってます。</t>
         </is>
       </c>
+      <c r="C1949" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:43:01</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
+        </is>
+      </c>
+      <c r="C1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:43:52</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1951" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D1951" t="n">
         <v>0</v>
@@ -57400,56 +57399,10 @@
     <row r="1952">
       <c r="A1952" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:01</t>
+          <t>2026-06-09 10:06:00</t>
         </is>
       </c>
       <c r="B1952" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
-        </is>
-      </c>
-      <c r="C1952" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1952" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1952" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1953">
-      <c r="A1953" t="inlineStr">
-        <is>
-          <t>2026-06-09 09:43:52</t>
-        </is>
-      </c>
-      <c r="B1953" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1953" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1953" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1953" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1954">
-      <c r="A1954" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:06:00</t>
-        </is>
-      </c>
-      <c r="B1954" t="inlineStr">
         <is>
           <t>受け身な男の脳内  
 小学生時代 
@@ -57464,50 +57417,50 @@
 「出世出来たら結婚出来るんだろうなぁ」</t>
         </is>
       </c>
-      <c r="C1954" t="n">
+      <c r="C1952" t="n">
         <v>84</v>
       </c>
-      <c r="D1954" t="n">
+      <c r="D1952" t="n">
         <v>6</v>
       </c>
-      <c r="E1954" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1955">
-      <c r="A1955" t="inlineStr">
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
         <is>
           <t>2026-06-09 10:12:00</t>
         </is>
       </c>
-      <c r="B1955" t="inlineStr">
+      <c r="B1953" t="inlineStr">
         <is>
           <t>スマホ中毒者は自分だけの「対策ノウハウ」を作っていけ。
 確かにタイムロック、瞑想等は効果はあるが単なるテクニック論に過ぎない。
 自分の癖を見つけて、ピンポイントで対策する方が効果的。</t>
         </is>
       </c>
-      <c r="C1955" t="n">
+      <c r="C1953" t="n">
         <v>19</v>
       </c>
-      <c r="D1955" t="n">
+      <c r="D1953" t="n">
         <v>2</v>
       </c>
-      <c r="E1955" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1956">
-      <c r="A1956" t="inlineStr">
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
         <is>
           <t>2026-06-09 10:48:00</t>
         </is>
       </c>
-      <c r="B1956" t="inlineStr">
+      <c r="B1954" t="inlineStr">
         <is>
           <t>非モテのコミュニケーション悪癖 
 ・名前を呼べない 
@@ -57522,25 +57475,25 @@
 2つ以上当てはまれば、キモがれらている可能性大。</t>
         </is>
       </c>
-      <c r="C1956" t="n">
+      <c r="C1954" t="n">
         <v>54</v>
       </c>
-      <c r="D1956" t="n">
+      <c r="D1954" t="n">
         <v>6</v>
       </c>
-      <c r="E1956" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1957">
-      <c r="A1957" t="inlineStr">
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
         <is>
           <t>2026-06-09 11:20:00</t>
         </is>
       </c>
-      <c r="B1957" t="inlineStr">
+      <c r="B1955" t="inlineStr">
         <is>
           <t>モテテクは結果論。 
 ・返信を遅らせる 
@@ -57550,49 +57503,49 @@
 確かに非モテのモテテク武装は大事。 だから無意味ではないが、 結果論であることを理解した上で使った方がいい。</t>
         </is>
       </c>
-      <c r="C1957" t="n">
+      <c r="C1955" t="n">
         <v>20</v>
       </c>
-      <c r="D1957" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1957" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1958">
-      <c r="A1958" t="inlineStr">
+      <c r="D1955" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
         <is>
           <t>2026-06-09 11:30:00</t>
         </is>
       </c>
-      <c r="B1958" t="inlineStr">
+      <c r="B1956" t="inlineStr">
         <is>
           <t>筋トレをやらない理由はない。 
 毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
         </is>
       </c>
-      <c r="C1958" t="n">
+      <c r="C1956" t="n">
         <v>22</v>
       </c>
-      <c r="D1958" t="n">
+      <c r="D1956" t="n">
         <v>1</v>
       </c>
-      <c r="E1958" t="inlineStr">
+      <c r="E1956" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1959">
-      <c r="A1959" t="inlineStr">
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
         <is>
           <t>2026-06-10 07:40:00</t>
         </is>
       </c>
-      <c r="B1959" t="inlineStr">
+      <c r="B1957" t="inlineStr">
         <is>
           <t>スマホが近くにあるだけで頭が悪くなる。
 脳が「スマホを無視しろ」とコマンドを送るのにリソースを割くからです。
@@ -57601,25 +57554,25 @@
 物理的な距離だけがあなたの脳を解放します。</t>
         </is>
       </c>
-      <c r="C1959" t="n">
+      <c r="C1957" t="n">
         <v>15</v>
       </c>
-      <c r="D1959" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1959" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1960">
-      <c r="A1960" t="inlineStr">
+      <c r="D1957" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
         <is>
           <t>2026-06-10 08:23:00</t>
         </is>
       </c>
-      <c r="B1960" t="inlineStr">
+      <c r="B1958" t="inlineStr">
         <is>
           <t>一番、結果が出るのはコンフォートゾーンでガチガチにハメ技決めてる時。
 ・毎日、同じ食事を摂る
@@ -57629,25 +57582,25 @@
 「つまらない」と感じると思うが、いちいち新しいことを始める必要はない。君の努力は正しい。</t>
         </is>
       </c>
-      <c r="C1960" t="n">
+      <c r="C1958" t="n">
         <v>45</v>
       </c>
-      <c r="D1960" t="n">
+      <c r="D1958" t="n">
         <v>5</v>
       </c>
-      <c r="E1960" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1961">
-      <c r="A1961" t="inlineStr">
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
         <is>
           <t>2026-06-10 08:42:00</t>
         </is>
       </c>
-      <c r="B1961" t="inlineStr">
+      <c r="B1959" t="inlineStr">
         <is>
           <t>ストイックには2種類ある。  
 ・サボらない努力マシーン 
@@ -57657,25 +57610,25 @@
 そして、翌日には何事もなかったようにルーティンに戻る。</t>
         </is>
       </c>
-      <c r="C1961" t="n">
+      <c r="C1959" t="n">
         <v>31</v>
       </c>
-      <c r="D1961" t="n">
+      <c r="D1959" t="n">
         <v>5</v>
       </c>
-      <c r="E1961" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1962">
-      <c r="A1962" t="inlineStr">
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
         <is>
           <t>2026-06-10 09:20:00</t>
         </is>
       </c>
-      <c r="B1962" t="inlineStr">
+      <c r="B1960" t="inlineStr">
         <is>
           <t>筋トレで得たもの 
 ・自信 
@@ -57690,25 +57643,25 @@
 やらない理由がない。</t>
         </is>
       </c>
-      <c r="C1962" t="n">
+      <c r="C1960" t="n">
         <v>59</v>
       </c>
-      <c r="D1962" t="n">
+      <c r="D1960" t="n">
         <v>4</v>
       </c>
-      <c r="E1962" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1963">
-      <c r="A1963" t="inlineStr">
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
         <is>
           <t>2026-06-10 09:36:00</t>
         </is>
       </c>
-      <c r="B1963" t="inlineStr">
+      <c r="B1961" t="inlineStr">
         <is>
           <t>ヒョロガリのマインド
 「ハイTな食事🤓（2300kcal）」
@@ -57720,25 +57673,25 @@
 黙って食え。</t>
         </is>
       </c>
-      <c r="C1963" t="n">
+      <c r="C1961" t="n">
         <v>47</v>
       </c>
-      <c r="D1963" t="n">
+      <c r="D1961" t="n">
         <v>1</v>
       </c>
-      <c r="E1963" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1964">
-      <c r="A1964" t="inlineStr">
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
         <is>
           <t>2026-06-10 10:00:00</t>
         </is>
       </c>
-      <c r="B1964" t="inlineStr">
+      <c r="B1962" t="inlineStr">
         <is>
           <t>自信がない奴の特徴 
 ・姿勢が悪い 
@@ -57755,25 +57708,25 @@
 俺は筋トレで体を変えてから自信がついた。</t>
         </is>
       </c>
-      <c r="C1964" t="n">
+      <c r="C1962" t="n">
         <v>58</v>
       </c>
-      <c r="D1964" t="n">
+      <c r="D1962" t="n">
         <v>5</v>
       </c>
-      <c r="E1964" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1965">
-      <c r="A1965" t="inlineStr">
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
         <is>
           <t>2026-06-10 10:45:00</t>
         </is>
       </c>
-      <c r="B1965" t="inlineStr">
+      <c r="B1963" t="inlineStr">
         <is>
           <t>スマホ中毒の唯一の基準は
 「目標達成を妨げているか否か」。
@@ -57784,48 +57737,48 @@
 スクリーンタイムよりも使い方を見直せ。</t>
         </is>
       </c>
-      <c r="C1965" t="n">
+      <c r="C1963" t="n">
         <v>25</v>
       </c>
-      <c r="D1965" t="n">
+      <c r="D1963" t="n">
         <v>4</v>
       </c>
-      <c r="E1965" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1966">
-      <c r="A1966" t="inlineStr">
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
         <is>
           <t>2026-06-10 10:49:46</t>
         </is>
       </c>
-      <c r="B1966" t="inlineStr">
+      <c r="B1964" t="inlineStr">
         <is>
           <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
         </is>
       </c>
-      <c r="C1966" t="n">
+      <c r="C1964" t="n">
         <v>1</v>
       </c>
-      <c r="D1966" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1966" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1967">
-      <c r="A1967" t="inlineStr">
+      <c r="D1964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
         <is>
           <t>2026-06-10 11:00:03</t>
         </is>
       </c>
-      <c r="B1967" t="inlineStr">
+      <c r="B1965" t="inlineStr">
         <is>
           <t>男磨きしている人が陥りがちな失敗は「禁欲の目的化」。
 確かにオナ禁、コールドシャワー、瞑想といった習慣はスピではなく、科学的根拠がある。
@@ -57833,25 +57786,25 @@
 あくまで廃人が自己管理能力を上げる手段でしかない。</t>
         </is>
       </c>
-      <c r="C1967" t="n">
+      <c r="C1965" t="n">
         <v>46</v>
       </c>
-      <c r="D1967" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1967" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1968">
-      <c r="A1968" t="inlineStr">
+      <c r="D1965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
         <is>
           <t>2026-06-10 11:29:00</t>
         </is>
       </c>
-      <c r="B1968" t="inlineStr">
+      <c r="B1966" t="inlineStr">
         <is>
           <t>一般的な弱者男性の日常。
 平日は経営者のために働き、上司と得意先に頭を下げる。帰宅後は推しの配信で時間を潰す。 
@@ -57861,25 +57814,25 @@
 哲学的ゾンビとはこのこと。</t>
         </is>
       </c>
-      <c r="C1968" t="n">
+      <c r="C1966" t="n">
         <v>44</v>
       </c>
-      <c r="D1968" t="n">
+      <c r="D1966" t="n">
         <v>6</v>
       </c>
-      <c r="E1968" t="inlineStr">
+      <c r="E1966" t="inlineStr">
         <is>
           <t>sunday</t>
         </is>
       </c>
     </row>
-    <row r="1969">
-      <c r="A1969" t="inlineStr">
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
         <is>
           <t>2026-06-10 12:06:00</t>
         </is>
       </c>
-      <c r="B1969" t="inlineStr">
+      <c r="B1967" t="inlineStr">
         <is>
           <t>睡眠を30分削ると、 
 ・テストステロン低下 
@@ -57892,25 +57845,25 @@
 そして、翌朝はアラーム無しで起きる奴こそが強者。</t>
         </is>
       </c>
-      <c r="C1969" t="n">
+      <c r="C1967" t="n">
         <v>27</v>
       </c>
-      <c r="D1969" t="n">
+      <c r="D1967" t="n">
         <v>4</v>
       </c>
-      <c r="E1969" t="inlineStr">
+      <c r="E1967" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1970">
-      <c r="A1970" t="inlineStr">
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
         <is>
           <t>2026-06-11 06:18:00</t>
         </is>
       </c>
-      <c r="B1970" t="inlineStr">
+      <c r="B1968" t="inlineStr">
         <is>
           <t>弱者男性の先天的欠点
 ・短足
@@ -57926,25 +57879,25 @@
 複数当てはまると、結構人生ハードモード。</t>
         </is>
       </c>
-      <c r="C1970" t="n">
+      <c r="C1968" t="n">
         <v>38</v>
       </c>
-      <c r="D1970" t="n">
+      <c r="D1968" t="n">
         <v>2</v>
       </c>
-      <c r="E1970" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1971">
-      <c r="A1971" t="inlineStr">
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
         <is>
           <t>2026-06-11 06:29:00</t>
         </is>
       </c>
-      <c r="B1971" t="inlineStr">
+      <c r="B1969" t="inlineStr">
         <is>
           <t>ヒョロガリは週3回、BIG3をそれぞれやるだけで十分全身を鍛えられる。
 5分割で2時間は多分、続かない。
@@ -57952,25 +57905,25 @@
 週3は忙しくても行ける。</t>
         </is>
       </c>
-      <c r="C1971" t="n">
+      <c r="C1969" t="n">
         <v>36</v>
       </c>
-      <c r="D1971" t="n">
+      <c r="D1969" t="n">
         <v>1</v>
       </c>
-      <c r="E1971" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1972">
-      <c r="A1972" t="inlineStr">
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
         <is>
           <t>2026-06-11 08:44:00</t>
         </is>
       </c>
-      <c r="B1972" t="inlineStr">
+      <c r="B1970" t="inlineStr">
         <is>
           <t>俺が童貞(20歳)に戻ったらやること 
 ・ ジム入会 
@@ -57984,11 +57937,57 @@
 ・ブスでもBBAでも片っ端からアプローチ</t>
         </is>
       </c>
+      <c r="C1970" t="n">
+        <v>261</v>
+      </c>
+      <c r="D1970" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:11:09</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:12:47</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
+        </is>
+      </c>
       <c r="C1972" t="n">
-        <v>261</v>
+        <v>1</v>
       </c>
       <c r="D1972" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E1972" t="inlineStr">
         <is>
@@ -57999,56 +57998,10 @@
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>2026-06-11 09:11:09</t>
+          <t>2026-06-11 09:13:00</t>
         </is>
       </c>
       <c r="B1973" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1973" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1973" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1973" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1974">
-      <c r="A1974" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:12:47</t>
-        </is>
-      </c>
-      <c r="B1974" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
-        </is>
-      </c>
-      <c r="C1974" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1974" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1974" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1975">
-      <c r="A1975" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:13:00</t>
-        </is>
-      </c>
-      <c r="B1975" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。 環境を変える努力をしろ。 
@@ -58062,48 +58015,48 @@
 ・やるか死ぬかの状況</t>
         </is>
       </c>
-      <c r="C1975" t="n">
+      <c r="C1973" t="n">
         <v>54</v>
       </c>
-      <c r="D1975" t="n">
+      <c r="D1973" t="n">
         <v>8</v>
       </c>
-      <c r="E1975" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1976">
-      <c r="A1976" t="inlineStr">
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
         <is>
           <t>2026-06-11 09:15:26</t>
         </is>
       </c>
-      <c r="B1976" t="inlineStr">
+      <c r="B1974" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1976" t="n">
+      <c r="C1974" t="n">
         <v>2</v>
       </c>
-      <c r="D1976" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1976" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1977">
-      <c r="A1977" t="inlineStr">
+      <c r="D1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
         <is>
           <t>2026-06-11 09:45:00</t>
         </is>
       </c>
-      <c r="B1977" t="inlineStr">
+      <c r="B1975" t="inlineStr">
         <is>
           <t>あなたがチー牛顔である理由 
 ・一重 
@@ -58117,48 +58070,48 @@
 ・体脂肪率20%以上</t>
         </is>
       </c>
-      <c r="C1977" t="n">
+      <c r="C1975" t="n">
         <v>280</v>
       </c>
-      <c r="D1977" t="n">
+      <c r="D1975" t="n">
         <v>17</v>
       </c>
-      <c r="E1977" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1978">
-      <c r="A1978" t="inlineStr">
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
         <is>
           <t>2026-06-11 09:48:30</t>
         </is>
       </c>
-      <c r="B1978" t="inlineStr">
+      <c r="B1976" t="inlineStr">
         <is>
           <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
         </is>
       </c>
-      <c r="C1978" t="n">
+      <c r="C1976" t="n">
         <v>16</v>
       </c>
-      <c r="D1978" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1978" t="inlineStr">
+      <c r="D1976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1976" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1979">
-      <c r="A1979" t="inlineStr">
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
         <is>
           <t>2026-06-11 10:10:00</t>
         </is>
       </c>
-      <c r="B1979" t="inlineStr">
+      <c r="B1977" t="inlineStr">
         <is>
           <t>孤独でもメンタルを安定させる方法 
 男磨きは孤独との戦いになるので実践してほしい。
@@ -58172,25 +58125,25 @@
 むしろ人生はいい方向に進む。</t>
         </is>
       </c>
-      <c r="C1979" t="n">
+      <c r="C1977" t="n">
         <v>81</v>
       </c>
-      <c r="D1979" t="n">
+      <c r="D1977" t="n">
         <v>7</v>
       </c>
-      <c r="E1979" t="inlineStr">
+      <c r="E1977" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1980">
-      <c r="A1980" t="inlineStr">
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
         <is>
           <t>2026-06-11 10:37:00</t>
         </is>
       </c>
-      <c r="B1980" t="inlineStr">
+      <c r="B1978" t="inlineStr">
         <is>
           <t>スマホ断ちがあなたに与えるもの 
 ・思考力 
@@ -58204,96 +58157,96 @@
 SNSを受動的に見ることは百害あって一利なし。</t>
         </is>
       </c>
-      <c r="C1980" t="n">
+      <c r="C1978" t="n">
         <v>30</v>
       </c>
-      <c r="D1980" t="n">
+      <c r="D1978" t="n">
         <v>3</v>
       </c>
-      <c r="E1980" t="inlineStr">
+      <c r="E1978" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1981">
-      <c r="A1981" t="inlineStr">
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
         <is>
           <t>2026-06-11 10:45:10</t>
         </is>
       </c>
-      <c r="B1981" t="inlineStr">
+      <c r="B1979" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1981" t="n">
+      <c r="C1979" t="n">
         <v>3</v>
       </c>
-      <c r="D1981" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1982">
-      <c r="A1982" t="inlineStr">
+      <c r="D1979" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
         <is>
           <t>2026-06-11 11:26:00</t>
         </is>
       </c>
-      <c r="B1982" t="inlineStr">
+      <c r="B1980" t="inlineStr">
         <is>
           <t>男磨きのゴールは「俺は一生、セ◯クスに困らない」という自信を作ること。 
 この自信がモテ以外の人生の楽しみに集中させてくれる。 そして、余裕を生みさらにモテを生んでくれる。 
 だから、俺は「ブスでもBBAでもいいから片っ端からいけ」と言ってるのよ。</t>
         </is>
       </c>
-      <c r="C1982" t="n">
+      <c r="C1980" t="n">
         <v>70</v>
       </c>
-      <c r="D1982" t="n">
+      <c r="D1980" t="n">
         <v>4</v>
       </c>
-      <c r="E1982" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1983">
-      <c r="A1983" t="inlineStr">
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
         <is>
           <t>2026-06-11 11:30:28</t>
         </is>
       </c>
-      <c r="B1983" t="inlineStr">
+      <c r="B1981" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1983" t="n">
+      <c r="C1981" t="n">
         <v>2</v>
       </c>
-      <c r="D1983" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1983" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1984">
-      <c r="A1984" t="inlineStr">
+      <c r="D1981" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
         <is>
           <t>2026-06-12 08:50:00</t>
         </is>
       </c>
-      <c r="B1984" t="inlineStr">
+      <c r="B1982" t="inlineStr">
         <is>
           <t>奥手な童貞の脳内  
 小学生時代 
@@ -58308,25 +58261,25 @@
 「昇進して女を見返すやで！」</t>
         </is>
       </c>
-      <c r="C1984" t="n">
+      <c r="C1982" t="n">
         <v>274</v>
       </c>
-      <c r="D1984" t="n">
+      <c r="D1982" t="n">
         <v>9</v>
       </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
         <is>
           <t>2026-06-12 09:20:00</t>
         </is>
       </c>
-      <c r="B1985" t="inlineStr">
+      <c r="B1983" t="inlineStr">
         <is>
           <t>退化を促すドーパミン 
 ・悪口 
@@ -58344,48 +58297,48 @@
 ドーパミンを得る対象を変えるだけで、人生は変わる。</t>
         </is>
       </c>
-      <c r="C1985" t="n">
+      <c r="C1983" t="n">
         <v>17</v>
       </c>
-      <c r="D1985" t="n">
+      <c r="D1983" t="n">
         <v>1</v>
       </c>
-      <c r="E1985" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1986">
-      <c r="A1986" t="inlineStr">
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
         <is>
           <t>2026-06-12 09:41:33</t>
         </is>
       </c>
-      <c r="B1986" t="inlineStr">
+      <c r="B1984" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1986" t="n">
+      <c r="C1984" t="n">
         <v>6</v>
       </c>
-      <c r="D1986" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1986" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1987">
-      <c r="A1987" t="inlineStr">
+      <c r="D1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
         <is>
           <t>2026-06-12 10:00:02</t>
         </is>
       </c>
-      <c r="B1987" t="inlineStr">
+      <c r="B1985" t="inlineStr">
         <is>
           <t>非モテはいきなり本命に行くな。
 あなたが「俺でもイケるかも」と思っている女にさえ、チキってアプローチできない時点で無理です。 
@@ -58394,25 +58347,25 @@
 まずは男磨きをし、ブスとBBAを口説くことから始めてください。</t>
         </is>
       </c>
-      <c r="C1987" t="n">
+      <c r="C1985" t="n">
         <v>14</v>
       </c>
-      <c r="D1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
+      <c r="D1985" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
         <is>
           <t>2026-06-12 10:28:00</t>
         </is>
       </c>
-      <c r="B1988" t="inlineStr">
+      <c r="B1986" t="inlineStr">
         <is>
           <t>負け犬の遠吠え集 
 ・「独身貴族」 
@@ -58426,11 +58379,57 @@
 逆に素直に「うらやましい」「悔しい」が言える男は強い。</t>
         </is>
       </c>
+      <c r="C1986" t="n">
+        <v>28</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:40:53</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:49:07</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1988" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D1988" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E1988" t="inlineStr">
         <is>
@@ -58441,56 +58440,10 @@
     <row r="1989">
       <c r="A1989" t="inlineStr">
         <is>
-          <t>2026-06-12 10:40:53</t>
+          <t>2026-06-12 10:53:00</t>
         </is>
       </c>
       <c r="B1989" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
-        </is>
-      </c>
-      <c r="C1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1989" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:49:07</t>
-        </is>
-      </c>
-      <c r="B1990" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1990" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1990" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1990" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1991">
-      <c r="A1991" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:53:00</t>
-        </is>
-      </c>
-      <c r="B1991" t="inlineStr">
         <is>
           <t>決定疲れを減らす方法 
 ・デスクの整理 
@@ -58502,74 +58455,74 @@
 これで大事なタスクへの火力が爆上がりします。</t>
         </is>
       </c>
-      <c r="C1991" t="n">
+      <c r="C1989" t="n">
         <v>15</v>
       </c>
-      <c r="D1991" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1991" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
+      <c r="D1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
         <is>
           <t>2026-06-12 11:17:04</t>
         </is>
       </c>
-      <c r="B1992" t="inlineStr">
+      <c r="B1990" t="inlineStr">
         <is>
           <t>男の人生はシンプル。
 唸るほど金を持ち、ジムに行き、女行き倒す。
 他の事はどうでもいい。 https://t.co/9LrSQYOjXd</t>
         </is>
       </c>
-      <c r="C1992" t="n">
+      <c r="C1990" t="n">
         <v>77</v>
       </c>
-      <c r="D1992" t="n">
+      <c r="D1990" t="n">
         <v>6</v>
       </c>
-      <c r="E1992" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
         <is>
           <t>2026-06-12 11:46:23</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1991" t="inlineStr">
         <is>
           <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
 無料で空気を吸った方がコスパいい。</t>
         </is>
       </c>
-      <c r="C1993" t="n">
+      <c r="C1991" t="n">
         <v>19</v>
       </c>
-      <c r="D1993" t="n">
+      <c r="D1991" t="n">
         <v>1</v>
       </c>
-      <c r="E1993" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1994">
-      <c r="A1994" t="inlineStr">
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-12 12:00:00</t>
         </is>
       </c>
-      <c r="B1994" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>疲れているのに眠れない原因 
 ①反芻思考 
@@ -58581,50 +58534,50 @@
 まずは原因を分析するところから始めよう。</t>
         </is>
       </c>
-      <c r="C1994" t="n">
+      <c r="C1992" t="n">
         <v>11</v>
       </c>
-      <c r="D1994" t="n">
+      <c r="D1992" t="n">
         <v>1</v>
       </c>
-      <c r="E1994" t="inlineStr">
+      <c r="E1992" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
         <is>
           <t>2026-06-12 12:32:00</t>
         </is>
       </c>
-      <c r="B1995" t="inlineStr">
+      <c r="B1993" t="inlineStr">
         <is>
           <t>睡眠の質を測るために、昔はスマートウォッチつけて寝てたけどやめちゃったな。
 理由はゴツゴツしてて睡眠の邪魔になっていたのと、別に計測したからといって質が上がるわけではないから。
 ”翌日のパフォーマンスが向上しているか”という体感こそがエビデンスだと思っています。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
+      <c r="C1993" t="n">
         <v>7</v>
       </c>
-      <c r="D1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1995" t="inlineStr">
+      <c r="D1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1993" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
         <is>
           <t>2026-06-12 21:47:00</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1994" t="inlineStr">
         <is>
           <t>朝の水分補給は、ただの真水では睡眠中に失った電解質は取り戻せない。 
 また、電解質が入っていないと飲んだ水が身体に行き届きにくくなる。 
@@ -58632,25 +58585,25 @@
 もしこれが不味くて飲めないなら、「みそ汁」「コーンスープ」「電解質パウダー」でもOK</t>
         </is>
       </c>
-      <c r="C1996" t="n">
+      <c r="C1994" t="n">
         <v>21</v>
       </c>
-      <c r="D1996" t="n">
+      <c r="D1994" t="n">
         <v>2</v>
       </c>
-      <c r="E1996" t="inlineStr">
+      <c r="E1994" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-13 07:32:34</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>スマホ依存症を治すために私がやったこと 
 ・スマホなし1時間散歩 
@@ -58663,25 +58616,25 @@
 そして、SNSを全部PCに移せば、スマホを使う理由は少なくなる。</t>
         </is>
       </c>
-      <c r="C1997" t="n">
+      <c r="C1995" t="n">
         <v>82</v>
       </c>
-      <c r="D1997" t="n">
+      <c r="D1995" t="n">
         <v>4</v>
       </c>
-      <c r="E1997" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-13 08:27:00</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>非モテがチン騎士になる理由。  
 結論、それ以外の関わり方を知らないから。 
@@ -58690,25 +58643,25 @@
 優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
+      <c r="C1996" t="n">
         <v>57</v>
       </c>
-      <c r="D1998" t="n">
+      <c r="D1996" t="n">
         <v>1</v>
       </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-13 09:00:01</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>スマホ依存症の症状 
 ・起きた瞬間にチェック 
@@ -58724,25 +58677,25 @@
 ・21時以降は見ない</t>
         </is>
       </c>
-      <c r="C1999" t="n">
+      <c r="C1997" t="n">
         <v>16</v>
       </c>
-      <c r="D1999" t="n">
+      <c r="D1997" t="n">
         <v>2</v>
       </c>
-      <c r="E1999" t="inlineStr">
+      <c r="E1997" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-13 09:21:45</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>自己満男磨き(笑)と呼ばれている習慣を擁護します。  
 【オナ禁】
@@ -58773,25 +58726,25 @@
 正しく評価して自分に落とし込むことが重要。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
+      <c r="C1998" t="n">
         <v>10</v>
       </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-13 09:28:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>口呼吸が習慣化している人の特徴 
 ①舌が白い 
@@ -58802,25 +58755,25 @@
 高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
+      <c r="C1999" t="n">
         <v>26</v>
       </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-13 10:06:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58834,11 +58787,57 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
+      <c r="C2000" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:00:02</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:17:03</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C2002" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D2002" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2002" t="inlineStr">
         <is>
@@ -58849,56 +58848,10 @@
     <row r="2003">
       <c r="A2003" t="inlineStr">
         <is>
-          <t>2026-06-13 11:00:02</t>
+          <t>2026-06-13 12:26:00</t>
         </is>
       </c>
       <c r="B2003" t="inlineStr">
-        <is>
-          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
-        </is>
-      </c>
-      <c r="C2003" t="n">
-        <v>60</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
-        <is>
-          <t>2026-06-13 11:17:03</t>
-        </is>
-      </c>
-      <c r="B2004" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C2004" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
-        <is>
-          <t>2026-06-13 12:26:00</t>
-        </is>
-      </c>
-      <c r="B2005" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58910,25 +58863,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
+      <c r="C2003" t="n">
         <v>16</v>
       </c>
-      <c r="D2005" t="n">
+      <c r="D2003" t="n">
         <v>1</v>
       </c>
-      <c r="E2005" t="inlineStr">
+      <c r="E2003" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58939,25 +58892,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
+      <c r="C2004" t="n">
         <v>19</v>
       </c>
-      <c r="D2006" t="n">
+      <c r="D2004" t="n">
         <v>2</v>
       </c>
-      <c r="E2006" t="inlineStr">
+      <c r="E2004" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58969,25 +58922,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
+      <c r="C2005" t="n">
         <v>19</v>
       </c>
-      <c r="D2007" t="n">
+      <c r="D2005" t="n">
         <v>2</v>
       </c>
-      <c r="E2007" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -59004,25 +58957,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C2008" t="n">
+      <c r="C2006" t="n">
         <v>22</v>
       </c>
-      <c r="D2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2008" t="inlineStr">
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -59038,25 +58991,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
+      <c r="C2007" t="n">
         <v>17</v>
       </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -59069,48 +59022,48 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
+      <c r="C2008" t="n">
         <v>5</v>
       </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-14 09:07:02</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-14 09:31:00</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -59126,25 +59079,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -59154,25 +59107,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -59184,25 +59137,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -59214,25 +59167,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -59246,25 +59199,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -59281,25 +59234,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -59309,25 +59262,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -59341,25 +59294,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -59369,25 +59322,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -59398,25 +59351,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -59429,25 +59382,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59457,25 +59410,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59484,25 +59437,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59510,49 +59463,49 @@
 地味なライフハック。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-21 09:41:41</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>起床3秒後のEAA❌
 起床3秒後の歯磨き⭕</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-21 07:01:00</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59565,25 +59518,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59593,6 +59546,53 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:03:13</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+        </is>
+      </c>
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-06-19 19:34:04</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
+        </is>
+      </c>
       <c r="C2028" t="n">
         <v>0</v>
       </c>
@@ -59608,57 +59608,10 @@
     <row r="2029">
       <c r="A2029" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B2029" t="inlineStr">
-        <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
-        </is>
-      </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
-        <is>
-          <t>2026-06-19 19:34:04</t>
-        </is>
-      </c>
-      <c r="B2030" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B2031" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59666,73 +59619,73 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="C2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-06-16 18:11:46</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
         </is>
       </c>
-      <c r="C2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-16 06:56:00</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59747,25 +59700,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59776,25 +59729,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
+      <c r="C2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2033" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59802,25 +59755,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59835,25 +59788,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59864,25 +59817,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59894,25 +59847,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59922,25 +59875,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59948,25 +59901,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59977,25 +59930,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -60008,25 +59961,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -60034,25 +59987,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -60064,25 +60017,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -60090,25 +60043,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -60123,25 +60076,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -60152,25 +60105,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -60187,25 +60140,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -60221,54 +60174,54 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
-      <c r="C2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2050" t="inlineStr">
+      <c r="C2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2048" t="inlineStr">
         <is>
           <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-06-25 19:07:20</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
 すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
         </is>
       </c>
-      <c r="C2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="C2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-06-25 19:26:49</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -60296,25 +60249,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="C2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -60326,25 +60279,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="C2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -60357,25 +60310,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="C2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -60386,25 +60339,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="C2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -60412,25 +60365,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="C2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -60440,30 +60393,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2057" t="inlineStr">
+      <c r="C2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2055" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60474,30 +60427,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2058" t="inlineStr">
+      <c r="C2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2056" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60507,30 +60460,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2059" t="inlineStr">
+      <c r="C2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2057" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60543,30 +60496,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2060" t="inlineStr">
+      <c r="C2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2058" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60577,55 +60530,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="C2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2062" t="inlineStr">
+      <c r="C2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2060" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60638,25 +60591,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60667,25 +60620,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60696,25 +60649,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60723,19 +60676,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60752,19 +60705,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60777,19 +60730,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60801,19 +60754,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60822,19 +60775,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60847,19 +60800,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60870,19 +60823,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60894,19 +60847,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60915,19 +60868,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60946,24 +60899,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2073" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60975,19 +60928,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -61002,19 +60955,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -61028,19 +60981,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -61051,19 +61004,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -61073,38 +61026,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -61113,19 +61066,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -61137,19 +61090,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-07-24 12:00:00</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>マチアプはあなたの恋愛市場価値を測るための試金石。
 【上位1%】
@@ -61171,25 +61124,25 @@
 俺が変われたのは、チー牛時代にマチアプで惨敗して現実を知ったから。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -61199,19 +61152,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -61225,19 +61178,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -61255,24 +61208,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2087" t="inlineStr">
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2085" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -61283,24 +61236,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2088" t="inlineStr">
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2086" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -61310,24 +61263,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2089" t="inlineStr">
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2087" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -61336,19 +61289,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -61362,19 +61315,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -61387,19 +61340,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -61412,19 +61365,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61438,19 +61391,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61471,19 +61424,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61491,19 +61444,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61511,19 +61464,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61533,19 +61486,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61554,19 +61507,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61580,25 +61533,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61612,30 +61565,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2099" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61648,25 +61601,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61681,25 +61634,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61712,25 +61665,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61740,25 +61693,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61772,25 +61725,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61813,25 +61766,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61840,25 +61793,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61873,25 +61826,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61908,25 +61861,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61937,25 +61890,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61973,25 +61926,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -62004,25 +61957,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -62033,48 +61986,48 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
         </is>
       </c>
-      <c r="C2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -62093,25 +62046,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -62127,25 +62080,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="C2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -62157,25 +62110,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="C2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -62185,25 +62138,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="C2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -62215,25 +62168,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="C2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -62243,25 +62196,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="C2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -62283,25 +62236,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="C2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -62315,30 +62268,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2123" t="inlineStr">
+      <c r="C2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2121" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -62350,25 +62303,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="C2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -62379,25 +62332,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62433,25 +62386,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62463,25 +62416,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62497,25 +62450,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62527,25 +62480,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="C2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62574,50 +62527,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="C2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="C2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62632,25 +62585,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="C2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62661,25 +62614,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="C2131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62697,19 +62650,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62730,19 +62683,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62754,19 +62707,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62778,19 +62731,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62801,19 +62754,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62827,19 +62780,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62851,19 +62804,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62876,19 +62829,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62904,19 +62857,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62934,19 +62887,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62960,19 +62913,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62984,19 +62937,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -63009,19 +62962,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -63032,19 +62985,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -63053,19 +63006,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -63075,19 +63028,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2149" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2148" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -63099,19 +63052,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2150" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2151">
-      <c r="A2151" t="inlineStr">
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2149" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -63126,19 +63079,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2151" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2152">
-      <c r="A2152" t="inlineStr">
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2152" t="inlineStr">
+      <c r="B2150" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -63151,19 +63104,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2152" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2153">
-      <c r="A2153" t="inlineStr">
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2151" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -63176,19 +63129,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2153" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2154">
-      <c r="A2154" t="inlineStr">
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2152" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -63204,19 +63157,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2154" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2155">
-      <c r="A2155" t="inlineStr">
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2153" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -63233,19 +63186,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2155" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2156">
-      <c r="A2156" t="inlineStr">
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2154" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -63258,19 +63211,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2156" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2157">
-      <c r="A2157" t="inlineStr">
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2157" t="inlineStr">
+      <c r="B2155" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -63280,19 +63233,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2157" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2158">
-      <c r="A2158" t="inlineStr">
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2156" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -63303,19 +63256,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2158" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2159">
-      <c r="A2159" t="inlineStr">
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2159" t="inlineStr">
+      <c r="B2157" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -63328,19 +63281,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2159" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2160">
-      <c r="A2160" t="inlineStr">
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2160" t="inlineStr">
+      <c r="B2158" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -63356,19 +63309,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2160" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2161">
-      <c r="A2161" t="inlineStr">
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2161" t="inlineStr">
+      <c r="B2159" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -63383,19 +63336,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2161" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2162">
-      <c r="A2162" t="inlineStr">
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2162" t="inlineStr">
+      <c r="B2160" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -63412,7 +63365,7 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2162" t="inlineStr">
+      <c r="E2160" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2160"/>
+  <dimension ref="A1:G2159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56703,36 +56703,10 @@
     <row r="1927">
       <c r="A1927" t="inlineStr">
         <is>
-          <t>2026-06-07 09:06:12</t>
+          <t>2026-06-07 09:20:00</t>
         </is>
       </c>
       <c r="B1927" t="inlineStr">
-        <is>
-          <t>毎日、行動してくださる方が現れてとても嬉しいです。
-数年前まで私は「クラスで一言も喋らない自閉症のチー牛」でした。
-そこから、努力と知識で自分を変えてきた集大成を公開しています。
-これを見たあなたは今後人生で女や金、憂鬱な人生に困ることはないです。… https://t.co/16wOk9Tj8f</t>
-        </is>
-      </c>
-      <c r="C1927" t="n">
-        <v>4</v>
-      </c>
-      <c r="D1927" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1927" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1928">
-      <c r="A1928" t="inlineStr">
-        <is>
-          <t>2026-06-07 09:20:00</t>
-        </is>
-      </c>
-      <c r="B1928" t="inlineStr">
         <is>
           <t>あなたが時間貧乏である理由 
 ①汚部屋 
@@ -56747,25 +56721,25 @@
 要領がいい人は、これの逆を行きます。</t>
         </is>
       </c>
-      <c r="C1928" t="n">
+      <c r="C1927" t="n">
         <v>123</v>
       </c>
-      <c r="D1928" t="n">
+      <c r="D1927" t="n">
         <v>14</v>
       </c>
-      <c r="E1928" t="inlineStr">
+      <c r="E1927" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1929">
-      <c r="A1929" t="inlineStr">
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
         <is>
           <t>2026-06-07 09:41:00</t>
         </is>
       </c>
-      <c r="B1929" t="inlineStr">
+      <c r="B1928" t="inlineStr">
         <is>
           <t>清潔感を出すためにやること 
 ・眉毛を整える 
@@ -56778,11 +56752,34 @@
 やって当たり前のこと。</t>
         </is>
       </c>
+      <c r="C1928" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-06-07 09:47:57</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1929" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D1929" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1929" t="inlineStr">
         <is>
@@ -56793,33 +56790,10 @@
     <row r="1930">
       <c r="A1930" t="inlineStr">
         <is>
-          <t>2026-06-07 09:47:57</t>
+          <t>2026-06-07 10:45:00</t>
         </is>
       </c>
       <c r="B1930" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1930" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1930" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1930" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1931">
-      <c r="A1931" t="inlineStr">
-        <is>
-          <t>2026-06-07 10:45:00</t>
-        </is>
-      </c>
-      <c r="B1931" t="inlineStr">
         <is>
           <t>大学デビュー失敗した陰キャたちへ 
 結論、挽回は無理。 
@@ -56834,25 +56808,25 @@
 種まきの期間だと思え。</t>
         </is>
       </c>
-      <c r="C1931" t="n">
+      <c r="C1930" t="n">
         <v>165</v>
       </c>
-      <c r="D1931" t="n">
+      <c r="D1930" t="n">
         <v>9</v>
       </c>
-      <c r="E1931" t="inlineStr">
+      <c r="E1930" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
     </row>
-    <row r="1932">
-      <c r="A1932" t="inlineStr">
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
         <is>
           <t>2026-06-07 10:57:46</t>
         </is>
       </c>
-      <c r="B1932" t="inlineStr">
+      <c r="B1931" t="inlineStr">
         <is>
           <t>私はスポーツ観戦大好きで、ニート時代は深夜にプレミアリーグ見まくっていたサカ豚。
 でも、間違いなく人の応援をしている場合じゃなかった。
@@ -56860,48 +56834,48 @@
 スポーツ観戦はすでにやることを終えた上級国民の娯楽。 https://t.co/0yTrug56kv</t>
         </is>
       </c>
+      <c r="C1931" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-06-07 11:20:26</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1932" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D1932" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1932" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>2026-06-07 11:20:26</t>
+          <t>2026-06-07 11:47:00</t>
         </is>
       </c>
       <c r="B1933" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1933" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1933" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1933" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1934">
-      <c r="A1934" t="inlineStr">
-        <is>
-          <t>2026-06-07 11:47:00</t>
-        </is>
-      </c>
-      <c r="B1934" t="inlineStr">
         <is>
           <t>早起きできない奴の特徴 
 ・寝る時間が遅い 
@@ -56917,25 +56891,25 @@
 ・8~9時間確保する</t>
         </is>
       </c>
-      <c r="C1934" t="n">
+      <c r="C1933" t="n">
         <v>44</v>
       </c>
-      <c r="D1934" t="n">
+      <c r="D1933" t="n">
         <v>6</v>
       </c>
-      <c r="E1934" t="inlineStr">
+      <c r="E1933" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1935">
-      <c r="A1935" t="inlineStr">
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
         <is>
           <t>2026-06-07 21:59:00</t>
         </is>
       </c>
-      <c r="B1935" t="inlineStr">
+      <c r="B1934" t="inlineStr">
         <is>
           <t>朝コーヒーがあなたにもたらすもの 
 ・集中力の爆上がり 
@@ -56949,48 +56923,48 @@
 俺はブラックコーヒー飲んで爆速でポストを量産している。</t>
         </is>
       </c>
+      <c r="C1934" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:45:52</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
+        </is>
+      </c>
       <c r="C1935" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D1935" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1935" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>2026-06-08 02:45:52</t>
+          <t>2026-06-08 03:03:37</t>
         </is>
       </c>
       <c r="B1936" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
-        </is>
-      </c>
-      <c r="C1936" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1936" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1936" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1937">
-      <c r="A1937" t="inlineStr">
-        <is>
-          <t>2026-06-08 03:03:37</t>
-        </is>
-      </c>
-      <c r="B1937" t="inlineStr">
         <is>
           <t>地味にQOLを上げる方法
 ・歯ブラシ
@@ -57001,25 +56975,25 @@
 いつも使う物に少し金払うだけで、QOLは上がる。</t>
         </is>
       </c>
-      <c r="C1937" t="n">
+      <c r="C1936" t="n">
         <v>66</v>
       </c>
-      <c r="D1937" t="n">
+      <c r="D1936" t="n">
         <v>5</v>
       </c>
-      <c r="E1937" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1938">
-      <c r="A1938" t="inlineStr">
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
         <is>
           <t>2026-06-08 07:49:00</t>
         </is>
       </c>
-      <c r="B1938" t="inlineStr">
+      <c r="B1937" t="inlineStr">
         <is>
           <t>睡眠不足で筋トレしても意味ない 
 ・筋肉は寝てる間に成長する 
@@ -57029,25 +57003,25 @@
 まずは寝ろ。</t>
         </is>
       </c>
-      <c r="C1938" t="n">
+      <c r="C1937" t="n">
         <v>33</v>
       </c>
-      <c r="D1938" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1938" t="inlineStr">
+      <c r="D1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1937" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1939">
-      <c r="A1939" t="inlineStr">
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
         <is>
           <t>2026-06-08 08:43:00</t>
         </is>
       </c>
-      <c r="B1939" t="inlineStr">
+      <c r="B1938" t="inlineStr">
         <is>
           <t>”極振り”が人生を変える。
 女攻略したいなら
@@ -57059,25 +57033,25 @@
 俺はこの極振りでコンプを克服してきた。</t>
         </is>
       </c>
-      <c r="C1939" t="n">
+      <c r="C1938" t="n">
         <v>113</v>
       </c>
-      <c r="D1939" t="n">
+      <c r="D1938" t="n">
         <v>10</v>
       </c>
-      <c r="E1939" t="inlineStr">
+      <c r="E1938" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1940">
-      <c r="A1940" t="inlineStr">
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
         <is>
           <t>2026-06-08 09:14:00</t>
         </is>
       </c>
-      <c r="B1940" t="inlineStr">
+      <c r="B1939" t="inlineStr">
         <is>
           <t>童貞は
 ・身長10cm盛る
@@ -57088,25 +57062,25 @@
 「俺のち〇こを必要としている人はいる」という自信にはなる。</t>
         </is>
       </c>
-      <c r="C1940" t="n">
+      <c r="C1939" t="n">
         <v>158</v>
       </c>
-      <c r="D1940" t="n">
+      <c r="D1939" t="n">
         <v>6</v>
       </c>
-      <c r="E1940" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1941">
-      <c r="A1941" t="inlineStr">
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
         <is>
           <t>2026-06-08 10:00:01</t>
         </is>
       </c>
-      <c r="B1941" t="inlineStr">
+      <c r="B1940" t="inlineStr">
         <is>
           <t>「チー牛家庭」の問題点。
 ・食事から教育方針まで、すべて母親が決める 
@@ -57117,25 +57091,25 @@
 はしごを外され、決断力を育ててこなかった</t>
         </is>
       </c>
-      <c r="C1941" t="n">
+      <c r="C1940" t="n">
         <v>32</v>
       </c>
-      <c r="D1941" t="n">
+      <c r="D1940" t="n">
         <v>1</v>
       </c>
-      <c r="E1941" t="inlineStr">
+      <c r="E1940" t="inlineStr">
         <is>
           <t>exam</t>
         </is>
       </c>
     </row>
-    <row r="1942">
-      <c r="A1942" t="inlineStr">
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
         <is>
           <t>2026-06-08 10:41:00</t>
         </is>
       </c>
-      <c r="B1942" t="inlineStr">
+      <c r="B1941" t="inlineStr">
         <is>
           <t>正直、学生時代に”イジメすらもされないような陰キャ”だった方がSNSやマチアプで人気者になるのは厳しい。 
 これらはあくまで拡声器。 
@@ -57143,25 +57117,25 @@
 やることは自己啓発陰キャになり、自分本体をひたすら磨くこと。</t>
         </is>
       </c>
-      <c r="C1942" t="n">
+      <c r="C1941" t="n">
         <v>53</v>
       </c>
-      <c r="D1942" t="n">
+      <c r="D1941" t="n">
         <v>4</v>
       </c>
-      <c r="E1942" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1943">
-      <c r="A1943" t="inlineStr">
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
         <is>
           <t>2026-06-08 11:09:00</t>
         </is>
       </c>
-      <c r="B1943" t="inlineStr">
+      <c r="B1942" t="inlineStr">
         <is>
           <t>スマホ中毒がデフォルトの時代。 
 そこを脱して「静寂」を手に入れた人間は、
@@ -57169,8 +57143,31 @@
 周りが耽溺している間に、あなたは淡々とリアルな成果を積み上げる側へ回れ。</t>
         </is>
       </c>
+      <c r="C1942" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:14:05</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1943" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D1943" t="n">
         <v>1</v>
@@ -57184,33 +57181,10 @@
     <row r="1944">
       <c r="A1944" t="inlineStr">
         <is>
-          <t>2026-06-08 11:14:05</t>
+          <t>2026-06-08 12:00:01</t>
         </is>
       </c>
       <c r="B1944" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1944" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1944" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1944" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1945">
-      <c r="A1945" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:00:01</t>
-        </is>
-      </c>
-      <c r="B1945" t="inlineStr">
         <is>
           <t>睡眠を削ると時間が減る。
 判断力低下
@@ -57223,25 +57197,25 @@
 睡眠を削るのは「ここぞ」という時だけでいい。</t>
         </is>
       </c>
-      <c r="C1945" t="n">
+      <c r="C1944" t="n">
         <v>29</v>
       </c>
-      <c r="D1945" t="n">
+      <c r="D1944" t="n">
         <v>1</v>
       </c>
-      <c r="E1945" t="inlineStr">
+      <c r="E1944" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1946">
-      <c r="A1946" t="inlineStr">
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
         <is>
           <t>2026-06-09 07:28:00</t>
         </is>
       </c>
-      <c r="B1946" t="inlineStr">
+      <c r="B1945" t="inlineStr">
         <is>
           <t>モテる男は周りから固めていく。
 まず本命の友達から評価を得てクチコミを広める。
@@ -57249,25 +57223,25 @@
 逆に非モテはガンギマリで女にピンポイントで、くそきもアプローチだけする。</t>
         </is>
       </c>
-      <c r="C1946" t="n">
+      <c r="C1945" t="n">
         <v>23</v>
       </c>
-      <c r="D1946" t="n">
+      <c r="D1945" t="n">
         <v>2</v>
       </c>
-      <c r="E1946" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1947">
-      <c r="A1947" t="inlineStr">
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
         <is>
           <t>2026-06-09 08:06:00</t>
         </is>
       </c>
-      <c r="B1947" t="inlineStr">
+      <c r="B1946" t="inlineStr">
         <is>
           <t>3日坊主の奴はSNSを見すぎ。
 他人の投稿ばかり見て、隣の芝生が青く見えるがゆえ、やることがブレている。
@@ -57276,25 +57250,25 @@
 フォローは厳選している。</t>
         </is>
       </c>
-      <c r="C1947" t="n">
+      <c r="C1946" t="n">
         <v>22</v>
       </c>
-      <c r="D1947" t="n">
+      <c r="D1946" t="n">
         <v>1</v>
       </c>
-      <c r="E1947" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1948">
-      <c r="A1948" t="inlineStr">
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
         <is>
           <t>2026-06-09 08:50:00</t>
         </is>
       </c>
-      <c r="B1948" t="inlineStr">
+      <c r="B1947" t="inlineStr">
         <is>
           <t>テストステロンを1日で取り戻す方法 
 ・8時間睡眠 
@@ -57310,25 +57284,25 @@
 翌日には余裕で回復してる。</t>
         </is>
       </c>
-      <c r="C1948" t="n">
+      <c r="C1947" t="n">
         <v>953</v>
       </c>
-      <c r="D1948" t="n">
+      <c r="D1947" t="n">
         <v>66</v>
       </c>
-      <c r="E1948" t="inlineStr">
+      <c r="E1947" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1949">
-      <c r="A1949" t="inlineStr">
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
         <is>
           <t>2026-06-09 09:30:00</t>
         </is>
       </c>
-      <c r="B1949" t="inlineStr">
+      <c r="B1948" t="inlineStr">
         <is>
           <t>・「ヒョロガリがフリーウェイト使うのは申し訳ない。」 
 ・「インターバル3分も取るのは気まずい。」 
@@ -57338,8 +57312,31 @@
 そして、あなたも他の会員と同じ額の会費を払ってます。</t>
         </is>
       </c>
+      <c r="C1948" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:43:01</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
+        </is>
+      </c>
       <c r="C1949" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D1949" t="n">
         <v>0</v>
@@ -57353,12 +57350,12 @@
     <row r="1950">
       <c r="A1950" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:01</t>
+          <t>2026-06-09 09:43:52</t>
         </is>
       </c>
       <c r="B1950" t="inlineStr">
         <is>
-          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C1950" t="n">
@@ -57376,33 +57373,10 @@
     <row r="1951">
       <c r="A1951" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:52</t>
+          <t>2026-06-09 10:06:00</t>
         </is>
       </c>
       <c r="B1951" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1951" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1951" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1951" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1952">
-      <c r="A1952" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:06:00</t>
-        </is>
-      </c>
-      <c r="B1952" t="inlineStr">
         <is>
           <t>受け身な男の脳内  
 小学生時代 
@@ -57417,50 +57391,50 @@
 「出世出来たら結婚出来るんだろうなぁ」</t>
         </is>
       </c>
-      <c r="C1952" t="n">
+      <c r="C1951" t="n">
         <v>84</v>
       </c>
-      <c r="D1952" t="n">
+      <c r="D1951" t="n">
         <v>6</v>
       </c>
-      <c r="E1952" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1953">
-      <c r="A1953" t="inlineStr">
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
         <is>
           <t>2026-06-09 10:12:00</t>
         </is>
       </c>
-      <c r="B1953" t="inlineStr">
+      <c r="B1952" t="inlineStr">
         <is>
           <t>スマホ中毒者は自分だけの「対策ノウハウ」を作っていけ。
 確かにタイムロック、瞑想等は効果はあるが単なるテクニック論に過ぎない。
 自分の癖を見つけて、ピンポイントで対策する方が効果的。</t>
         </is>
       </c>
-      <c r="C1953" t="n">
+      <c r="C1952" t="n">
         <v>19</v>
       </c>
-      <c r="D1953" t="n">
+      <c r="D1952" t="n">
         <v>2</v>
       </c>
-      <c r="E1953" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1954">
-      <c r="A1954" t="inlineStr">
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
         <is>
           <t>2026-06-09 10:48:00</t>
         </is>
       </c>
-      <c r="B1954" t="inlineStr">
+      <c r="B1953" t="inlineStr">
         <is>
           <t>非モテのコミュニケーション悪癖 
 ・名前を呼べない 
@@ -57475,25 +57449,25 @@
 2つ以上当てはまれば、キモがれらている可能性大。</t>
         </is>
       </c>
-      <c r="C1954" t="n">
+      <c r="C1953" t="n">
         <v>54</v>
       </c>
-      <c r="D1954" t="n">
+      <c r="D1953" t="n">
         <v>6</v>
       </c>
-      <c r="E1954" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1955">
-      <c r="A1955" t="inlineStr">
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
         <is>
           <t>2026-06-09 11:20:00</t>
         </is>
       </c>
-      <c r="B1955" t="inlineStr">
+      <c r="B1954" t="inlineStr">
         <is>
           <t>モテテクは結果論。 
 ・返信を遅らせる 
@@ -57503,49 +57477,49 @@
 確かに非モテのモテテク武装は大事。 だから無意味ではないが、 結果論であることを理解した上で使った方がいい。</t>
         </is>
       </c>
+      <c r="C1954" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:30:00</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>筋トレをやらない理由はない。 
+毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
+        </is>
+      </c>
       <c r="C1955" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1955" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1955" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="1956">
       <c r="A1956" t="inlineStr">
         <is>
-          <t>2026-06-09 11:30:00</t>
+          <t>2026-06-10 07:40:00</t>
         </is>
       </c>
       <c r="B1956" t="inlineStr">
-        <is>
-          <t>筋トレをやらない理由はない。 
-毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
-        </is>
-      </c>
-      <c r="C1956" t="n">
-        <v>22</v>
-      </c>
-      <c r="D1956" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1956" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="1957">
-      <c r="A1957" t="inlineStr">
-        <is>
-          <t>2026-06-10 07:40:00</t>
-        </is>
-      </c>
-      <c r="B1957" t="inlineStr">
         <is>
           <t>スマホが近くにあるだけで頭が悪くなる。
 脳が「スマホを無視しろ」とコマンドを送るのにリソースを割くからです。
@@ -57554,25 +57528,25 @@
 物理的な距離だけがあなたの脳を解放します。</t>
         </is>
       </c>
-      <c r="C1957" t="n">
+      <c r="C1956" t="n">
         <v>15</v>
       </c>
-      <c r="D1957" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1957" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1958">
-      <c r="A1958" t="inlineStr">
+      <c r="D1956" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
         <is>
           <t>2026-06-10 08:23:00</t>
         </is>
       </c>
-      <c r="B1958" t="inlineStr">
+      <c r="B1957" t="inlineStr">
         <is>
           <t>一番、結果が出るのはコンフォートゾーンでガチガチにハメ技決めてる時。
 ・毎日、同じ食事を摂る
@@ -57582,25 +57556,25 @@
 「つまらない」と感じると思うが、いちいち新しいことを始める必要はない。君の努力は正しい。</t>
         </is>
       </c>
-      <c r="C1958" t="n">
+      <c r="C1957" t="n">
         <v>45</v>
       </c>
-      <c r="D1958" t="n">
+      <c r="D1957" t="n">
         <v>5</v>
       </c>
-      <c r="E1958" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1959">
-      <c r="A1959" t="inlineStr">
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
         <is>
           <t>2026-06-10 08:42:00</t>
         </is>
       </c>
-      <c r="B1959" t="inlineStr">
+      <c r="B1958" t="inlineStr">
         <is>
           <t>ストイックには2種類ある。  
 ・サボらない努力マシーン 
@@ -57610,25 +57584,25 @@
 そして、翌日には何事もなかったようにルーティンに戻る。</t>
         </is>
       </c>
-      <c r="C1959" t="n">
+      <c r="C1958" t="n">
         <v>31</v>
       </c>
-      <c r="D1959" t="n">
+      <c r="D1958" t="n">
         <v>5</v>
       </c>
-      <c r="E1959" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1960">
-      <c r="A1960" t="inlineStr">
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
         <is>
           <t>2026-06-10 09:20:00</t>
         </is>
       </c>
-      <c r="B1960" t="inlineStr">
+      <c r="B1959" t="inlineStr">
         <is>
           <t>筋トレで得たもの 
 ・自信 
@@ -57643,25 +57617,25 @@
 やらない理由がない。</t>
         </is>
       </c>
-      <c r="C1960" t="n">
+      <c r="C1959" t="n">
         <v>59</v>
       </c>
-      <c r="D1960" t="n">
+      <c r="D1959" t="n">
         <v>4</v>
       </c>
-      <c r="E1960" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1961">
-      <c r="A1961" t="inlineStr">
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
         <is>
           <t>2026-06-10 09:36:00</t>
         </is>
       </c>
-      <c r="B1961" t="inlineStr">
+      <c r="B1960" t="inlineStr">
         <is>
           <t>ヒョロガリのマインド
 「ハイTな食事🤓（2300kcal）」
@@ -57673,25 +57647,25 @@
 黙って食え。</t>
         </is>
       </c>
-      <c r="C1961" t="n">
+      <c r="C1960" t="n">
         <v>47</v>
       </c>
-      <c r="D1961" t="n">
+      <c r="D1960" t="n">
         <v>1</v>
       </c>
-      <c r="E1961" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1962">
-      <c r="A1962" t="inlineStr">
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
         <is>
           <t>2026-06-10 10:00:00</t>
         </is>
       </c>
-      <c r="B1962" t="inlineStr">
+      <c r="B1961" t="inlineStr">
         <is>
           <t>自信がない奴の特徴 
 ・姿勢が悪い 
@@ -57708,25 +57682,25 @@
 俺は筋トレで体を変えてから自信がついた。</t>
         </is>
       </c>
-      <c r="C1962" t="n">
+      <c r="C1961" t="n">
         <v>58</v>
       </c>
-      <c r="D1962" t="n">
+      <c r="D1961" t="n">
         <v>5</v>
       </c>
-      <c r="E1962" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1963">
-      <c r="A1963" t="inlineStr">
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
         <is>
           <t>2026-06-10 10:45:00</t>
         </is>
       </c>
-      <c r="B1963" t="inlineStr">
+      <c r="B1962" t="inlineStr">
         <is>
           <t>スマホ中毒の唯一の基準は
 「目標達成を妨げているか否か」。
@@ -57737,11 +57711,34 @@
 スクリーンタイムよりも使い方を見直せ。</t>
         </is>
       </c>
+      <c r="C1962" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1962" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:49:46</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
+        </is>
+      </c>
       <c r="C1963" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D1963" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1963" t="inlineStr">
         <is>
@@ -57752,33 +57749,10 @@
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>2026-06-10 10:49:46</t>
+          <t>2026-06-10 11:00:03</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
-        </is>
-      </c>
-      <c r="C1964" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1964" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1964" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1965">
-      <c r="A1965" t="inlineStr">
-        <is>
-          <t>2026-06-10 11:00:03</t>
-        </is>
-      </c>
-      <c r="B1965" t="inlineStr">
         <is>
           <t>男磨きしている人が陥りがちな失敗は「禁欲の目的化」。
 確かにオナ禁、コールドシャワー、瞑想といった習慣はスピではなく、科学的根拠がある。
@@ -57786,25 +57760,25 @@
 あくまで廃人が自己管理能力を上げる手段でしかない。</t>
         </is>
       </c>
-      <c r="C1965" t="n">
+      <c r="C1964" t="n">
         <v>46</v>
       </c>
-      <c r="D1965" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1965" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1966">
-      <c r="A1966" t="inlineStr">
+      <c r="D1964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
         <is>
           <t>2026-06-10 11:29:00</t>
         </is>
       </c>
-      <c r="B1966" t="inlineStr">
+      <c r="B1965" t="inlineStr">
         <is>
           <t>一般的な弱者男性の日常。
 平日は経営者のために働き、上司と得意先に頭を下げる。帰宅後は推しの配信で時間を潰す。 
@@ -57814,25 +57788,25 @@
 哲学的ゾンビとはこのこと。</t>
         </is>
       </c>
-      <c r="C1966" t="n">
+      <c r="C1965" t="n">
         <v>44</v>
       </c>
-      <c r="D1966" t="n">
+      <c r="D1965" t="n">
         <v>6</v>
       </c>
-      <c r="E1966" t="inlineStr">
+      <c r="E1965" t="inlineStr">
         <is>
           <t>sunday</t>
         </is>
       </c>
     </row>
-    <row r="1967">
-      <c r="A1967" t="inlineStr">
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
         <is>
           <t>2026-06-10 12:06:00</t>
         </is>
       </c>
-      <c r="B1967" t="inlineStr">
+      <c r="B1966" t="inlineStr">
         <is>
           <t>睡眠を30分削ると、 
 ・テストステロン低下 
@@ -57845,25 +57819,25 @@
 そして、翌朝はアラーム無しで起きる奴こそが強者。</t>
         </is>
       </c>
-      <c r="C1967" t="n">
+      <c r="C1966" t="n">
         <v>27</v>
       </c>
-      <c r="D1967" t="n">
+      <c r="D1966" t="n">
         <v>4</v>
       </c>
-      <c r="E1967" t="inlineStr">
+      <c r="E1966" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1968">
-      <c r="A1968" t="inlineStr">
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
         <is>
           <t>2026-06-11 06:18:00</t>
         </is>
       </c>
-      <c r="B1968" t="inlineStr">
+      <c r="B1967" t="inlineStr">
         <is>
           <t>弱者男性の先天的欠点
 ・短足
@@ -57879,25 +57853,25 @@
 複数当てはまると、結構人生ハードモード。</t>
         </is>
       </c>
-      <c r="C1968" t="n">
+      <c r="C1967" t="n">
         <v>38</v>
       </c>
-      <c r="D1968" t="n">
+      <c r="D1967" t="n">
         <v>2</v>
       </c>
-      <c r="E1968" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1969">
-      <c r="A1969" t="inlineStr">
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
         <is>
           <t>2026-06-11 06:29:00</t>
         </is>
       </c>
-      <c r="B1969" t="inlineStr">
+      <c r="B1968" t="inlineStr">
         <is>
           <t>ヒョロガリは週3回、BIG3をそれぞれやるだけで十分全身を鍛えられる。
 5分割で2時間は多分、続かない。
@@ -57905,25 +57879,25 @@
 週3は忙しくても行ける。</t>
         </is>
       </c>
-      <c r="C1969" t="n">
+      <c r="C1968" t="n">
         <v>36</v>
       </c>
-      <c r="D1969" t="n">
+      <c r="D1968" t="n">
         <v>1</v>
       </c>
-      <c r="E1969" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1970">
-      <c r="A1970" t="inlineStr">
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
         <is>
           <t>2026-06-11 08:44:00</t>
         </is>
       </c>
-      <c r="B1970" t="inlineStr">
+      <c r="B1969" t="inlineStr">
         <is>
           <t>俺が童貞(20歳)に戻ったらやること 
 ・ ジム入会 
@@ -57937,11 +57911,34 @@
 ・ブスでもBBAでも片っ端からアプローチ</t>
         </is>
       </c>
+      <c r="C1969" t="n">
+        <v>261</v>
+      </c>
+      <c r="D1969" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:11:09</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1970" t="n">
-        <v>261</v>
+        <v>6</v>
       </c>
       <c r="D1970" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E1970" t="inlineStr">
         <is>
@@ -57952,16 +57949,16 @@
     <row r="1971">
       <c r="A1971" t="inlineStr">
         <is>
-          <t>2026-06-11 09:11:09</t>
+          <t>2026-06-11 09:12:47</t>
         </is>
       </c>
       <c r="B1971" t="inlineStr">
         <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
         </is>
       </c>
       <c r="C1971" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D1971" t="n">
         <v>0</v>
@@ -57975,33 +57972,10 @@
     <row r="1972">
       <c r="A1972" t="inlineStr">
         <is>
-          <t>2026-06-11 09:12:47</t>
+          <t>2026-06-11 09:13:00</t>
         </is>
       </c>
       <c r="B1972" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
-        </is>
-      </c>
-      <c r="C1972" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1972" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1972" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1973">
-      <c r="A1973" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:13:00</t>
-        </is>
-      </c>
-      <c r="B1973" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。 環境を変える努力をしろ。 
@@ -58015,11 +57989,34 @@
 ・やるか死ぬかの状況</t>
         </is>
       </c>
+      <c r="C1972" t="n">
+        <v>54</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:15:26</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1973" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D1973" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E1973" t="inlineStr">
         <is>
@@ -58030,33 +58027,10 @@
     <row r="1974">
       <c r="A1974" t="inlineStr">
         <is>
-          <t>2026-06-11 09:15:26</t>
+          <t>2026-06-11 09:45:00</t>
         </is>
       </c>
       <c r="B1974" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1974" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1974" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1974" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1975">
-      <c r="A1975" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:45:00</t>
-        </is>
-      </c>
-      <c r="B1975" t="inlineStr">
         <is>
           <t>あなたがチー牛顔である理由 
 ・一重 
@@ -58070,48 +58044,48 @@
 ・体脂肪率20%以上</t>
         </is>
       </c>
+      <c r="C1974" t="n">
+        <v>280</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:48:30</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
+        </is>
+      </c>
       <c r="C1975" t="n">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="D1975" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E1975" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lunch</t>
         </is>
       </c>
     </row>
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>2026-06-11 09:48:30</t>
+          <t>2026-06-11 10:10:00</t>
         </is>
       </c>
       <c r="B1976" t="inlineStr">
-        <is>
-          <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
-        </is>
-      </c>
-      <c r="C1976" t="n">
-        <v>16</v>
-      </c>
-      <c r="D1976" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1976" t="inlineStr">
-        <is>
-          <t>lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="1977">
-      <c r="A1977" t="inlineStr">
-        <is>
-          <t>2026-06-11 10:10:00</t>
-        </is>
-      </c>
-      <c r="B1977" t="inlineStr">
         <is>
           <t>孤独でもメンタルを安定させる方法 
 男磨きは孤独との戦いになるので実践してほしい。
@@ -58125,25 +58099,25 @@
 むしろ人生はいい方向に進む。</t>
         </is>
       </c>
-      <c r="C1977" t="n">
+      <c r="C1976" t="n">
         <v>81</v>
       </c>
-      <c r="D1977" t="n">
+      <c r="D1976" t="n">
         <v>7</v>
       </c>
-      <c r="E1977" t="inlineStr">
+      <c r="E1976" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1978">
-      <c r="A1978" t="inlineStr">
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
         <is>
           <t>2026-06-11 10:37:00</t>
         </is>
       </c>
-      <c r="B1978" t="inlineStr">
+      <c r="B1977" t="inlineStr">
         <is>
           <t>スマホ断ちがあなたに与えるもの 
 ・思考力 
@@ -58157,59 +58131,82 @@
 SNSを受動的に見ることは百害あって一利なし。</t>
         </is>
       </c>
+      <c r="C1977" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-06-11 10:45:10</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1978" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D1978" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1978" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="1979">
       <c r="A1979" t="inlineStr">
         <is>
-          <t>2026-06-11 10:45:10</t>
+          <t>2026-06-11 11:26:00</t>
         </is>
       </c>
       <c r="B1979" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1979" t="n">
-        <v>3</v>
-      </c>
-      <c r="D1979" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1979" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1980">
-      <c r="A1980" t="inlineStr">
-        <is>
-          <t>2026-06-11 11:26:00</t>
-        </is>
-      </c>
-      <c r="B1980" t="inlineStr">
         <is>
           <t>男磨きのゴールは「俺は一生、セ◯クスに困らない」という自信を作ること。 
 この自信がモテ以外の人生の楽しみに集中させてくれる。 そして、余裕を生みさらにモテを生んでくれる。 
 だから、俺は「ブスでもBBAでもいいから片っ端からいけ」と言ってるのよ。</t>
         </is>
       </c>
+      <c r="C1979" t="n">
+        <v>70</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:30:28</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1980" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D1980" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1980" t="inlineStr">
         <is>
@@ -58220,33 +58217,10 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>2026-06-11 11:30:28</t>
+          <t>2026-06-12 08:50:00</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1981" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1981" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1982">
-      <c r="A1982" t="inlineStr">
-        <is>
-          <t>2026-06-12 08:50:00</t>
-        </is>
-      </c>
-      <c r="B1982" t="inlineStr">
         <is>
           <t>奥手な童貞の脳内  
 小学生時代 
@@ -58261,25 +58235,25 @@
 「昇進して女を見返すやで！」</t>
         </is>
       </c>
-      <c r="C1982" t="n">
+      <c r="C1981" t="n">
         <v>274</v>
       </c>
-      <c r="D1982" t="n">
+      <c r="D1981" t="n">
         <v>9</v>
       </c>
-      <c r="E1982" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1983">
-      <c r="A1983" t="inlineStr">
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
         <is>
           <t>2026-06-12 09:20:00</t>
         </is>
       </c>
-      <c r="B1983" t="inlineStr">
+      <c r="B1982" t="inlineStr">
         <is>
           <t>退化を促すドーパミン 
 ・悪口 
@@ -58297,11 +58271,34 @@
 ドーパミンを得る対象を変えるだけで、人生は変わる。</t>
         </is>
       </c>
+      <c r="C1982" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:41:33</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
+        </is>
+      </c>
       <c r="C1983" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D1983" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1983" t="inlineStr">
         <is>
@@ -58312,33 +58309,10 @@
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>2026-06-12 09:41:33</t>
+          <t>2026-06-12 10:00:02</t>
         </is>
       </c>
       <c r="B1984" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1984" t="n">
-        <v>6</v>
-      </c>
-      <c r="D1984" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:00:02</t>
-        </is>
-      </c>
-      <c r="B1985" t="inlineStr">
         <is>
           <t>非モテはいきなり本命に行くな。
 あなたが「俺でもイケるかも」と思っている女にさえ、チキってアプローチできない時点で無理です。 
@@ -58347,25 +58321,25 @@
 まずは男磨きをし、ブスとBBAを口説くことから始めてください。</t>
         </is>
       </c>
-      <c r="C1985" t="n">
+      <c r="C1984" t="n">
         <v>14</v>
       </c>
-      <c r="D1985" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1985" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1986">
-      <c r="A1986" t="inlineStr">
+      <c r="D1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
         <is>
           <t>2026-06-12 10:28:00</t>
         </is>
       </c>
-      <c r="B1986" t="inlineStr">
+      <c r="B1985" t="inlineStr">
         <is>
           <t>負け犬の遠吠え集 
 ・「独身貴族」 
@@ -58379,11 +58353,34 @@
 逆に素直に「うらやましい」「悔しい」が言える男は強い。</t>
         </is>
       </c>
+      <c r="C1985" t="n">
+        <v>28</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:40:53</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
+        </is>
+      </c>
       <c r="C1986" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D1986" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E1986" t="inlineStr">
         <is>
@@ -58394,16 +58391,16 @@
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>2026-06-12 10:40:53</t>
+          <t>2026-06-12 10:49:07</t>
         </is>
       </c>
       <c r="B1987" t="inlineStr">
         <is>
-          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
       <c r="C1987" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1987" t="n">
         <v>0</v>
@@ -58417,33 +58414,10 @@
     <row r="1988">
       <c r="A1988" t="inlineStr">
         <is>
-          <t>2026-06-12 10:49:07</t>
+          <t>2026-06-12 10:53:00</t>
         </is>
       </c>
       <c r="B1988" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
-        </is>
-      </c>
-      <c r="C1988" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1988" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:53:00</t>
-        </is>
-      </c>
-      <c r="B1989" t="inlineStr">
         <is>
           <t>決定疲れを減らす方法 
 ・デスクの整理 
@@ -58455,36 +58429,60 @@
 これで大事なタスクへの火力が爆上がりします。</t>
         </is>
       </c>
-      <c r="C1989" t="n">
+      <c r="C1988" t="n">
         <v>15</v>
       </c>
-      <c r="D1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1989" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
+      <c r="D1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
         <is>
           <t>2026-06-12 11:17:04</t>
         </is>
       </c>
-      <c r="B1990" t="inlineStr">
+      <c r="B1989" t="inlineStr">
         <is>
           <t>男の人生はシンプル。
 唸るほど金を持ち、ジムに行き、女行き倒す。
 他の事はどうでもいい。 https://t.co/9LrSQYOjXd</t>
         </is>
       </c>
+      <c r="C1989" t="n">
+        <v>77</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:46:23</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
+無料で空気を吸った方がコスパいい。</t>
+        </is>
+      </c>
       <c r="C1990" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="D1990" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1990" t="inlineStr">
         <is>
@@ -58495,34 +58493,10 @@
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>2026-06-12 11:46:23</t>
+          <t>2026-06-12 12:00:00</t>
         </is>
       </c>
       <c r="B1991" t="inlineStr">
-        <is>
-          <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
-無料で空気を吸った方がコスパいい。</t>
-        </is>
-      </c>
-      <c r="C1991" t="n">
-        <v>19</v>
-      </c>
-      <c r="D1991" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1991" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
-        <is>
-          <t>2026-06-12 12:00:00</t>
-        </is>
-      </c>
-      <c r="B1992" t="inlineStr">
         <is>
           <t>疲れているのに眠れない原因 
 ①反芻思考 
@@ -58534,50 +58508,50 @@
 まずは原因を分析するところから始めよう。</t>
         </is>
       </c>
-      <c r="C1992" t="n">
+      <c r="C1991" t="n">
         <v>11</v>
       </c>
-      <c r="D1992" t="n">
+      <c r="D1991" t="n">
         <v>1</v>
       </c>
-      <c r="E1992" t="inlineStr">
+      <c r="E1991" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-12 12:32:00</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>睡眠の質を測るために、昔はスマートウォッチつけて寝てたけどやめちゃったな。
 理由はゴツゴツしてて睡眠の邪魔になっていたのと、別に計測したからといって質が上がるわけではないから。
 ”翌日のパフォーマンスが向上しているか”という体感こそがエビデンスだと思っています。</t>
         </is>
       </c>
-      <c r="C1993" t="n">
+      <c r="C1992" t="n">
         <v>7</v>
       </c>
-      <c r="D1993" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1993" t="inlineStr">
+      <c r="D1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1992" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1994">
-      <c r="A1994" t="inlineStr">
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
         <is>
           <t>2026-06-12 21:47:00</t>
         </is>
       </c>
-      <c r="B1994" t="inlineStr">
+      <c r="B1993" t="inlineStr">
         <is>
           <t>朝の水分補給は、ただの真水では睡眠中に失った電解質は取り戻せない。 
 また、電解質が入っていないと飲んだ水が身体に行き届きにくくなる。 
@@ -58585,25 +58559,25 @@
 もしこれが不味くて飲めないなら、「みそ汁」「コーンスープ」「電解質パウダー」でもOK</t>
         </is>
       </c>
-      <c r="C1994" t="n">
+      <c r="C1993" t="n">
         <v>21</v>
       </c>
-      <c r="D1994" t="n">
+      <c r="D1993" t="n">
         <v>2</v>
       </c>
-      <c r="E1994" t="inlineStr">
+      <c r="E1993" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
         <is>
           <t>2026-06-13 07:32:34</t>
         </is>
       </c>
-      <c r="B1995" t="inlineStr">
+      <c r="B1994" t="inlineStr">
         <is>
           <t>スマホ依存症を治すために私がやったこと 
 ・スマホなし1時間散歩 
@@ -58616,25 +58590,25 @@
 そして、SNSを全部PCに移せば、スマホを使う理由は少なくなる。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
+      <c r="C1994" t="n">
         <v>82</v>
       </c>
-      <c r="D1995" t="n">
+      <c r="D1994" t="n">
         <v>4</v>
       </c>
-      <c r="E1995" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-13 08:27:00</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>非モテがチン騎士になる理由。  
 結論、それ以外の関わり方を知らないから。 
@@ -58643,25 +58617,25 @@
 優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
         </is>
       </c>
-      <c r="C1996" t="n">
+      <c r="C1995" t="n">
         <v>57</v>
       </c>
-      <c r="D1996" t="n">
+      <c r="D1995" t="n">
         <v>1</v>
       </c>
-      <c r="E1996" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-13 09:00:01</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>スマホ依存症の症状 
 ・起きた瞬間にチェック 
@@ -58677,25 +58651,25 @@
 ・21時以降は見ない</t>
         </is>
       </c>
-      <c r="C1997" t="n">
+      <c r="C1996" t="n">
         <v>16</v>
       </c>
-      <c r="D1997" t="n">
+      <c r="D1996" t="n">
         <v>2</v>
       </c>
-      <c r="E1997" t="inlineStr">
+      <c r="E1996" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-13 09:21:45</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>自己満男磨き(笑)と呼ばれている習慣を擁護します。  
 【オナ禁】
@@ -58726,25 +58700,25 @@
 正しく評価して自分に落とし込むことが重要。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
+      <c r="C1997" t="n">
         <v>10</v>
       </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-13 09:28:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>口呼吸が習慣化している人の特徴 
 ①舌が白い 
@@ -58755,25 +58729,25 @@
 高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
+      <c r="C1998" t="n">
         <v>26</v>
       </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-13 10:06:00</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58787,11 +58761,34 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
+      <c r="C1999" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:00:02</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+        </is>
+      </c>
       <c r="C2000" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D2000" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2000" t="inlineStr">
         <is>
@@ -58802,19 +58799,19 @@
     <row r="2001">
       <c r="A2001" t="inlineStr">
         <is>
-          <t>2026-06-13 11:00:02</t>
+          <t>2026-06-13 11:17:03</t>
         </is>
       </c>
       <c r="B2001" t="inlineStr">
         <is>
-          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C2001" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D2001" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2001" t="inlineStr">
         <is>
@@ -58825,33 +58822,10 @@
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>2026-06-13 11:17:03</t>
+          <t>2026-06-13 12:26:00</t>
         </is>
       </c>
       <c r="B2002" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C2002" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
-        <is>
-          <t>2026-06-13 12:26:00</t>
-        </is>
-      </c>
-      <c r="B2003" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58863,25 +58837,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
+      <c r="C2002" t="n">
         <v>16</v>
       </c>
-      <c r="D2003" t="n">
+      <c r="D2002" t="n">
         <v>1</v>
       </c>
-      <c r="E2003" t="inlineStr">
+      <c r="E2002" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58892,25 +58866,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
+      <c r="C2003" t="n">
         <v>19</v>
       </c>
-      <c r="D2004" t="n">
+      <c r="D2003" t="n">
         <v>2</v>
       </c>
-      <c r="E2004" t="inlineStr">
+      <c r="E2003" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58922,25 +58896,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
+      <c r="C2004" t="n">
         <v>19</v>
       </c>
-      <c r="D2005" t="n">
+      <c r="D2004" t="n">
         <v>2</v>
       </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -58957,25 +58931,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
+      <c r="C2005" t="n">
         <v>22</v>
       </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -58991,25 +58965,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
+      <c r="C2006" t="n">
         <v>17</v>
       </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -59022,8 +58996,31 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
+      <c r="C2007" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:07:02</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
+        </is>
+      </c>
       <c r="C2008" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2008" t="n">
         <v>0</v>
@@ -59037,33 +59034,10 @@
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>2026-06-14 09:07:02</t>
+          <t>2026-06-14 09:31:00</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
-        </is>
-      </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
-        <is>
-          <t>2026-06-14 09:31:00</t>
-        </is>
-      </c>
-      <c r="B2010" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -59079,25 +59053,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -59107,25 +59081,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -59137,25 +59111,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -59167,25 +59141,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -59199,25 +59173,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -59234,25 +59208,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -59262,25 +59236,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -59294,25 +59268,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -59322,25 +59296,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -59351,25 +59325,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -59382,25 +59356,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59410,25 +59384,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59437,25 +59411,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59463,6 +59437,30 @@
 地味なライフハック。</t>
         </is>
       </c>
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:41:41</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>起床3秒後のEAA❌
+起床3秒後の歯磨き⭕</t>
+        </is>
+      </c>
       <c r="C2023" t="n">
         <v>0</v>
       </c>
@@ -59478,34 +59476,10 @@
     <row r="2024">
       <c r="A2024" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-21 07:01:00</t>
         </is>
       </c>
       <c r="B2024" t="inlineStr">
-        <is>
-          <t>起床3秒後のEAA❌
-起床3秒後の歯磨き⭕</t>
-        </is>
-      </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:01:00</t>
-        </is>
-      </c>
-      <c r="B2025" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59518,25 +59492,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59546,6 +59520,29 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:03:13</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+        </is>
+      </c>
       <c r="C2026" t="n">
         <v>0</v>
       </c>
@@ -59561,12 +59558,13 @@
     <row r="2027">
       <c r="A2027" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-19 19:34:04</t>
         </is>
       </c>
       <c r="B2027" t="inlineStr">
         <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
       <c r="C2027" t="n">
@@ -59584,34 +59582,10 @@
     <row r="2028">
       <c r="A2028" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B2028" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B2029" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59619,31 +59593,54 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:46</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
+        </is>
+      </c>
       <c r="C2030" t="n">
         <v>0</v>
       </c>
@@ -59659,33 +59656,10 @@
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>2026-06-16 18:11:46</t>
+          <t>2026-06-16 06:56:00</t>
         </is>
       </c>
       <c r="B2031" t="inlineStr">
-        <is>
-          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
-        </is>
-      </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:56:00</t>
-        </is>
-      </c>
-      <c r="B2032" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59700,25 +59674,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59729,25 +59703,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2033" t="inlineStr">
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59755,25 +59729,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="C2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59788,25 +59762,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59817,25 +59791,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59847,25 +59821,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59875,25 +59849,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59901,25 +59875,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59930,25 +59904,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59961,25 +59935,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59987,25 +59961,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -60017,25 +59991,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -60043,25 +60017,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -60076,25 +60050,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -60105,25 +60079,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -60140,25 +60114,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -60174,6 +60148,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2047" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2048" t="n">
         <v>0</v>
       </c>
@@ -60183,45 +60186,16 @@
       <c r="E2048" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2048" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2049" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2050" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -60249,25 +60223,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="C2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -60279,25 +60253,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="C2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -60310,25 +60284,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="C2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -60339,25 +60313,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="C2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -60365,25 +60339,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="C2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -60393,30 +60367,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2055" t="inlineStr">
+      <c r="C2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2054" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60427,30 +60401,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2056" t="inlineStr">
+      <c r="C2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2055" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60460,30 +60434,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2057" t="inlineStr">
+      <c r="C2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2056" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60496,30 +60470,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2058" t="inlineStr">
+      <c r="C2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2057" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60530,55 +60504,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="C2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2060" t="inlineStr">
+      <c r="C2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2059" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60591,25 +60565,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="C2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60620,25 +60594,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60649,25 +60623,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60676,19 +60650,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60705,19 +60679,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60730,19 +60704,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60754,19 +60728,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60775,19 +60749,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60800,19 +60774,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60823,19 +60797,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60847,19 +60821,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60868,19 +60842,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60899,24 +60873,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2073" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2072" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60928,19 +60902,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60955,19 +60929,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60981,19 +60955,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -61004,19 +60978,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -61026,38 +61000,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -61066,19 +61040,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -61090,19 +61064,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-07-24 12:00:00</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>マチアプはあなたの恋愛市場価値を測るための試金石。
 【上位1%】
@@ -61124,25 +61098,25 @@
 俺が変われたのは、チー牛時代にマチアプで惨敗して現実を知ったから。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -61152,19 +61126,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -61178,19 +61152,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -61208,24 +61182,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2085" t="inlineStr">
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2084" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -61236,24 +61210,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2086" t="inlineStr">
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2085" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -61263,24 +61237,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2087" t="inlineStr">
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2086" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -61289,19 +61263,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -61315,19 +61289,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -61340,19 +61314,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -61365,19 +61339,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61391,19 +61365,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61424,19 +61398,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61444,19 +61418,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61464,19 +61438,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61486,19 +61460,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61507,19 +61481,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61533,25 +61507,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61565,30 +61539,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2099" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2098" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61601,25 +61575,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61634,25 +61608,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61665,25 +61639,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61693,25 +61667,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61725,25 +61699,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61766,25 +61740,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61793,25 +61767,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61826,25 +61800,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61861,25 +61835,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61890,25 +61864,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61926,25 +61900,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61957,25 +61931,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61986,6 +61960,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2112" t="n">
         <v>0</v>
       </c>
@@ -62005,29 +62002,6 @@
         </is>
       </c>
       <c r="B2113" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2114" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -62046,25 +62020,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -62080,25 +62054,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -62110,25 +62084,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="C2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -62138,25 +62112,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="C2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -62168,25 +62142,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="C2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -62196,25 +62170,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="C2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -62236,25 +62210,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="C2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -62268,30 +62242,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2121" t="inlineStr">
+      <c r="C2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2120" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -62303,25 +62277,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="C2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -62332,25 +62306,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="C2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62386,25 +62360,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62416,25 +62390,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62450,25 +62424,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62480,25 +62454,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62527,50 +62501,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="C2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="C2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62585,25 +62559,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="C2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62614,25 +62588,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="C2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62650,19 +62624,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62683,19 +62657,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62707,19 +62681,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62731,19 +62705,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62754,19 +62728,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62780,19 +62754,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62804,19 +62778,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62829,19 +62803,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62857,19 +62831,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62887,19 +62861,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62913,19 +62887,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62937,19 +62911,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62962,19 +62936,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62985,19 +62959,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -63006,19 +62980,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -63028,19 +63002,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -63052,19 +63026,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2148" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -63079,19 +63053,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2149" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2149" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -63104,19 +63078,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2150" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2151">
-      <c r="A2151" t="inlineStr">
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2150" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -63129,19 +63103,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2151" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2152">
-      <c r="A2152" t="inlineStr">
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2152" t="inlineStr">
+      <c r="B2151" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -63157,19 +63131,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2152" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2153">
-      <c r="A2153" t="inlineStr">
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2152" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -63186,19 +63160,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2153" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2154">
-      <c r="A2154" t="inlineStr">
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2153" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -63211,19 +63185,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2154" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2155">
-      <c r="A2155" t="inlineStr">
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2154" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -63233,19 +63207,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2155" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2156">
-      <c r="A2156" t="inlineStr">
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2155" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -63256,19 +63230,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2156" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2157">
-      <c r="A2157" t="inlineStr">
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2157" t="inlineStr">
+      <c r="B2156" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -63281,19 +63255,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2157" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2158">
-      <c r="A2158" t="inlineStr">
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2157" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -63309,19 +63283,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2158" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2159">
-      <c r="A2159" t="inlineStr">
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2159" t="inlineStr">
+      <c r="B2158" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -63336,19 +63310,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2159" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2160">
-      <c r="A2160" t="inlineStr">
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2160" t="inlineStr">
+      <c r="B2159" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -63365,7 +63339,7 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2160" t="inlineStr">
+      <c r="E2159" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2159"/>
+  <dimension ref="A1:G2154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56938,33 +56938,10 @@
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>2026-06-08 02:45:52</t>
+          <t>2026-06-08 03:03:37</t>
         </is>
       </c>
       <c r="B1935" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/LF4G9gUM7D</t>
-        </is>
-      </c>
-      <c r="C1935" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1935" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1935" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1936">
-      <c r="A1936" t="inlineStr">
-        <is>
-          <t>2026-06-08 03:03:37</t>
-        </is>
-      </c>
-      <c r="B1936" t="inlineStr">
         <is>
           <t>地味にQOLを上げる方法
 ・歯ブラシ
@@ -56975,25 +56952,25 @@
 いつも使う物に少し金払うだけで、QOLは上がる。</t>
         </is>
       </c>
-      <c r="C1936" t="n">
+      <c r="C1935" t="n">
         <v>66</v>
       </c>
-      <c r="D1936" t="n">
+      <c r="D1935" t="n">
         <v>5</v>
       </c>
-      <c r="E1936" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1937">
-      <c r="A1937" t="inlineStr">
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
         <is>
           <t>2026-06-08 07:49:00</t>
         </is>
       </c>
-      <c r="B1937" t="inlineStr">
+      <c r="B1936" t="inlineStr">
         <is>
           <t>睡眠不足で筋トレしても意味ない 
 ・筋肉は寝てる間に成長する 
@@ -57003,25 +56980,25 @@
 まずは寝ろ。</t>
         </is>
       </c>
-      <c r="C1937" t="n">
+      <c r="C1936" t="n">
         <v>33</v>
       </c>
-      <c r="D1937" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1937" t="inlineStr">
+      <c r="D1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1936" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1938">
-      <c r="A1938" t="inlineStr">
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
         <is>
           <t>2026-06-08 08:43:00</t>
         </is>
       </c>
-      <c r="B1938" t="inlineStr">
+      <c r="B1937" t="inlineStr">
         <is>
           <t>”極振り”が人生を変える。
 女攻略したいなら
@@ -57033,25 +57010,25 @@
 俺はこの極振りでコンプを克服してきた。</t>
         </is>
       </c>
-      <c r="C1938" t="n">
+      <c r="C1937" t="n">
         <v>113</v>
       </c>
-      <c r="D1938" t="n">
+      <c r="D1937" t="n">
         <v>10</v>
       </c>
-      <c r="E1938" t="inlineStr">
+      <c r="E1937" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1939">
-      <c r="A1939" t="inlineStr">
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
         <is>
           <t>2026-06-08 09:14:00</t>
         </is>
       </c>
-      <c r="B1939" t="inlineStr">
+      <c r="B1938" t="inlineStr">
         <is>
           <t>童貞は
 ・身長10cm盛る
@@ -57062,25 +57039,25 @@
 「俺のち〇こを必要としている人はいる」という自信にはなる。</t>
         </is>
       </c>
-      <c r="C1939" t="n">
+      <c r="C1938" t="n">
         <v>158</v>
       </c>
-      <c r="D1939" t="n">
+      <c r="D1938" t="n">
         <v>6</v>
       </c>
-      <c r="E1939" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1940">
-      <c r="A1940" t="inlineStr">
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
         <is>
           <t>2026-06-08 10:00:01</t>
         </is>
       </c>
-      <c r="B1940" t="inlineStr">
+      <c r="B1939" t="inlineStr">
         <is>
           <t>「チー牛家庭」の問題点。
 ・食事から教育方針まで、すべて母親が決める 
@@ -57091,25 +57068,25 @@
 はしごを外され、決断力を育ててこなかった</t>
         </is>
       </c>
-      <c r="C1940" t="n">
+      <c r="C1939" t="n">
         <v>32</v>
       </c>
-      <c r="D1940" t="n">
+      <c r="D1939" t="n">
         <v>1</v>
       </c>
-      <c r="E1940" t="inlineStr">
+      <c r="E1939" t="inlineStr">
         <is>
           <t>exam</t>
         </is>
       </c>
     </row>
-    <row r="1941">
-      <c r="A1941" t="inlineStr">
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
         <is>
           <t>2026-06-08 10:41:00</t>
         </is>
       </c>
-      <c r="B1941" t="inlineStr">
+      <c r="B1940" t="inlineStr">
         <is>
           <t>正直、学生時代に”イジメすらもされないような陰キャ”だった方がSNSやマチアプで人気者になるのは厳しい。 
 これらはあくまで拡声器。 
@@ -57117,25 +57094,25 @@
 やることは自己啓発陰キャになり、自分本体をひたすら磨くこと。</t>
         </is>
       </c>
-      <c r="C1941" t="n">
+      <c r="C1940" t="n">
         <v>53</v>
       </c>
-      <c r="D1941" t="n">
+      <c r="D1940" t="n">
         <v>4</v>
       </c>
-      <c r="E1941" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1942">
-      <c r="A1942" t="inlineStr">
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
         <is>
           <t>2026-06-08 11:09:00</t>
         </is>
       </c>
-      <c r="B1942" t="inlineStr">
+      <c r="B1941" t="inlineStr">
         <is>
           <t>スマホ中毒がデフォルトの時代。 
 そこを脱して「静寂」を手に入れた人間は、
@@ -57143,8 +57120,31 @@
 周りが耽溺している間に、あなたは淡々とリアルな成果を積み上げる側へ回れ。</t>
         </is>
       </c>
+      <c r="C1941" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:14:05</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1942" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D1942" t="n">
         <v>1</v>
@@ -57158,33 +57158,10 @@
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>2026-06-08 11:14:05</t>
+          <t>2026-06-08 12:00:01</t>
         </is>
       </c>
       <c r="B1943" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1943" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1943" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1943" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1944">
-      <c r="A1944" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:00:01</t>
-        </is>
-      </c>
-      <c r="B1944" t="inlineStr">
         <is>
           <t>睡眠を削ると時間が減る。
 判断力低下
@@ -57197,25 +57174,25 @@
 睡眠を削るのは「ここぞ」という時だけでいい。</t>
         </is>
       </c>
-      <c r="C1944" t="n">
+      <c r="C1943" t="n">
         <v>29</v>
       </c>
-      <c r="D1944" t="n">
+      <c r="D1943" t="n">
         <v>1</v>
       </c>
-      <c r="E1944" t="inlineStr">
+      <c r="E1943" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1945">
-      <c r="A1945" t="inlineStr">
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
         <is>
           <t>2026-06-09 07:28:00</t>
         </is>
       </c>
-      <c r="B1945" t="inlineStr">
+      <c r="B1944" t="inlineStr">
         <is>
           <t>モテる男は周りから固めていく。
 まず本命の友達から評価を得てクチコミを広める。
@@ -57223,25 +57200,25 @@
 逆に非モテはガンギマリで女にピンポイントで、くそきもアプローチだけする。</t>
         </is>
       </c>
-      <c r="C1945" t="n">
+      <c r="C1944" t="n">
         <v>23</v>
       </c>
-      <c r="D1945" t="n">
+      <c r="D1944" t="n">
         <v>2</v>
       </c>
-      <c r="E1945" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1946">
-      <c r="A1946" t="inlineStr">
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
         <is>
           <t>2026-06-09 08:06:00</t>
         </is>
       </c>
-      <c r="B1946" t="inlineStr">
+      <c r="B1945" t="inlineStr">
         <is>
           <t>3日坊主の奴はSNSを見すぎ。
 他人の投稿ばかり見て、隣の芝生が青く見えるがゆえ、やることがブレている。
@@ -57250,25 +57227,25 @@
 フォローは厳選している。</t>
         </is>
       </c>
-      <c r="C1946" t="n">
+      <c r="C1945" t="n">
         <v>22</v>
       </c>
-      <c r="D1946" t="n">
+      <c r="D1945" t="n">
         <v>1</v>
       </c>
-      <c r="E1946" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1947">
-      <c r="A1947" t="inlineStr">
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
         <is>
           <t>2026-06-09 08:50:00</t>
         </is>
       </c>
-      <c r="B1947" t="inlineStr">
+      <c r="B1946" t="inlineStr">
         <is>
           <t>テストステロンを1日で取り戻す方法 
 ・8時間睡眠 
@@ -57284,25 +57261,25 @@
 翌日には余裕で回復してる。</t>
         </is>
       </c>
-      <c r="C1947" t="n">
+      <c r="C1946" t="n">
         <v>953</v>
       </c>
-      <c r="D1947" t="n">
+      <c r="D1946" t="n">
         <v>66</v>
       </c>
-      <c r="E1947" t="inlineStr">
+      <c r="E1946" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1948">
-      <c r="A1948" t="inlineStr">
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
         <is>
           <t>2026-06-09 09:30:00</t>
         </is>
       </c>
-      <c r="B1948" t="inlineStr">
+      <c r="B1947" t="inlineStr">
         <is>
           <t>・「ヒョロガリがフリーウェイト使うのは申し訳ない。」 
 ・「インターバル3分も取るのは気まずい。」 
@@ -57312,8 +57289,31 @@
 そして、あなたも他の会員と同じ額の会費を払ってます。</t>
         </is>
       </c>
+      <c r="C1947" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:43:52</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
+        </is>
+      </c>
       <c r="C1948" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D1948" t="n">
         <v>0</v>
@@ -57327,56 +57327,10 @@
     <row r="1949">
       <c r="A1949" t="inlineStr">
         <is>
-          <t>2026-06-09 09:43:01</t>
+          <t>2026-06-09 10:06:00</t>
         </is>
       </c>
       <c r="B1949" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/qLJDnfITgQ</t>
-        </is>
-      </c>
-      <c r="C1949" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1949" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1949" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1950">
-      <c r="A1950" t="inlineStr">
-        <is>
-          <t>2026-06-09 09:43:52</t>
-        </is>
-      </c>
-      <c r="B1950" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1950" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1950" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1950" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1951">
-      <c r="A1951" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:06:00</t>
-        </is>
-      </c>
-      <c r="B1951" t="inlineStr">
         <is>
           <t>受け身な男の脳内  
 小学生時代 
@@ -57391,50 +57345,50 @@
 「出世出来たら結婚出来るんだろうなぁ」</t>
         </is>
       </c>
-      <c r="C1951" t="n">
+      <c r="C1949" t="n">
         <v>84</v>
       </c>
-      <c r="D1951" t="n">
+      <c r="D1949" t="n">
         <v>6</v>
       </c>
-      <c r="E1951" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1952">
-      <c r="A1952" t="inlineStr">
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
         <is>
           <t>2026-06-09 10:12:00</t>
         </is>
       </c>
-      <c r="B1952" t="inlineStr">
+      <c r="B1950" t="inlineStr">
         <is>
           <t>スマホ中毒者は自分だけの「対策ノウハウ」を作っていけ。
 確かにタイムロック、瞑想等は効果はあるが単なるテクニック論に過ぎない。
 自分の癖を見つけて、ピンポイントで対策する方が効果的。</t>
         </is>
       </c>
-      <c r="C1952" t="n">
+      <c r="C1950" t="n">
         <v>19</v>
       </c>
-      <c r="D1952" t="n">
+      <c r="D1950" t="n">
         <v>2</v>
       </c>
-      <c r="E1952" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1953">
-      <c r="A1953" t="inlineStr">
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
         <is>
           <t>2026-06-09 10:48:00</t>
         </is>
       </c>
-      <c r="B1953" t="inlineStr">
+      <c r="B1951" t="inlineStr">
         <is>
           <t>非モテのコミュニケーション悪癖 
 ・名前を呼べない 
@@ -57449,25 +57403,25 @@
 2つ以上当てはまれば、キモがれらている可能性大。</t>
         </is>
       </c>
-      <c r="C1953" t="n">
+      <c r="C1951" t="n">
         <v>54</v>
       </c>
-      <c r="D1953" t="n">
+      <c r="D1951" t="n">
         <v>6</v>
       </c>
-      <c r="E1953" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1954">
-      <c r="A1954" t="inlineStr">
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
         <is>
           <t>2026-06-09 11:20:00</t>
         </is>
       </c>
-      <c r="B1954" t="inlineStr">
+      <c r="B1952" t="inlineStr">
         <is>
           <t>モテテクは結果論。 
 ・返信を遅らせる 
@@ -57477,49 +57431,49 @@
 確かに非モテのモテテク武装は大事。 だから無意味ではないが、 結果論であることを理解した上で使った方がいい。</t>
         </is>
       </c>
-      <c r="C1954" t="n">
+      <c r="C1952" t="n">
         <v>20</v>
       </c>
-      <c r="D1954" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1954" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1955">
-      <c r="A1955" t="inlineStr">
+      <c r="D1952" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
         <is>
           <t>2026-06-09 11:30:00</t>
         </is>
       </c>
-      <c r="B1955" t="inlineStr">
+      <c r="B1953" t="inlineStr">
         <is>
           <t>筋トレをやらない理由はない。 
 毎朝、鏡でユニセフのア〇ガキ体型の自分を見るか。 それとも、デカい肩幅と引き締まったウェストを見るか。 両者で1日のテンションは全然違う。 自信は意外とこういう所から来る。</t>
         </is>
       </c>
-      <c r="C1955" t="n">
+      <c r="C1953" t="n">
         <v>22</v>
       </c>
-      <c r="D1955" t="n">
+      <c r="D1953" t="n">
         <v>1</v>
       </c>
-      <c r="E1955" t="inlineStr">
+      <c r="E1953" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1956">
-      <c r="A1956" t="inlineStr">
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
         <is>
           <t>2026-06-10 07:40:00</t>
         </is>
       </c>
-      <c r="B1956" t="inlineStr">
+      <c r="B1954" t="inlineStr">
         <is>
           <t>スマホが近くにあるだけで頭が悪くなる。
 脳が「スマホを無視しろ」とコマンドを送るのにリソースを割くからです。
@@ -57528,25 +57482,25 @@
 物理的な距離だけがあなたの脳を解放します。</t>
         </is>
       </c>
-      <c r="C1956" t="n">
+      <c r="C1954" t="n">
         <v>15</v>
       </c>
-      <c r="D1956" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1956" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1957">
-      <c r="A1957" t="inlineStr">
+      <c r="D1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
         <is>
           <t>2026-06-10 08:23:00</t>
         </is>
       </c>
-      <c r="B1957" t="inlineStr">
+      <c r="B1955" t="inlineStr">
         <is>
           <t>一番、結果が出るのはコンフォートゾーンでガチガチにハメ技決めてる時。
 ・毎日、同じ食事を摂る
@@ -57556,25 +57510,25 @@
 「つまらない」と感じると思うが、いちいち新しいことを始める必要はない。君の努力は正しい。</t>
         </is>
       </c>
-      <c r="C1957" t="n">
+      <c r="C1955" t="n">
         <v>45</v>
       </c>
-      <c r="D1957" t="n">
+      <c r="D1955" t="n">
         <v>5</v>
       </c>
-      <c r="E1957" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1958">
-      <c r="A1958" t="inlineStr">
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
         <is>
           <t>2026-06-10 08:42:00</t>
         </is>
       </c>
-      <c r="B1958" t="inlineStr">
+      <c r="B1956" t="inlineStr">
         <is>
           <t>ストイックには2種類ある。  
 ・サボらない努力マシーン 
@@ -57584,25 +57538,25 @@
 そして、翌日には何事もなかったようにルーティンに戻る。</t>
         </is>
       </c>
-      <c r="C1958" t="n">
+      <c r="C1956" t="n">
         <v>31</v>
       </c>
-      <c r="D1958" t="n">
+      <c r="D1956" t="n">
         <v>5</v>
       </c>
-      <c r="E1958" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1959">
-      <c r="A1959" t="inlineStr">
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
         <is>
           <t>2026-06-10 09:20:00</t>
         </is>
       </c>
-      <c r="B1959" t="inlineStr">
+      <c r="B1957" t="inlineStr">
         <is>
           <t>筋トレで得たもの 
 ・自信 
@@ -57617,25 +57571,25 @@
 やらない理由がない。</t>
         </is>
       </c>
-      <c r="C1959" t="n">
+      <c r="C1957" t="n">
         <v>59</v>
       </c>
-      <c r="D1959" t="n">
+      <c r="D1957" t="n">
         <v>4</v>
       </c>
-      <c r="E1959" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1960">
-      <c r="A1960" t="inlineStr">
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
         <is>
           <t>2026-06-10 09:36:00</t>
         </is>
       </c>
-      <c r="B1960" t="inlineStr">
+      <c r="B1958" t="inlineStr">
         <is>
           <t>ヒョロガリのマインド
 「ハイTな食事🤓（2300kcal）」
@@ -57647,25 +57601,25 @@
 黙って食え。</t>
         </is>
       </c>
-      <c r="C1960" t="n">
+      <c r="C1958" t="n">
         <v>47</v>
       </c>
-      <c r="D1960" t="n">
+      <c r="D1958" t="n">
         <v>1</v>
       </c>
-      <c r="E1960" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1961">
-      <c r="A1961" t="inlineStr">
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
         <is>
           <t>2026-06-10 10:00:00</t>
         </is>
       </c>
-      <c r="B1961" t="inlineStr">
+      <c r="B1959" t="inlineStr">
         <is>
           <t>自信がない奴の特徴 
 ・姿勢が悪い 
@@ -57682,25 +57636,25 @@
 俺は筋トレで体を変えてから自信がついた。</t>
         </is>
       </c>
-      <c r="C1961" t="n">
+      <c r="C1959" t="n">
         <v>58</v>
       </c>
-      <c r="D1961" t="n">
+      <c r="D1959" t="n">
         <v>5</v>
       </c>
-      <c r="E1961" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1962">
-      <c r="A1962" t="inlineStr">
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
         <is>
           <t>2026-06-10 10:45:00</t>
         </is>
       </c>
-      <c r="B1962" t="inlineStr">
+      <c r="B1960" t="inlineStr">
         <is>
           <t>スマホ中毒の唯一の基準は
 「目標達成を妨げているか否か」。
@@ -57711,48 +57665,25 @@
 スクリーンタイムよりも使い方を見直せ。</t>
         </is>
       </c>
-      <c r="C1962" t="n">
+      <c r="C1960" t="n">
         <v>25</v>
       </c>
-      <c r="D1962" t="n">
+      <c r="D1960" t="n">
         <v>4</v>
       </c>
-      <c r="E1962" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1963">
-      <c r="A1963" t="inlineStr">
-        <is>
-          <t>2026-06-10 10:49:46</t>
-        </is>
-      </c>
-      <c r="B1963" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/unoeq1hcNE</t>
-        </is>
-      </c>
-      <c r="C1963" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1963" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1963" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1964">
-      <c r="A1964" t="inlineStr">
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
         <is>
           <t>2026-06-10 11:00:03</t>
         </is>
       </c>
-      <c r="B1964" t="inlineStr">
+      <c r="B1961" t="inlineStr">
         <is>
           <t>男磨きしている人が陥りがちな失敗は「禁欲の目的化」。
 確かにオナ禁、コールドシャワー、瞑想といった習慣はスピではなく、科学的根拠がある。
@@ -57760,25 +57691,25 @@
 あくまで廃人が自己管理能力を上げる手段でしかない。</t>
         </is>
       </c>
-      <c r="C1964" t="n">
+      <c r="C1961" t="n">
         <v>46</v>
       </c>
-      <c r="D1964" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1964" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1965">
-      <c r="A1965" t="inlineStr">
+      <c r="D1961" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
         <is>
           <t>2026-06-10 11:29:00</t>
         </is>
       </c>
-      <c r="B1965" t="inlineStr">
+      <c r="B1962" t="inlineStr">
         <is>
           <t>一般的な弱者男性の日常。
 平日は経営者のために働き、上司と得意先に頭を下げる。帰宅後は推しの配信で時間を潰す。 
@@ -57788,25 +57719,25 @@
 哲学的ゾンビとはこのこと。</t>
         </is>
       </c>
-      <c r="C1965" t="n">
+      <c r="C1962" t="n">
         <v>44</v>
       </c>
-      <c r="D1965" t="n">
+      <c r="D1962" t="n">
         <v>6</v>
       </c>
-      <c r="E1965" t="inlineStr">
+      <c r="E1962" t="inlineStr">
         <is>
           <t>sunday</t>
         </is>
       </c>
     </row>
-    <row r="1966">
-      <c r="A1966" t="inlineStr">
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
         <is>
           <t>2026-06-10 12:06:00</t>
         </is>
       </c>
-      <c r="B1966" t="inlineStr">
+      <c r="B1963" t="inlineStr">
         <is>
           <t>睡眠を30分削ると、 
 ・テストステロン低下 
@@ -57819,25 +57750,25 @@
 そして、翌朝はアラーム無しで起きる奴こそが強者。</t>
         </is>
       </c>
-      <c r="C1966" t="n">
+      <c r="C1963" t="n">
         <v>27</v>
       </c>
-      <c r="D1966" t="n">
+      <c r="D1963" t="n">
         <v>4</v>
       </c>
-      <c r="E1966" t="inlineStr">
+      <c r="E1963" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1967">
-      <c r="A1967" t="inlineStr">
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
         <is>
           <t>2026-06-11 06:18:00</t>
         </is>
       </c>
-      <c r="B1967" t="inlineStr">
+      <c r="B1964" t="inlineStr">
         <is>
           <t>弱者男性の先天的欠点
 ・短足
@@ -57853,25 +57784,25 @@
 複数当てはまると、結構人生ハードモード。</t>
         </is>
       </c>
-      <c r="C1967" t="n">
+      <c r="C1964" t="n">
         <v>38</v>
       </c>
-      <c r="D1967" t="n">
+      <c r="D1964" t="n">
         <v>2</v>
       </c>
-      <c r="E1967" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1968">
-      <c r="A1968" t="inlineStr">
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
         <is>
           <t>2026-06-11 06:29:00</t>
         </is>
       </c>
-      <c r="B1968" t="inlineStr">
+      <c r="B1965" t="inlineStr">
         <is>
           <t>ヒョロガリは週3回、BIG3をそれぞれやるだけで十分全身を鍛えられる。
 5分割で2時間は多分、続かない。
@@ -57879,25 +57810,25 @@
 週3は忙しくても行ける。</t>
         </is>
       </c>
-      <c r="C1968" t="n">
+      <c r="C1965" t="n">
         <v>36</v>
       </c>
-      <c r="D1968" t="n">
+      <c r="D1965" t="n">
         <v>1</v>
       </c>
-      <c r="E1968" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1969">
-      <c r="A1969" t="inlineStr">
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
         <is>
           <t>2026-06-11 08:44:00</t>
         </is>
       </c>
-      <c r="B1969" t="inlineStr">
+      <c r="B1966" t="inlineStr">
         <is>
           <t>俺が童貞(20歳)に戻ったらやること 
 ・ ジム入会 
@@ -57911,71 +57842,48 @@
 ・ブスでもBBAでも片っ端からアプローチ</t>
         </is>
       </c>
-      <c r="C1969" t="n">
+      <c r="C1966" t="n">
         <v>261</v>
       </c>
-      <c r="D1969" t="n">
+      <c r="D1966" t="n">
         <v>13</v>
       </c>
-      <c r="E1969" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1970">
-      <c r="A1970" t="inlineStr">
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
         <is>
           <t>2026-06-11 09:11:09</t>
         </is>
       </c>
-      <c r="B1970" t="inlineStr">
+      <c r="B1967" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1970" t="n">
+      <c r="C1967" t="n">
         <v>6</v>
       </c>
-      <c r="D1970" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1970" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1971">
-      <c r="A1971" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:12:47</t>
-        </is>
-      </c>
-      <c r="B1971" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/THP9aKICYW</t>
-        </is>
-      </c>
-      <c r="C1971" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1971" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1971" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1972">
-      <c r="A1972" t="inlineStr">
+      <c r="D1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
         <is>
           <t>2026-06-11 09:13:00</t>
         </is>
       </c>
-      <c r="B1972" t="inlineStr">
+      <c r="B1968" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。 環境を変える努力をしろ。 
@@ -57989,48 +57897,48 @@
 ・やるか死ぬかの状況</t>
         </is>
       </c>
-      <c r="C1972" t="n">
+      <c r="C1968" t="n">
         <v>54</v>
       </c>
-      <c r="D1972" t="n">
+      <c r="D1968" t="n">
         <v>8</v>
       </c>
-      <c r="E1972" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1973">
-      <c r="A1973" t="inlineStr">
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
         <is>
           <t>2026-06-11 09:15:26</t>
         </is>
       </c>
-      <c r="B1973" t="inlineStr">
+      <c r="B1969" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1973" t="n">
+      <c r="C1969" t="n">
         <v>2</v>
       </c>
-      <c r="D1973" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1973" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1974">
-      <c r="A1974" t="inlineStr">
+      <c r="D1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
         <is>
           <t>2026-06-11 09:45:00</t>
         </is>
       </c>
-      <c r="B1974" t="inlineStr">
+      <c r="B1970" t="inlineStr">
         <is>
           <t>あなたがチー牛顔である理由 
 ・一重 
@@ -58044,48 +57952,48 @@
 ・体脂肪率20%以上</t>
         </is>
       </c>
-      <c r="C1974" t="n">
+      <c r="C1970" t="n">
         <v>280</v>
       </c>
-      <c r="D1974" t="n">
+      <c r="D1970" t="n">
         <v>17</v>
       </c>
-      <c r="E1974" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1975">
-      <c r="A1975" t="inlineStr">
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
         <is>
           <t>2026-06-11 09:48:30</t>
         </is>
       </c>
-      <c r="B1975" t="inlineStr">
+      <c r="B1971" t="inlineStr">
         <is>
           <t>【整形級】チー牛顔を治した一日10分で　モテるフェイスラインを作るトレーニング5選https://t.co/BLbPOtIUV1</t>
         </is>
       </c>
-      <c r="C1975" t="n">
+      <c r="C1971" t="n">
         <v>16</v>
       </c>
-      <c r="D1975" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1975" t="inlineStr">
+      <c r="D1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1971" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1976">
-      <c r="A1976" t="inlineStr">
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
         <is>
           <t>2026-06-11 10:10:00</t>
         </is>
       </c>
-      <c r="B1976" t="inlineStr">
+      <c r="B1972" t="inlineStr">
         <is>
           <t>孤独でもメンタルを安定させる方法 
 男磨きは孤独との戦いになるので実践してほしい。
@@ -58099,25 +58007,25 @@
 むしろ人生はいい方向に進む。</t>
         </is>
       </c>
-      <c r="C1976" t="n">
+      <c r="C1972" t="n">
         <v>81</v>
       </c>
-      <c r="D1976" t="n">
+      <c r="D1972" t="n">
         <v>7</v>
       </c>
-      <c r="E1976" t="inlineStr">
+      <c r="E1972" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1977">
-      <c r="A1977" t="inlineStr">
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
         <is>
           <t>2026-06-11 10:37:00</t>
         </is>
       </c>
-      <c r="B1977" t="inlineStr">
+      <c r="B1973" t="inlineStr">
         <is>
           <t>スマホ断ちがあなたに与えるもの 
 ・思考力 
@@ -58131,96 +58039,96 @@
 SNSを受動的に見ることは百害あって一利なし。</t>
         </is>
       </c>
-      <c r="C1977" t="n">
+      <c r="C1973" t="n">
         <v>30</v>
       </c>
-      <c r="D1977" t="n">
+      <c r="D1973" t="n">
         <v>3</v>
       </c>
-      <c r="E1977" t="inlineStr">
+      <c r="E1973" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1978">
-      <c r="A1978" t="inlineStr">
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
         <is>
           <t>2026-06-11 10:45:10</t>
         </is>
       </c>
-      <c r="B1978" t="inlineStr">
+      <c r="B1974" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1978" t="n">
+      <c r="C1974" t="n">
         <v>3</v>
       </c>
-      <c r="D1978" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1978" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1979">
-      <c r="A1979" t="inlineStr">
+      <c r="D1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
         <is>
           <t>2026-06-11 11:26:00</t>
         </is>
       </c>
-      <c r="B1979" t="inlineStr">
+      <c r="B1975" t="inlineStr">
         <is>
           <t>男磨きのゴールは「俺は一生、セ◯クスに困らない」という自信を作ること。 
 この自信がモテ以外の人生の楽しみに集中させてくれる。 そして、余裕を生みさらにモテを生んでくれる。 
 だから、俺は「ブスでもBBAでもいいから片っ端からいけ」と言ってるのよ。</t>
         </is>
       </c>
-      <c r="C1979" t="n">
+      <c r="C1975" t="n">
         <v>70</v>
       </c>
-      <c r="D1979" t="n">
+      <c r="D1975" t="n">
         <v>4</v>
       </c>
-      <c r="E1979" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1980">
-      <c r="A1980" t="inlineStr">
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
         <is>
           <t>2026-06-11 11:30:28</t>
         </is>
       </c>
-      <c r="B1980" t="inlineStr">
+      <c r="B1976" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1980" t="n">
+      <c r="C1976" t="n">
         <v>2</v>
       </c>
-      <c r="D1980" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1980" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1981">
-      <c r="A1981" t="inlineStr">
+      <c r="D1976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
         <is>
           <t>2026-06-12 08:50:00</t>
         </is>
       </c>
-      <c r="B1981" t="inlineStr">
+      <c r="B1977" t="inlineStr">
         <is>
           <t>奥手な童貞の脳内  
 小学生時代 
@@ -58235,25 +58143,25 @@
 「昇進して女を見返すやで！」</t>
         </is>
       </c>
-      <c r="C1981" t="n">
+      <c r="C1977" t="n">
         <v>274</v>
       </c>
-      <c r="D1981" t="n">
+      <c r="D1977" t="n">
         <v>9</v>
       </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1982">
-      <c r="A1982" t="inlineStr">
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
         <is>
           <t>2026-06-12 09:20:00</t>
         </is>
       </c>
-      <c r="B1982" t="inlineStr">
+      <c r="B1978" t="inlineStr">
         <is>
           <t>退化を促すドーパミン 
 ・悪口 
@@ -58271,48 +58179,48 @@
 ドーパミンを得る対象を変えるだけで、人生は変わる。</t>
         </is>
       </c>
-      <c r="C1982" t="n">
+      <c r="C1978" t="n">
         <v>17</v>
       </c>
-      <c r="D1982" t="n">
+      <c r="D1978" t="n">
         <v>1</v>
       </c>
-      <c r="E1982" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1983">
-      <c r="A1983" t="inlineStr">
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
         <is>
           <t>2026-06-12 09:41:33</t>
         </is>
       </c>
-      <c r="B1983" t="inlineStr">
+      <c r="B1979" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説　https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1983" t="n">
+      <c r="C1979" t="n">
         <v>6</v>
       </c>
-      <c r="D1983" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1983" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1984">
-      <c r="A1984" t="inlineStr">
+      <c r="D1979" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
         <is>
           <t>2026-06-12 10:00:02</t>
         </is>
       </c>
-      <c r="B1984" t="inlineStr">
+      <c r="B1980" t="inlineStr">
         <is>
           <t>非モテはいきなり本命に行くな。
 あなたが「俺でもイケるかも」と思っている女にさえ、チキってアプローチできない時点で無理です。 
@@ -58321,25 +58229,25 @@
 まずは男磨きをし、ブスとBBAを口説くことから始めてください。</t>
         </is>
       </c>
-      <c r="C1984" t="n">
+      <c r="C1980" t="n">
         <v>14</v>
       </c>
-      <c r="D1984" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
+      <c r="D1980" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
         <is>
           <t>2026-06-12 10:28:00</t>
         </is>
       </c>
-      <c r="B1985" t="inlineStr">
+      <c r="B1981" t="inlineStr">
         <is>
           <t>負け犬の遠吠え集 
 ・「独身貴族」 
@@ -58353,71 +58261,48 @@
 逆に素直に「うらやましい」「悔しい」が言える男は強い。</t>
         </is>
       </c>
-      <c r="C1985" t="n">
+      <c r="C1981" t="n">
         <v>28</v>
       </c>
-      <c r="D1985" t="n">
+      <c r="D1981" t="n">
         <v>6</v>
       </c>
-      <c r="E1985" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1986">
-      <c r="A1986" t="inlineStr">
-        <is>
-          <t>2026-06-12 10:40:53</t>
-        </is>
-      </c>
-      <c r="B1986" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥 https://t.co/kaEFKpQPm9</t>
-        </is>
-      </c>
-      <c r="C1986" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1986" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1986" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1987">
-      <c r="A1987" t="inlineStr">
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
         <is>
           <t>2026-06-12 10:49:07</t>
         </is>
       </c>
-      <c r="B1987" t="inlineStr">
+      <c r="B1982" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/wxcdh2dWIc</t>
         </is>
       </c>
-      <c r="C1987" t="n">
+      <c r="C1982" t="n">
         <v>1</v>
       </c>
-      <c r="D1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
+      <c r="D1982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
         <is>
           <t>2026-06-12 10:53:00</t>
         </is>
       </c>
-      <c r="B1988" t="inlineStr">
+      <c r="B1983" t="inlineStr">
         <is>
           <t>決定疲れを減らす方法 
 ・デスクの整理 
@@ -58429,74 +58314,74 @@
 これで大事なタスクへの火力が爆上がりします。</t>
         </is>
       </c>
-      <c r="C1988" t="n">
+      <c r="C1983" t="n">
         <v>15</v>
       </c>
-      <c r="D1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1988" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
+      <c r="D1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
         <is>
           <t>2026-06-12 11:17:04</t>
         </is>
       </c>
-      <c r="B1989" t="inlineStr">
+      <c r="B1984" t="inlineStr">
         <is>
           <t>男の人生はシンプル。
 唸るほど金を持ち、ジムに行き、女行き倒す。
 他の事はどうでもいい。 https://t.co/9LrSQYOjXd</t>
         </is>
       </c>
-      <c r="C1989" t="n">
+      <c r="C1984" t="n">
         <v>77</v>
       </c>
-      <c r="D1989" t="n">
+      <c r="D1984" t="n">
         <v>6</v>
       </c>
-      <c r="E1989" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
         <is>
           <t>2026-06-12 11:46:23</t>
         </is>
       </c>
-      <c r="B1990" t="inlineStr">
+      <c r="B1985" t="inlineStr">
         <is>
           <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
 無料で空気を吸った方がコスパいい。</t>
         </is>
       </c>
-      <c r="C1990" t="n">
+      <c r="C1985" t="n">
         <v>19</v>
       </c>
-      <c r="D1990" t="n">
+      <c r="D1985" t="n">
         <v>1</v>
       </c>
-      <c r="E1990" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1991">
-      <c r="A1991" t="inlineStr">
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
         <is>
           <t>2026-06-12 12:00:00</t>
         </is>
       </c>
-      <c r="B1991" t="inlineStr">
+      <c r="B1986" t="inlineStr">
         <is>
           <t>疲れているのに眠れない原因 
 ①反芻思考 
@@ -58508,50 +58393,50 @@
 まずは原因を分析するところから始めよう。</t>
         </is>
       </c>
-      <c r="C1991" t="n">
+      <c r="C1986" t="n">
         <v>11</v>
       </c>
-      <c r="D1991" t="n">
+      <c r="D1986" t="n">
         <v>1</v>
       </c>
-      <c r="E1991" t="inlineStr">
+      <c r="E1986" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
         <is>
           <t>2026-06-12 12:32:00</t>
         </is>
       </c>
-      <c r="B1992" t="inlineStr">
+      <c r="B1987" t="inlineStr">
         <is>
           <t>睡眠の質を測るために、昔はスマートウォッチつけて寝てたけどやめちゃったな。
 理由はゴツゴツしてて睡眠の邪魔になっていたのと、別に計測したからといって質が上がるわけではないから。
 ”翌日のパフォーマンスが向上しているか”という体感こそがエビデンスだと思っています。</t>
         </is>
       </c>
-      <c r="C1992" t="n">
+      <c r="C1987" t="n">
         <v>7</v>
       </c>
-      <c r="D1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1992" t="inlineStr">
+      <c r="D1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1987" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
         <is>
           <t>2026-06-12 21:47:00</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1988" t="inlineStr">
         <is>
           <t>朝の水分補給は、ただの真水では睡眠中に失った電解質は取り戻せない。 
 また、電解質が入っていないと飲んだ水が身体に行き届きにくくなる。 
@@ -58559,25 +58444,25 @@
 もしこれが不味くて飲めないなら、「みそ汁」「コーンスープ」「電解質パウダー」でもOK</t>
         </is>
       </c>
-      <c r="C1993" t="n">
+      <c r="C1988" t="n">
         <v>21</v>
       </c>
-      <c r="D1993" t="n">
+      <c r="D1988" t="n">
         <v>2</v>
       </c>
-      <c r="E1993" t="inlineStr">
+      <c r="E1988" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1994">
-      <c r="A1994" t="inlineStr">
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
         <is>
           <t>2026-06-13 07:32:34</t>
         </is>
       </c>
-      <c r="B1994" t="inlineStr">
+      <c r="B1989" t="inlineStr">
         <is>
           <t>スマホ依存症を治すために私がやったこと 
 ・スマホなし1時間散歩 
@@ -58590,25 +58475,25 @@
 そして、SNSを全部PCに移せば、スマホを使う理由は少なくなる。</t>
         </is>
       </c>
-      <c r="C1994" t="n">
+      <c r="C1989" t="n">
         <v>82</v>
       </c>
-      <c r="D1994" t="n">
+      <c r="D1989" t="n">
         <v>4</v>
       </c>
-      <c r="E1994" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
         <is>
           <t>2026-06-13 08:27:00</t>
         </is>
       </c>
-      <c r="B1995" t="inlineStr">
+      <c r="B1990" t="inlineStr">
         <is>
           <t>非モテがチン騎士になる理由。  
 結論、それ以外の関わり方を知らないから。 
@@ -58617,25 +58502,25 @@
 優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
+      <c r="C1990" t="n">
         <v>57</v>
       </c>
-      <c r="D1995" t="n">
+      <c r="D1990" t="n">
         <v>1</v>
       </c>
-      <c r="E1995" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
         <is>
           <t>2026-06-13 09:00:01</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1991" t="inlineStr">
         <is>
           <t>スマホ依存症の症状 
 ・起きた瞬間にチェック 
@@ -58651,25 +58536,25 @@
 ・21時以降は見ない</t>
         </is>
       </c>
-      <c r="C1996" t="n">
+      <c r="C1991" t="n">
         <v>16</v>
       </c>
-      <c r="D1996" t="n">
+      <c r="D1991" t="n">
         <v>2</v>
       </c>
-      <c r="E1996" t="inlineStr">
+      <c r="E1991" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-13 09:21:45</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>自己満男磨き(笑)と呼ばれている習慣を擁護します。  
 【オナ禁】
@@ -58700,25 +58585,25 @@
 正しく評価して自分に落とし込むことが重要。</t>
         </is>
       </c>
-      <c r="C1997" t="n">
+      <c r="C1992" t="n">
         <v>10</v>
       </c>
-      <c r="D1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1997" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+      <c r="D1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
         <is>
           <t>2026-06-13 09:28:00</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1993" t="inlineStr">
         <is>
           <t>口呼吸が習慣化している人の特徴 
 ①舌が白い 
@@ -58729,25 +58614,25 @@
 高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
+      <c r="C1993" t="n">
         <v>26</v>
       </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="D1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
         <is>
           <t>2026-06-13 10:06:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1994" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58761,71 +58646,71 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
+      <c r="C1994" t="n">
         <v>49</v>
       </c>
-      <c r="D1999" t="n">
+      <c r="D1994" t="n">
         <v>3</v>
       </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-13 11:00:02</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
+      <c r="C1995" t="n">
         <v>60</v>
       </c>
-      <c r="D2000" t="n">
+      <c r="D1995" t="n">
         <v>2</v>
       </c>
-      <c r="E2000" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-13 11:17:03</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
-      <c r="C2001" t="n">
+      <c r="C1996" t="n">
         <v>1</v>
       </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-13 12:26:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58837,25 +58722,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
+      <c r="C1997" t="n">
         <v>16</v>
       </c>
-      <c r="D2002" t="n">
+      <c r="D1997" t="n">
         <v>1</v>
       </c>
-      <c r="E2002" t="inlineStr">
+      <c r="E1997" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58866,25 +58751,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
+      <c r="C1998" t="n">
         <v>19</v>
       </c>
-      <c r="D2003" t="n">
+      <c r="D1998" t="n">
         <v>2</v>
       </c>
-      <c r="E2003" t="inlineStr">
+      <c r="E1998" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58896,25 +58781,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
+      <c r="C1999" t="n">
         <v>19</v>
       </c>
-      <c r="D2004" t="n">
+      <c r="D1999" t="n">
         <v>2</v>
       </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -58931,25 +58816,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
+      <c r="C2000" t="n">
         <v>22</v>
       </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -58965,25 +58850,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
+      <c r="C2001" t="n">
         <v>17</v>
       </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -58996,48 +58881,48 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
+      <c r="C2002" t="n">
         <v>5</v>
       </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-14 09:07:02</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
         </is>
       </c>
-      <c r="C2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2008" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-14 09:31:00</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -59053,25 +58938,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -59081,25 +58966,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -59111,25 +58996,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -59141,25 +59026,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -59173,25 +59058,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -59208,25 +59093,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -59236,25 +59121,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -59268,25 +59153,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -59296,25 +59181,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -59325,25 +59210,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -59356,25 +59241,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59384,25 +59269,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59411,25 +59296,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59437,49 +59322,49 @@
 地味なライフハック。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-21 09:41:41</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>起床3秒後のEAA❌
 起床3秒後の歯磨き⭕</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-21 07:01:00</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59492,25 +59377,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59520,72 +59405,72 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-20 16:03:13</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-19 19:34:04</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
 失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-17 18:00:28</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59593,73 +59478,73 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-16 18:11:46</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
         </is>
       </c>
-      <c r="C2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-16 06:56:00</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59674,25 +59559,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59703,25 +59588,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59729,25 +59614,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59762,25 +59647,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59791,25 +59676,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="C2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59821,25 +59706,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59849,25 +59734,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59875,25 +59760,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="C2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59904,25 +59789,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59935,25 +59820,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59961,25 +59846,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59991,25 +59876,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -60017,25 +59902,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -60050,25 +59935,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -60079,25 +59964,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -60114,25 +59999,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -60148,54 +60033,54 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
-      <c r="C2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2047" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2042" t="inlineStr">
         <is>
           <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-06-25 19:07:20</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
 すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
         </is>
       </c>
-      <c r="C2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-06-25 19:26:49</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -60223,25 +60108,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2049" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -60253,25 +60138,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2050" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -60284,25 +60169,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2051" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -60313,25 +60198,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2052" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -60339,25 +60224,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2053" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="C2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -60367,30 +60252,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2054" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2054" t="inlineStr">
+      <c r="C2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2049" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60401,30 +60286,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2055" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2055" t="inlineStr">
+      <c r="C2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2050" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60434,30 +60319,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2056" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2056" t="inlineStr">
+      <c r="C2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2051" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60470,30 +60355,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2057" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2057" t="inlineStr">
+      <c r="C2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2052" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60504,55 +60389,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2058" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="C2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2059" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2059" t="inlineStr">
+      <c r="C2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2054" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60565,25 +60450,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="C2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60594,25 +60479,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="C2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60623,25 +60508,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="C2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60650,19 +60535,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60679,19 +60564,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60704,19 +60589,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60728,19 +60613,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60749,19 +60634,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60774,19 +60659,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60797,19 +60682,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60821,19 +60706,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60842,19 +60727,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60873,24 +60758,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2072" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2067" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60902,19 +60787,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60929,19 +60814,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60955,19 +60840,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60978,19 +60863,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -61000,38 +60885,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -61040,19 +60925,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -61064,19 +60949,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-24 12:00:00</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>マチアプはあなたの恋愛市場価値を測るための試金石。
 【上位1%】
@@ -61098,25 +60983,25 @@
 俺が変われたのは、チー牛時代にマチアプで惨敗して現実を知ったから。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
+      <c r="C2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2076" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -61126,19 +61011,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -61152,19 +61037,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -61182,24 +61067,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2084" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2079" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -61210,24 +61095,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2085" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2080" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -61237,24 +61122,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2086" t="inlineStr">
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2081" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -61263,19 +61148,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -61289,19 +61174,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -61314,19 +61199,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -61339,19 +61224,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61365,19 +61250,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61398,19 +61283,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61418,19 +61303,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61438,19 +61323,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61460,19 +61345,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61481,19 +61366,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61507,25 +61392,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61539,30 +61424,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2098" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2093" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61575,25 +61460,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61608,25 +61493,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61639,25 +61524,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61667,25 +61552,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61699,25 +61584,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61740,25 +61625,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61767,25 +61652,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61800,25 +61685,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61835,25 +61720,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61864,25 +61749,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61900,25 +61785,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61931,25 +61816,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61960,48 +61845,48 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -62020,25 +61905,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -62054,25 +61939,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -62084,25 +61969,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -62112,25 +61997,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -62142,25 +62027,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -62170,25 +62055,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -62210,25 +62095,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -62242,30 +62127,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2120" t="inlineStr">
+      <c r="C2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2115" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -62277,25 +62162,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="C2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -62306,25 +62191,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="C2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62360,25 +62245,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="C2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62390,25 +62275,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="C2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62424,25 +62309,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62454,25 +62339,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62501,50 +62386,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62559,25 +62444,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62588,25 +62473,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62624,19 +62509,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62657,19 +62542,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62681,19 +62566,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62705,19 +62590,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62728,19 +62613,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62754,19 +62639,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62778,19 +62663,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62803,19 +62688,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62831,19 +62716,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62861,19 +62746,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62887,19 +62772,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62911,19 +62796,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62936,19 +62821,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62959,19 +62844,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62980,19 +62865,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -63002,19 +62887,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -63026,19 +62911,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -63053,19 +62938,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -63078,19 +62963,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2149" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -63103,19 +62988,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2150" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2151">
-      <c r="A2151" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -63131,19 +63016,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2151" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2152">
-      <c r="A2152" t="inlineStr">
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2152" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -63160,19 +63045,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2152" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2153">
-      <c r="A2153" t="inlineStr">
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2148" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -63185,19 +63070,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2153" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2154">
-      <c r="A2154" t="inlineStr">
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2149" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -63207,19 +63092,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2154" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2155">
-      <c r="A2155" t="inlineStr">
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2150" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -63230,19 +63115,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2155" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2156">
-      <c r="A2156" t="inlineStr">
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2151" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -63255,19 +63140,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2156" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2157">
-      <c r="A2157" t="inlineStr">
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2157" t="inlineStr">
+      <c r="B2152" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -63283,19 +63168,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2157" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2158">
-      <c r="A2158" t="inlineStr">
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2153" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -63310,19 +63195,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2158" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2159">
-      <c r="A2159" t="inlineStr">
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2159" t="inlineStr">
+      <c r="B2154" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -63339,7 +63224,7 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2159" t="inlineStr">
+      <c r="E2154" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -57342,7 +57342,8 @@
 大学時代 
 「〇社入ったら彼女出来るんだろうなぁ」 
 社会人時代 
-「出世出来たら結婚出来るんだろうなぁ」</t>
+「出世出来たら結婚出来るんだろうなぁ」  
+天から運命の女性が降ってくることはない。</t>
         </is>
       </c>
       <c r="C1949" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2145"/>
+  <dimension ref="A1:G2146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63022,6 +63022,41 @@
         </is>
       </c>
     </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>環境のせいにしろ。
+あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
+環境を変える努力をしろ。
+意識する事は
+・職場
+・関わる人
+・住む場所
+・SNSで誰をフォローするか
+・ネガティブ人間をミュート
+・部屋、デスク環境
+・やるか死ぬかの状況
+環境を変化させれば努力は自動化する。
+いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -57978,7 +57978,11 @@
 大学時代 
 「オナ禁！ジム！コールドシャワー！」 
 社会人時代 
-「昇進して女を見返すやで！」</t>
+「昇進して女を見返すやで！」  
+結果、女性経験0のままイケメンに捨てられたATM目当ての35歳と結婚。  
+全てが自己完結になっていることが問題。  
+確かにスペックを上げることは重要。 
+でも、あなたに足りないのは女性に対する積極性。</t>
         </is>
       </c>
       <c r="C1970" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2146"/>
+  <dimension ref="A1:G2145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60754,50 +60754,10 @@
     <row r="2067">
       <c r="A2067" t="inlineStr">
         <is>
-          <t>2026-07-24 12:00:00</t>
+          <t>2026-05-26 00:00:00</t>
         </is>
       </c>
       <c r="B2067" t="inlineStr">
-        <is>
-          <t>マチアプはあなたの恋愛市場価値を測るための試金石。
-【上位1%】
-・毎日いいねが数十～数百件。
-・女性を選び放題。
-【上位20%】
-・毎日、数十人とマッチ。
-・普通に遊べる。
-・上位の女性とは稀にマッチする。
-【上位50%(フツメン層)】
-・マッチ率1～5%。
-・ブスやBBAが多め。
-・労力とリターンが合わない。
-【下位20%（チー牛層）】
-・マッチ率1％未満。
-・業者、マルチ勧誘、トランスとマッチ。
-・普通の女性には相手にされない。
-チー牛は今すぐ無料アプリをやって現実を見た方がいい。
-俺が変われたのは、チー牛時代にマチアプで惨敗して現実を知ったから。</t>
-        </is>
-      </c>
-      <c r="C2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
-        <is>
-          <t>2026-05-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2068" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -60807,19 +60767,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -60833,19 +60793,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60863,24 +60823,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2070" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2069" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60891,24 +60851,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2071" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2070" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60918,24 +60878,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2072" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2071" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60944,19 +60904,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60970,19 +60930,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60995,19 +60955,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -61020,19 +60980,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61046,19 +61006,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61079,19 +61039,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61099,19 +61059,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61119,19 +61079,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61141,19 +61101,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61162,19 +61122,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61188,25 +61148,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61220,30 +61180,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2084" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2083" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61256,25 +61216,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61289,25 +61249,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61320,25 +61280,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61348,25 +61308,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61380,25 +61340,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61421,25 +61381,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61448,25 +61408,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61481,25 +61441,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61516,25 +61476,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61545,25 +61505,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61581,25 +61541,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61612,25 +61572,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61641,6 +61601,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2097" t="n">
         <v>0</v>
       </c>
@@ -61660,29 +61643,6 @@
         </is>
       </c>
       <c r="B2098" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2099" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61701,25 +61661,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61735,25 +61695,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61765,25 +61725,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61793,25 +61753,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61823,25 +61783,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61851,25 +61811,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61891,25 +61851,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61923,30 +61883,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2106" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2105" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61958,25 +61918,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61987,25 +61947,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62041,25 +62001,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62071,25 +62031,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62105,25 +62065,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62135,25 +62095,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62182,50 +62142,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62240,25 +62200,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62269,25 +62229,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="C2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62305,19 +62265,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62338,19 +62298,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62362,19 +62322,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62386,19 +62346,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62409,19 +62369,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62435,19 +62395,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62459,19 +62419,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62484,19 +62444,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62512,19 +62472,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62542,19 +62502,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62568,19 +62528,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62592,19 +62552,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62617,19 +62577,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62640,19 +62600,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62661,19 +62621,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62683,19 +62643,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62707,19 +62667,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62734,19 +62694,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62759,19 +62719,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62784,19 +62744,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62812,19 +62772,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62841,19 +62801,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62866,19 +62826,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62888,19 +62848,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62911,19 +62871,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62936,19 +62896,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62964,19 +62924,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62991,19 +62951,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -63020,19 +62980,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -63049,13 +63009,13 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2146" t="inlineStr">
+      <c r="C2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2145" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2145"/>
+  <dimension ref="A1:G2146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63021,6 +63021,54 @@
         </is>
       </c>
     </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>ポルノ中毒には2種類ある。
+① 精液過多型
+テストステロン値が高く、性欲が強すぎて抜かずにはいられないタイプ。
+・思春期
+・トレーニー
+・性欲が強い男
+このタイプは、性欲高さが原因。
+必要なのは自己規律を作り、性欲をコントロールすること。
+そして童貞非モテであれば、モテることが課題。
+② 行為依存型
+こっちの方が危険。
+性欲ではなく、ポルノや自慰行為による快楽刺激に依存しているタイプ。
+・ストレス
+・退屈
+・孤独感
+・現実逃避
+こうした不快感を紛らわすためにポルノを利用し、気づけば習慣化している。
+このタイプは、テストステロン値の高さではなく、脳の報酬系と行動パターンの問題。
+だから、単純に性欲を抑えても解決しない。
+必要なのは、
+・依存を引き起こす環境の排除
+・ストレスへの対処法を身につける
+・ポルノ以外の報酬を増やす
+前者は性欲のコントロール。
+後者は依存行動の克服。
+同じ自慰行為でも、原因が違えば対策も違う</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2146"/>
+  <dimension ref="A1:G2147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63069,6 +63069,37 @@
         </is>
       </c>
     </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>筋トレでスマホやめると、
+セットの質が上がった。
+前までは「スマホくらいいじらせろよ」と
+思ってたけど、
+・呼吸に集中して整える
+・交感神経優位にする
+スマホいじってた時はシンプルに
+これが出来てなかったのかもしれない。
+そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2147"/>
+  <dimension ref="A1:G2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63100,6 +63100,38 @@
         </is>
       </c>
     </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>鬱は予防できる。
+カフェインを体重×3mg摂って、
+サンクラでトムプラッツ聴きながら、
+ジムで脚トレ2時間やる。
+週1でやってたら鬱になる方が難しい。</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2148" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2148"/>
+  <dimension ref="A1:G2147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58150,34 +58150,10 @@
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>2026-06-12 11:46:23</t>
+          <t>2026-06-12 12:00:00</t>
         </is>
       </c>
       <c r="B1976" t="inlineStr">
-        <is>
-          <t>タバコ吸うと落ち着くのは、単に呼吸が深くなるら。
-無料で空気を吸った方がコスパいい。</t>
-        </is>
-      </c>
-      <c r="C1976" t="n">
-        <v>19</v>
-      </c>
-      <c r="D1976" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1976" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1977">
-      <c r="A1977" t="inlineStr">
-        <is>
-          <t>2026-06-12 12:00:00</t>
-        </is>
-      </c>
-      <c r="B1977" t="inlineStr">
         <is>
           <t>疲れているのに眠れない原因 
 ①反芻思考 
@@ -58189,50 +58165,50 @@
 まずは原因を分析するところから始めよう。</t>
         </is>
       </c>
-      <c r="C1977" t="n">
+      <c r="C1976" t="n">
         <v>11</v>
       </c>
-      <c r="D1977" t="n">
+      <c r="D1976" t="n">
         <v>1</v>
       </c>
-      <c r="E1977" t="inlineStr">
+      <c r="E1976" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1978">
-      <c r="A1978" t="inlineStr">
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
         <is>
           <t>2026-06-12 12:32:00</t>
         </is>
       </c>
-      <c r="B1978" t="inlineStr">
+      <c r="B1977" t="inlineStr">
         <is>
           <t>睡眠の質を測るために、昔はスマートウォッチつけて寝てたけどやめちゃったな。
 理由はゴツゴツしてて睡眠の邪魔になっていたのと、別に計測したからといって質が上がるわけではないから。
 ”翌日のパフォーマンスが向上しているか”という体感こそがエビデンスだと思っています。</t>
         </is>
       </c>
-      <c r="C1978" t="n">
+      <c r="C1977" t="n">
         <v>7</v>
       </c>
-      <c r="D1978" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1978" t="inlineStr">
+      <c r="D1977" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1977" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1979">
-      <c r="A1979" t="inlineStr">
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
         <is>
           <t>2026-06-12 21:47:00</t>
         </is>
       </c>
-      <c r="B1979" t="inlineStr">
+      <c r="B1978" t="inlineStr">
         <is>
           <t>朝の水分補給は、ただの真水では睡眠中に失った電解質は取り戻せない。 
 また、電解質が入っていないと飲んだ水が身体に行き届きにくくなる。 
@@ -58240,25 +58216,25 @@
 もしこれが不味くて飲めないなら、「みそ汁」「コーンスープ」「電解質パウダー」でもOK</t>
         </is>
       </c>
-      <c r="C1979" t="n">
+      <c r="C1978" t="n">
         <v>21</v>
       </c>
-      <c r="D1979" t="n">
+      <c r="D1978" t="n">
         <v>2</v>
       </c>
-      <c r="E1979" t="inlineStr">
+      <c r="E1978" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1980">
-      <c r="A1980" t="inlineStr">
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
         <is>
           <t>2026-06-13 07:32:34</t>
         </is>
       </c>
-      <c r="B1980" t="inlineStr">
+      <c r="B1979" t="inlineStr">
         <is>
           <t>スマホ依存症を治すために私がやったこと 
 ・スマホなし1時間散歩 
@@ -58271,25 +58247,25 @@
 そして、SNSを全部PCに移せば、スマホを使う理由は少なくなる。</t>
         </is>
       </c>
-      <c r="C1980" t="n">
+      <c r="C1979" t="n">
         <v>82</v>
       </c>
-      <c r="D1980" t="n">
+      <c r="D1979" t="n">
         <v>4</v>
       </c>
-      <c r="E1980" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1981">
-      <c r="A1981" t="inlineStr">
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
         <is>
           <t>2026-06-13 08:27:00</t>
         </is>
       </c>
-      <c r="B1981" t="inlineStr">
+      <c r="B1980" t="inlineStr">
         <is>
           <t>非モテがチン騎士になる理由。  
 結論、それ以外の関わり方を知らないから。 
@@ -58298,25 +58274,25 @@
 優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
         </is>
       </c>
-      <c r="C1981" t="n">
+      <c r="C1980" t="n">
         <v>57</v>
       </c>
-      <c r="D1981" t="n">
+      <c r="D1980" t="n">
         <v>1</v>
       </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1982">
-      <c r="A1982" t="inlineStr">
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
         <is>
           <t>2026-06-13 09:00:01</t>
         </is>
       </c>
-      <c r="B1982" t="inlineStr">
+      <c r="B1981" t="inlineStr">
         <is>
           <t>スマホ依存症の症状 
 ・起きた瞬間にチェック 
@@ -58332,25 +58308,25 @@
 ・21時以降は見ない</t>
         </is>
       </c>
-      <c r="C1982" t="n">
+      <c r="C1981" t="n">
         <v>16</v>
       </c>
-      <c r="D1982" t="n">
+      <c r="D1981" t="n">
         <v>2</v>
       </c>
-      <c r="E1982" t="inlineStr">
+      <c r="E1981" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1983">
-      <c r="A1983" t="inlineStr">
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
         <is>
           <t>2026-06-13 09:21:45</t>
         </is>
       </c>
-      <c r="B1983" t="inlineStr">
+      <c r="B1982" t="inlineStr">
         <is>
           <t>自己満男磨き(笑)と呼ばれている習慣を擁護します。  
 【オナ禁】
@@ -58381,25 +58357,25 @@
 正しく評価して自分に落とし込むことが重要。</t>
         </is>
       </c>
-      <c r="C1983" t="n">
+      <c r="C1982" t="n">
         <v>10</v>
       </c>
-      <c r="D1983" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1983" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1984">
-      <c r="A1984" t="inlineStr">
+      <c r="D1982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
         <is>
           <t>2026-06-13 09:28:00</t>
         </is>
       </c>
-      <c r="B1984" t="inlineStr">
+      <c r="B1983" t="inlineStr">
         <is>
           <t>口呼吸が習慣化している人の特徴 
 ①舌が白い 
@@ -58410,25 +58386,25 @@
 高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
         </is>
       </c>
-      <c r="C1984" t="n">
+      <c r="C1983" t="n">
         <v>26</v>
       </c>
-      <c r="D1984" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
+      <c r="D1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
         <is>
           <t>2026-06-13 10:06:00</t>
         </is>
       </c>
-      <c r="B1985" t="inlineStr">
+      <c r="B1984" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58442,11 +58418,34 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
+      <c r="C1984" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:00:02</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+        </is>
+      </c>
       <c r="C1985" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D1985" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1985" t="inlineStr">
         <is>
@@ -58457,19 +58456,19 @@
     <row r="1986">
       <c r="A1986" t="inlineStr">
         <is>
-          <t>2026-06-13 11:00:02</t>
+          <t>2026-06-13 11:17:03</t>
         </is>
       </c>
       <c r="B1986" t="inlineStr">
         <is>
-          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C1986" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D1986" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1986" t="inlineStr">
         <is>
@@ -58480,33 +58479,10 @@
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>2026-06-13 11:17:03</t>
+          <t>2026-06-13 12:26:00</t>
         </is>
       </c>
       <c r="B1987" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1987" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
-        <is>
-          <t>2026-06-13 12:26:00</t>
-        </is>
-      </c>
-      <c r="B1988" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58518,25 +58494,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C1988" t="n">
+      <c r="C1987" t="n">
         <v>16</v>
       </c>
-      <c r="D1988" t="n">
+      <c r="D1987" t="n">
         <v>1</v>
       </c>
-      <c r="E1988" t="inlineStr">
+      <c r="E1987" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B1989" t="inlineStr">
+      <c r="B1988" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58547,25 +58523,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C1989" t="n">
+      <c r="C1988" t="n">
         <v>19</v>
       </c>
-      <c r="D1989" t="n">
+      <c r="D1988" t="n">
         <v>2</v>
       </c>
-      <c r="E1989" t="inlineStr">
+      <c r="E1988" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B1990" t="inlineStr">
+      <c r="B1989" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58577,25 +58553,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C1990" t="n">
+      <c r="C1989" t="n">
         <v>19</v>
       </c>
-      <c r="D1990" t="n">
+      <c r="D1989" t="n">
         <v>2</v>
       </c>
-      <c r="E1990" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1991">
-      <c r="A1991" t="inlineStr">
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B1991" t="inlineStr">
+      <c r="B1990" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -58612,25 +58588,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C1991" t="n">
+      <c r="C1990" t="n">
         <v>22</v>
       </c>
-      <c r="D1991" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1991" t="inlineStr">
+      <c r="D1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1990" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B1992" t="inlineStr">
+      <c r="B1991" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -58646,25 +58622,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C1992" t="n">
+      <c r="C1991" t="n">
         <v>17</v>
       </c>
-      <c r="D1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1992" t="inlineStr">
+      <c r="D1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1991" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -58677,8 +58653,31 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
+      <c r="C1992" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:07:02</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
+        </is>
+      </c>
       <c r="C1993" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D1993" t="n">
         <v>0</v>
@@ -58692,33 +58691,10 @@
     <row r="1994">
       <c r="A1994" t="inlineStr">
         <is>
-          <t>2026-06-14 09:07:02</t>
+          <t>2026-06-14 09:31:00</t>
         </is>
       </c>
       <c r="B1994" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
-        </is>
-      </c>
-      <c r="C1994" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1994" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1994" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
-        <is>
-          <t>2026-06-14 09:31:00</t>
-        </is>
-      </c>
-      <c r="B1995" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -58734,25 +58710,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1995" t="inlineStr">
+      <c r="C1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1994" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -58762,25 +58738,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1996" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+      <c r="C1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -58792,25 +58768,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1997" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -58822,25 +58798,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -58854,25 +58830,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -58889,25 +58865,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -58917,25 +58893,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -58949,25 +58925,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -58977,25 +58953,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -59006,25 +58982,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -59037,25 +59013,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59065,25 +59041,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59092,25 +59068,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59118,6 +59094,30 @@
 地味なライフハック。</t>
         </is>
       </c>
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:41:41</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>起床3秒後のEAA❌
+起床3秒後の歯磨き⭕</t>
+        </is>
+      </c>
       <c r="C2008" t="n">
         <v>0</v>
       </c>
@@ -59133,34 +59133,10 @@
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-21 07:01:00</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr">
-        <is>
-          <t>起床3秒後のEAA❌
-起床3秒後の歯磨き⭕</t>
-        </is>
-      </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:01:00</t>
-        </is>
-      </c>
-      <c r="B2010" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59173,25 +59149,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59201,6 +59177,29 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:03:13</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+        </is>
+      </c>
       <c r="C2011" t="n">
         <v>0</v>
       </c>
@@ -59216,12 +59215,13 @@
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-19 19:34:04</t>
         </is>
       </c>
       <c r="B2012" t="inlineStr">
         <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
       <c r="C2012" t="n">
@@ -59239,34 +59239,10 @@
     <row r="2013">
       <c r="A2013" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B2013" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B2014" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59274,31 +59250,54 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:46</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
+        </is>
+      </c>
       <c r="C2015" t="n">
         <v>0</v>
       </c>
@@ -59314,33 +59313,10 @@
     <row r="2016">
       <c r="A2016" t="inlineStr">
         <is>
-          <t>2026-06-16 18:11:46</t>
+          <t>2026-06-16 06:56:00</t>
         </is>
       </c>
       <c r="B2016" t="inlineStr">
-        <is>
-          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
-        </is>
-      </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:56:00</t>
-        </is>
-      </c>
-      <c r="B2017" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59355,25 +59331,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59384,25 +59360,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59410,25 +59386,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59443,25 +59419,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59472,25 +59448,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59502,25 +59478,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59530,25 +59506,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59556,25 +59532,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59585,25 +59561,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59616,25 +59592,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59642,25 +59618,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59672,25 +59648,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -59698,25 +59674,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -59731,25 +59707,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -59760,25 +59736,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+      <c r="C2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -59795,25 +59771,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -59829,6 +59805,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2032" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2033" t="n">
         <v>0</v>
       </c>
@@ -59838,45 +59843,16 @@
       <c r="E2033" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2033" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2035" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -59904,25 +59880,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59934,25 +59910,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59965,25 +59941,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59994,25 +59970,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -60020,25 +59996,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -60048,30 +60024,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2040" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2039" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60082,30 +60058,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2041" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2040" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60115,30 +60091,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2042" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2041" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60151,30 +60127,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2043" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2042" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60185,55 +60161,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2045" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2044" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60246,25 +60222,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2046" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60275,25 +60251,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2047" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60304,25 +60280,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2048" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60331,19 +60307,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60360,19 +60336,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60385,19 +60361,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60409,19 +60385,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60430,19 +60406,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60455,19 +60431,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60478,19 +60454,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60502,19 +60478,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60523,19 +60499,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60554,24 +60530,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2058" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2057" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60583,19 +60559,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60610,19 +60586,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60636,19 +60612,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60659,19 +60635,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60681,38 +60657,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60721,19 +60697,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60745,19 +60721,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -60767,19 +60743,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -60793,19 +60769,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60823,24 +60799,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2069" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2068" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60851,24 +60827,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2070" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2069" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60878,24 +60854,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2071" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2070" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60904,19 +60880,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60930,19 +60906,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60955,19 +60931,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60980,19 +60956,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -61006,19 +60982,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -61039,19 +61015,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61059,19 +61035,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61079,19 +61055,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61101,19 +61077,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61122,19 +61098,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61148,25 +61124,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61180,30 +61156,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2083" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2082" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61216,25 +61192,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61249,25 +61225,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61280,25 +61256,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61308,25 +61284,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61340,25 +61316,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61381,25 +61357,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61408,25 +61384,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61441,25 +61417,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61476,25 +61452,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61505,25 +61481,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61541,25 +61517,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61572,25 +61548,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61601,6 +61577,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2096" t="n">
         <v>0</v>
       </c>
@@ -61620,29 +61619,6 @@
         </is>
       </c>
       <c r="B2097" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2098" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61661,25 +61637,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61695,25 +61671,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61725,25 +61701,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61753,25 +61729,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61783,25 +61759,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61811,25 +61787,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61851,25 +61827,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61883,30 +61859,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2105" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2104" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61918,25 +61894,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61947,25 +61923,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -62001,25 +61977,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -62031,25 +62007,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62065,25 +62041,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62095,25 +62071,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62142,50 +62118,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62200,25 +62176,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62229,25 +62205,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62265,19 +62241,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62298,19 +62274,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62322,19 +62298,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62346,19 +62322,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62369,19 +62345,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62395,19 +62371,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62419,19 +62395,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62444,19 +62420,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62472,19 +62448,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62502,19 +62478,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62528,19 +62504,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62552,19 +62528,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62577,19 +62553,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62600,19 +62576,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62621,19 +62597,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62643,19 +62619,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62667,19 +62643,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62694,19 +62670,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62719,19 +62695,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62744,19 +62720,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62772,19 +62748,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62801,19 +62777,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62826,19 +62802,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62848,19 +62824,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62871,19 +62847,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62896,19 +62872,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62924,19 +62900,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62951,19 +62927,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62980,19 +62956,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -63009,25 +62985,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="C2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -63057,25 +63033,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="C2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -63088,25 +63064,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="C2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -63115,18 +63091,18 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2148" t="inlineStr">
+      <c r="C2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2147" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -58271,7 +58271,11 @@
 結論、それ以外の関わり方を知らないから。 
 非モテは「優しくすれば振り向てもらえる」と勘違いをしている。  
 しかし、現実は逆。 
-優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。</t>
+優しくすればするほど女は男を舐めてさらに大きいことを要求してくる。  
+またチン騎士的な態度を取っても、直接キモがれらることはないため「自分はモテている」と勘違いをしている点が厄介。  
+ムカつく女に対して 
+「きもい」「だるい」「消え失せろ」  
+この辺が言えない男はチン騎士の素質アリ。</t>
         </is>
       </c>
       <c r="C1980" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2147"/>
+  <dimension ref="A1:G2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63112,6 +63112,29 @@
         </is>
       </c>
     </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>「使えない筋肉」こそが至高。
+結局、人間はただの動物。
+ヒョロガリは舐められる。
+犯罪に老人や女子供が狙われるのも、抵抗できないと思われているから。
+男は筋肉をつけるだけで、体格による抑止力を得られる。
+強者はそもそも喧嘩にならない。
+身体のデカさ＝自己防衛</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2148"/>
+  <dimension ref="A1:G2149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63135,6 +63135,30 @@
         </is>
       </c>
     </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>メンズコーチにハマる男は、
+「父親に甘やかされてきた系」の弱男。
+グーで殴られた経験0の温玉
+だから父親代わりを探している。
+「本当のメンズコーチはお前の父親」と言う人はいるが実際そうでもない。
+自閉チー牛の私もTateやゴギンズを見てきた。
+生物学的な父と、
+精神的な父は違っていい。</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -63148,7 +63148,7 @@
 グーで殴られた経験0の温玉
 だから父親代わりを探している。
 「本当のメンズコーチはお前の父親」と言う人はいるが実際そうでもない。
-自閉チー牛の私もTateやゴギンズを見てきた。
+自閉チー牛の私もTopGやゴギンズを見てきた。
 生物学的な父と、
 精神的な父は違っていい。</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2149"/>
+  <dimension ref="A1:G2150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63159,6 +63159,29 @@
         </is>
       </c>
     </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
+5回シコっても翌日には、
+精液ローディングが完了するタイプ。
+私はこれだった。
+一方で、現実逃避や快楽依存は危険
+テストステロン値が高いわけではなく、
+行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -38889,7 +38889,29 @@
 ・「嫌われたらどうしよう」が強い
 対策：
 →場数。ナンパでもアプリでもいいから数を打て。
-恥ずかしい思いをして心臓に毛を生やす。</t>
+恥ずかしい思いをして心臓に毛を生やす。
+②積極童貞
+・女に行く勇気はある
+・大学デビュー失敗
+・距離感が下手
+・外見や雰囲気が整っていない
+対策：
+→筋トレ＋清潔感＋最低限のコミュ力。
+時間をかけて外見磨き。
+③悟り童貞
+・「女はめんどくさい」
+・「恋愛はコスパ悪い」
+・と語るが、実際は経験不足
+対策：
+→一度ちゃんと恋愛してみろ。
+経験してから語れ。
+④理想主義童貞
+・男子高出身に多め
+・完璧な恋愛を求める
+・二次元や幻想を追いがち
+対策：
+→現実の女性と関われ。友達止まりでもいい。
+まずは理想を壊す　が正しい</t>
         </is>
       </c>
       <c r="C1336" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -38911,7 +38911,7 @@
 ・二次元や幻想を追いがち
 対策：
 →現実の女性と関われ。友達止まりでもいい。
-まずは理想を壊す　が正しい</t>
+まずは理想を壊す</t>
         </is>
       </c>
       <c r="C1336" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2150"/>
+  <dimension ref="A1:G2151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63204,6 +63204,32 @@
         </is>
       </c>
     </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>テストステロンは原始的な生活で上がる。
+・1日1万歩歩く
+・重い物を持つ
+・硬いものを咀嚼する
+・裸で日光を浴びる
+・7〜9時間寝る
+・肉、魚、卵を食う
+・自然の中で過ごす
+・デジタルから離れる
+私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -51992,7 +51992,7 @@
 脂質 81g
 炭水化物 116g
 安いしマジで美味い。
-俺は豚ラーメンでミニカットなしで90kgを目指していく👍 https://t.co/DVNNKCLBTT https://t.co/OcjZPOUG0P</t>
+俺は豚ラーメンでミニカットなしで90kgを目指していく👍</t>
         </is>
       </c>
       <c r="C1762" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2149"/>
+  <dimension ref="A1:G2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58345,39 +58345,10 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>2026-06-13 09:28:00</t>
+          <t>2026-06-13 10:06:00</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
-        <is>
-          <t>口呼吸が習慣化している人の特徴 
-①舌が白い 
-②上唇が分厚い 
-③唇が乾燥する 
-④頻繁にのどが痛くなる 
-⑤瘦せているのに2重顎 
-高強度有酸素以外で口呼吸を習慣化するメリットはありません。</t>
-        </is>
-      </c>
-      <c r="C1981" t="n">
-        <v>26</v>
-      </c>
-      <c r="D1981" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1981" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1982">
-      <c r="A1982" t="inlineStr">
-        <is>
-          <t>2026-06-13 10:06:00</t>
-        </is>
-      </c>
-      <c r="B1982" t="inlineStr">
         <is>
           <t>奥手を治す方法1選 
 恋愛は 
@@ -58391,11 +58362,34 @@
 恋愛市場から強制退場させられる。</t>
         </is>
       </c>
+      <c r="C1981" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:00:02</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+        </is>
+      </c>
       <c r="C1982" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D1982" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1982" t="inlineStr">
         <is>
@@ -58406,19 +58400,19 @@
     <row r="1983">
       <c r="A1983" t="inlineStr">
         <is>
-          <t>2026-06-13 11:00:02</t>
+          <t>2026-06-13 11:17:03</t>
         </is>
       </c>
       <c r="B1983" t="inlineStr">
         <is>
-          <t>オナ猿はポテンシャルの塊。 普通の男には毎日3回以上シコるほどの性欲はない。 あとはこの性欲を自己研鑽に向けるのみ。 そして、なるべくデジタルデバイスをカットして週に3、4発に抑えること。 オナ禁というほどの禁欲はしなくていい。</t>
+          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
         </is>
       </c>
       <c r="C1983" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D1983" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1983" t="inlineStr">
         <is>
@@ -58429,33 +58423,10 @@
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>2026-06-13 11:17:03</t>
+          <t>2026-06-13 12:26:00</t>
         </is>
       </c>
       <c r="B1984" t="inlineStr">
-        <is>
-          <t>【脱非モテ】上位20%の男になるために必要な5つの要素 by 元自閉チー牛20歳童貞が解説https://t.co/e4uQAvxYot</t>
-        </is>
-      </c>
-      <c r="C1984" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1984" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1984" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1985">
-      <c r="A1985" t="inlineStr">
-        <is>
-          <t>2026-06-13 12:26:00</t>
-        </is>
-      </c>
-      <c r="B1985" t="inlineStr">
         <is>
           <t>夜にやめたこと 
 ・スマホを寝室に持ち込む 
@@ -58467,25 +58438,25 @@
 夜の過ごし方で朝が決まる。</t>
         </is>
       </c>
-      <c r="C1985" t="n">
+      <c r="C1984" t="n">
         <v>16</v>
       </c>
-      <c r="D1985" t="n">
+      <c r="D1984" t="n">
         <v>1</v>
       </c>
-      <c r="E1985" t="inlineStr">
+      <c r="E1984" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1986">
-      <c r="A1986" t="inlineStr">
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
         <is>
           <t>2026-06-13 22:25:00</t>
         </is>
       </c>
-      <c r="B1986" t="inlineStr">
+      <c r="B1985" t="inlineStr">
         <is>
           <t>朝スマホをやめて起きた変化 
 ・二度寝しなくなった 
@@ -58496,25 +58467,25 @@
 朝スマホは1日を殺す。</t>
         </is>
       </c>
-      <c r="C1986" t="n">
+      <c r="C1985" t="n">
         <v>19</v>
       </c>
-      <c r="D1986" t="n">
+      <c r="D1985" t="n">
         <v>2</v>
       </c>
-      <c r="E1986" t="inlineStr">
+      <c r="E1985" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1987">
-      <c r="A1987" t="inlineStr">
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
         <is>
           <t>2026-06-14 03:23:00</t>
         </is>
       </c>
-      <c r="B1987" t="inlineStr">
+      <c r="B1986" t="inlineStr">
         <is>
           <t>・日本でジムに通ってる人 
 →100人のうち4人 
@@ -58526,25 +58497,25 @@
 これだけで上位1％。</t>
         </is>
       </c>
-      <c r="C1987" t="n">
+      <c r="C1986" t="n">
         <v>19</v>
       </c>
-      <c r="D1987" t="n">
+      <c r="D1986" t="n">
         <v>2</v>
       </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
         <is>
           <t>2026-06-14 06:26:00</t>
         </is>
       </c>
-      <c r="B1988" t="inlineStr">
+      <c r="B1987" t="inlineStr">
         <is>
           <t>行動が早い奴の習慣 
 ・前日にタスクを決める 
@@ -58561,25 +58532,25 @@
 行動が遅い奴ほど考えすぎてる。</t>
         </is>
       </c>
-      <c r="C1988" t="n">
+      <c r="C1987" t="n">
         <v>22</v>
       </c>
-      <c r="D1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1988" t="inlineStr">
+      <c r="D1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1987" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
         <is>
           <t>2026-06-14 08:26:00</t>
         </is>
       </c>
-      <c r="B1989" t="inlineStr">
+      <c r="B1988" t="inlineStr">
         <is>
           <t>なぜ現代の男が弱っているのか？ 
 ・ポルノ 
@@ -58595,25 +58566,25 @@
 政治的要因は無理だが、生活習慣は変えられる。</t>
         </is>
       </c>
-      <c r="C1989" t="n">
+      <c r="C1988" t="n">
         <v>17</v>
       </c>
-      <c r="D1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1989" t="inlineStr">
+      <c r="D1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1988" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
         <is>
           <t>2026-06-14 09:00:00</t>
         </is>
       </c>
-      <c r="B1990" t="inlineStr">
+      <c r="B1989" t="inlineStr">
         <is>
           <t>ゲーム中毒を治す7ステップ 
 ①失った時間を認識する 
@@ -58626,8 +58597,31 @@
 私はこれを繰り返していく内にゲームへの執着が消えた。</t>
         </is>
       </c>
+      <c r="C1989" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:07:02</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
+        </is>
+      </c>
       <c r="C1990" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D1990" t="n">
         <v>0</v>
@@ -58641,33 +58635,10 @@
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>2026-06-14 09:07:02</t>
+          <t>2026-06-14 09:31:00</t>
         </is>
       </c>
       <c r="B1991" t="inlineStr">
-        <is>
-          <t>”爆速でモテる男磨きのやり方”非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説https://t.co/MBG8mm5jV3</t>
-        </is>
-      </c>
-      <c r="C1991" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1991" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1991" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1992">
-      <c r="A1992" t="inlineStr">
-        <is>
-          <t>2026-06-14 09:31:00</t>
-        </is>
-      </c>
-      <c r="B1992" t="inlineStr">
         <is>
           <t>チー牛がコミュ障な理由は "開示できる自己がない"から。  
 自己開示は相手と仲良くなる上で最初のステップ。  
@@ -58683,25 +58654,25 @@
 この辺を趣味にしておくとだいぶ変わる。</t>
         </is>
       </c>
-      <c r="C1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1992" t="inlineStr">
+      <c r="C1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1991" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
     </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1993" t="inlineStr">
+      <c r="B1992" t="inlineStr">
         <is>
           <t>マチアプをスワイプしている間、魅力は生まれない。
 SNSを更新している間、実力はつかない。
@@ -58711,25 +58682,25 @@
 これは自戒。</t>
         </is>
       </c>
-      <c r="C1993" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1993" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1993" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1994">
-      <c r="A1994" t="inlineStr">
+      <c r="C1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1994" t="inlineStr">
+      <c r="B1993" t="inlineStr">
         <is>
           <t>非モテの負け惜しみ
 ・美人は三日で飽きる
@@ -58741,25 +58712,25 @@
 全部「なってから言え」という話。</t>
         </is>
       </c>
-      <c r="C1994" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1994" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1994" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1995">
-      <c r="A1995" t="inlineStr">
+      <c r="C1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1995" t="inlineStr">
+      <c r="B1994" t="inlineStr">
         <is>
           <t>非モテは「小さなYes」が取れていない。
 いきなり家に誘う。
@@ -58771,25 +58742,25 @@
 小さなYesを積み重ねた先に、大きなYesがある。</t>
         </is>
       </c>
-      <c r="C1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1995" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
+      <c r="C1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1996" t="inlineStr">
+      <c r="B1995" t="inlineStr">
         <is>
           <t>陰キャ＝聞き上手は幻想。
 実際は話すことも聞くことも苦手。
@@ -58803,25 +58774,25 @@
 陰キャはまず、自分の頭を静かにすることから始める。</t>
         </is>
       </c>
-      <c r="C1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1996" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+      <c r="C1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>非モテが認めたがらない事実
 ・「筋トレすればモテる」
@@ -58838,25 +58809,25 @@
 → それが通用するのは上位1%のみ</t>
         </is>
       </c>
-      <c r="C1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1997" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>自重はジムに勝てない。
 筋肥大に必要なのは「重量を増やし続けること」。
@@ -58866,25 +58837,25 @@
 俺はこれで数年無駄にした。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>あなたが非モテなのは父親のせいです。
 何事にも口うるさい母親。
@@ -58898,25 +58869,25 @@
 誰でもいい。男としての生き方を見せてくれる存在を探せ。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
 別に金持ちになる必要はない。
@@ -58926,25 +58897,25 @@
 これをクリアできなければ遊ぶ資格はない。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
@@ -58955,25 +58926,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -58986,25 +58957,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -59014,25 +58985,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -59041,25 +59012,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -59067,6 +59038,30 @@
 地味なライフハック。</t>
         </is>
       </c>
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:41:41</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>起床3秒後のEAA❌
+起床3秒後の歯磨き⭕</t>
+        </is>
+      </c>
       <c r="C2005" t="n">
         <v>0</v>
       </c>
@@ -59082,34 +59077,10 @@
     <row r="2006">
       <c r="A2006" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-21 07:01:00</t>
         </is>
       </c>
       <c r="B2006" t="inlineStr">
-        <is>
-          <t>起床3秒後のEAA❌
-起床3秒後の歯磨き⭕</t>
-        </is>
-      </c>
-      <c r="C2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:01:00</t>
-        </is>
-      </c>
-      <c r="B2007" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -59122,25 +59093,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -59150,6 +59121,29 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:03:13</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+        </is>
+      </c>
       <c r="C2008" t="n">
         <v>0</v>
       </c>
@@ -59165,12 +59159,13 @@
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-19 19:34:04</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr">
         <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
       <c r="C2009" t="n">
@@ -59188,34 +59183,10 @@
     <row r="2010">
       <c r="A2010" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B2010" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B2011" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -59223,31 +59194,54 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:46</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
+        </is>
+      </c>
       <c r="C2012" t="n">
         <v>0</v>
       </c>
@@ -59263,33 +59257,10 @@
     <row r="2013">
       <c r="A2013" t="inlineStr">
         <is>
-          <t>2026-06-16 18:11:46</t>
+          <t>2026-06-16 06:56:00</t>
         </is>
       </c>
       <c r="B2013" t="inlineStr">
-        <is>
-          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
-        </is>
-      </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:56:00</t>
-        </is>
-      </c>
-      <c r="B2014" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -59304,25 +59275,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59333,25 +59304,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59359,25 +59330,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59392,25 +59363,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59421,25 +59392,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。 
 ・「嫌ならやめていい」 
@@ -59451,25 +59422,25 @@
 19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59479,25 +59450,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59505,25 +59476,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59534,25 +59505,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59565,25 +59536,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59591,25 +59562,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59621,25 +59592,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -59647,25 +59618,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -59680,25 +59651,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -59709,25 +59680,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -59744,25 +59715,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -59778,6 +59749,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2029" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2030" t="n">
         <v>0</v>
       </c>
@@ -59787,45 +59787,16 @@
       <c r="E2030" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2030" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2031" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2032" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -59853,25 +59824,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2032" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59883,25 +59854,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2033" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59914,25 +59885,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2034" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="C2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59943,25 +59914,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2035" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="C2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -59969,25 +59940,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2036" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="C2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -59997,30 +59968,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2037" t="inlineStr">
+      <c r="C2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2036" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -60031,30 +60002,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2038" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2038" t="inlineStr">
+      <c r="C2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2037" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -60064,30 +60035,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2039" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2039" t="inlineStr">
+      <c r="C2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2038" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -60100,30 +60071,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2040" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2040" t="inlineStr">
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2039" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -60134,55 +60105,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2041" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2042" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2042" t="inlineStr">
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2041" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -60195,25 +60166,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2043" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -60224,25 +60195,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2044" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -60253,25 +60224,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2045" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -60280,19 +60251,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -60309,19 +60280,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60334,19 +60305,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60358,19 +60329,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60379,19 +60350,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60404,19 +60375,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60427,19 +60398,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60451,19 +60422,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60472,19 +60443,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60503,24 +60474,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2055" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2054" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60532,19 +60503,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60559,19 +60530,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60585,19 +60556,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60608,19 +60579,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60630,38 +60601,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60670,19 +60641,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60694,19 +60665,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -60716,19 +60687,19 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-05-26 00:00:00</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>私が童貞チー牛だったら女は追わない。
 理由は上位20%以外はモテない構造だから。
@@ -60742,19 +60713,19 @@
 自分を好きになることが先。</t>
         </is>
       </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60772,24 +60743,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2066" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2065" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60800,24 +60771,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2067" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2066" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60827,24 +60798,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2068" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2067" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60853,19 +60824,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60879,19 +60850,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60904,19 +60875,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60929,19 +60900,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60955,19 +60926,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60988,19 +60959,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -61008,19 +60979,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61028,19 +60999,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61050,19 +61021,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61071,19 +61042,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61097,25 +61068,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61129,30 +61100,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2080" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2079" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61165,25 +61136,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61198,25 +61169,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61229,25 +61200,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61257,25 +61228,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61289,25 +61260,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61330,25 +61301,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61357,25 +61328,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61390,25 +61361,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61425,25 +61396,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61454,25 +61425,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61490,25 +61461,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61521,25 +61492,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61550,6 +61521,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2093" t="n">
         <v>0</v>
       </c>
@@ -61569,29 +61563,6 @@
         </is>
       </c>
       <c r="B2094" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2095" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61610,25 +61581,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61644,25 +61615,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61674,25 +61645,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="C2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61702,25 +61673,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61732,25 +61703,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61760,25 +61731,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61800,25 +61771,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61832,30 +61803,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2102" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2101" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61867,25 +61838,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61896,25 +61867,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61950,25 +61921,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61980,25 +61951,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -62014,25 +61985,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62044,25 +62015,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62091,50 +62062,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62149,25 +62120,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62178,25 +62149,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62214,19 +62185,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62247,19 +62218,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62271,19 +62242,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62295,19 +62266,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62318,19 +62289,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62344,19 +62315,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62368,19 +62339,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62393,19 +62364,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62421,19 +62392,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62451,19 +62422,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62477,19 +62448,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62501,19 +62472,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62526,19 +62497,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62549,19 +62520,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62570,19 +62541,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62592,19 +62563,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62616,19 +62587,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62643,19 +62614,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62668,19 +62639,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62693,19 +62664,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62721,19 +62692,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62750,19 +62721,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62775,19 +62746,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62797,19 +62768,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62820,19 +62791,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62845,19 +62816,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62873,19 +62844,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62900,19 +62871,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62929,19 +62900,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62958,25 +62929,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="C2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -63006,25 +62977,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="C2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -63037,25 +63008,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+      <c r="C2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -63064,30 +63035,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2145" t="inlineStr">
+      <c r="C2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2144" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -63098,19 +63069,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -63122,19 +63093,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2147" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -63145,19 +63116,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="A2149" t="inlineStr">
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2149" t="inlineStr">
+      <c r="B2148" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -63171,7 +63142,7 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2149" t="inlineStr">
+      <c r="E2148" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -39153,7 +39153,8 @@
 ・姿勢が良くなった
 ・人生の迷いが減った
 スクリーンタイム10時間→1〜2時間へ大幅に削減。
-その結果どう人生が変わったのか… https://t.co/IU4HRJ5oKY</t>
+その結果どう人生が変わったのか
+記事にまとめました。https://t.co/IU4HRJ5oKY</t>
         </is>
       </c>
       <c r="C1344" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2148"/>
+  <dimension ref="A1:G2146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60675,58 +60675,10 @@
     <row r="2063">
       <c r="A2063" t="inlineStr">
         <is>
-          <t>2026-05-26 00:00:00</t>
+          <t>2026-07-27 00:00:00</t>
         </is>
       </c>
       <c r="B2063" t="inlineStr">
-        <is>
-          <t>堕落を治すには起床3秒が勝負。
-スマホに手を伸ばすか、
-歯ブラシに手を伸ばすか。
-「朝活をやろう」なんて考えなくていい。
-起床直後に歯ブラシに手を伸ばすことだけ意識すれば、
-あとは流れで上手くいきやすい。</t>
-        </is>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
-        <is>
-          <t>2026-05-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2064" t="inlineStr">
-        <is>
-          <t>私が童貞チー牛だったら女は追わない。
-理由は上位20%以外はモテない構造だから。
-それよりも自分のコンプを解消する事に注力する。
-・ヒョロガリなら最低10kgバルクして減量。
-・貧乏ならバイト以外の収益源を作る。
-・外見（髪、眉毛、髭、ASD顔）を治す。
-→必要に応じて医療に頼る。チー牛顔なら特に口元を治す。
-チー牛がアプリで童卒出来てもラッキーパンチだから継続性がない。
-まず「堕落を治す」「性的魅力向上」から始める。
-自分を好きになることが先。</t>
-        </is>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
-        <is>
-          <t>2026-07-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2065" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60744,24 +60696,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2065" t="inlineStr">
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2063" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60772,24 +60724,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2066" t="inlineStr">
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2064" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60799,24 +60751,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2067" t="inlineStr">
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2065" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60825,19 +60777,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60851,19 +60803,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60876,19 +60828,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60901,19 +60853,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60927,19 +60879,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60960,19 +60912,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -60980,19 +60932,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -61000,19 +60952,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -61022,19 +60974,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -61043,19 +60995,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -61069,25 +61021,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="C2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -61101,30 +61053,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2079" t="inlineStr">
+      <c r="C2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2077" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -61137,25 +61089,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -61170,25 +61122,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -61201,25 +61153,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -61229,25 +61181,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -61261,25 +61213,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -61302,25 +61254,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -61329,25 +61281,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61362,25 +61314,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61397,25 +61349,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61426,25 +61378,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61462,25 +61414,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61493,25 +61445,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61522,48 +61474,48 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61582,25 +61534,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61616,25 +61568,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61646,25 +61598,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61674,25 +61626,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2097" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61704,25 +61656,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2098" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="C2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61732,25 +61684,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2099" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61772,25 +61724,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61804,30 +61756,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2101" t="inlineStr">
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2099" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61839,25 +61791,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61868,25 +61820,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61922,25 +61874,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61952,25 +61904,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -61986,25 +61938,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -62016,25 +61968,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -62063,50 +62015,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="C2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="C2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -62121,25 +62073,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="C2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -62150,25 +62102,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="C2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -62186,19 +62138,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -62219,19 +62171,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -62243,19 +62195,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -62267,19 +62219,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -62290,19 +62242,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -62316,19 +62268,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -62340,19 +62292,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62365,19 +62317,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62393,19 +62345,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62423,19 +62375,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62449,19 +62401,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62473,19 +62425,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62498,19 +62450,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62521,19 +62473,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62542,19 +62494,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62564,19 +62516,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62588,19 +62540,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62615,19 +62567,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62640,19 +62592,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62665,19 +62617,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62693,19 +62645,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62722,19 +62674,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62747,19 +62699,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62769,19 +62721,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62792,19 +62744,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62817,19 +62769,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62845,19 +62797,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62872,19 +62824,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="A2140" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2140" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62901,19 +62853,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2140" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="A2141" t="inlineStr">
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2141" t="inlineStr">
+      <c r="B2139" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62930,25 +62882,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2141" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="A2142" t="inlineStr">
+      <c r="C2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2142" t="inlineStr">
+      <c r="B2140" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -62978,25 +62930,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2142" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="A2143" t="inlineStr">
+      <c r="C2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2143" t="inlineStr">
+      <c r="B2141" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -63009,25 +62961,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2143" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
+      <c r="C2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2144" t="inlineStr">
+      <c r="B2142" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -63036,30 +62988,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2144" t="inlineStr">
+      <c r="C2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2142" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2145">
-      <c r="A2145" t="inlineStr">
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2145" t="inlineStr">
+      <c r="B2143" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -63070,19 +63022,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2145" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="A2146" t="inlineStr">
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2146" t="inlineStr">
+      <c r="B2144" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -63094,19 +63046,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2146" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="A2147" t="inlineStr">
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2147" t="inlineStr">
+      <c r="B2145" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -63117,19 +63069,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="A2148" t="inlineStr">
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2148" t="inlineStr">
+      <c r="B2146" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -63143,7 +63095,7 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2148" t="inlineStr">
+      <c r="E2146" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -11,7 +11,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -50,9 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2133"/>
+  <dimension ref="A1:G2134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62802,6 +62805,26 @@
         </is>
       </c>
     </row>
+    <row r="2134">
+      <c r="A2134" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>堕落を治すには起床3秒が勝負。
+スマホに手を伸ばすか、
+歯ブラシに手を伸ばすか。
+「朝活をやろう」なんて考えなくていい。
+起床直後に歯ブラシに手を伸ばすことだけ意識すれば、
+あとは流れで上手くいきやすい。</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -51001,7 +51001,7 @@
 ・キーボード、コントローラを売る
 して、物理的にゲームを出来なくしてしまえば3日で脳が慣れていく。
 ゲーム廃人の俺は大事な時期だけはコントローラをゴミに出してたよ。
-繰り返していく内に段々執着がなくなって、今はまったくやていない。これが正しい</t>
+繰り返していく内に段々執着がなくなって、今はまったくやていない。</t>
         </is>
       </c>
       <c r="C1731" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2134"/>
+  <dimension ref="A1:G2135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62825,6 +62825,29 @@
         </is>
       </c>
     </row>
+    <row r="2135">
+      <c r="A2135" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>モテ攻略に大学はターニングポイントになる。
+・サークル、ゼミ、バイト
+・女側もオープン
+・童貞でも引け目がない
+・女も処女5~7割
+・失敗しても次のチャンスがある
+私は童貞チー牛時代に、
+講義後にナンパしたのが最初。
+私文は特にチャンスが多い。</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -59117,14 +59117,16 @@
       </c>
       <c r="B2005" t="inlineStr">
         <is>
-          <t>甘い言葉に耳を傾けたら人生詰み。 
-・「嫌ならやめていい」 
-・「無理しなくていい」 
-・「若い内に遊ぶべき」 
-・「他人と比べなくていい」 
-・「好きなことだけで生きる」  
-これらの甘言を真に受けた 
-19歳の私は実家でニートしながら ゲーム、ポルノ、TikTokの毎日だった。</t>
+          <t>甘い言葉に耳を傾けたら人生詰み。
+・「嫌ならやめていい」
+・「無理しなくていい」
+・「若い内に遊ぶべき」
+・「他人と比べなくていい」
+・「好きなことだけで生きる」
+これらの甘言を真に受けた
+19歳の私は実家でニートしながら
+ゲーム、ポルノ、TikTokの毎日だった。
+快楽主義の末路はプライドだけ高いゴミ人間。</t>
         </is>
       </c>
       <c r="C2005" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2135"/>
+  <dimension ref="A1:G2134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58939,33 +58939,10 @@
     <row r="1999">
       <c r="A1999" t="inlineStr">
         <is>
-          <t>2026-06-16 18:11:46</t>
+          <t>2026-06-16 06:56:00</t>
         </is>
       </c>
       <c r="B1999" t="inlineStr">
-        <is>
-          <t>これは苦労話ではなく単にジムが好きだっただけです。</t>
-        </is>
-      </c>
-      <c r="C1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:56:00</t>
-        </is>
-      </c>
-      <c r="B2000" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -58980,25 +58957,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -59009,25 +58986,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59035,25 +59012,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59068,25 +59045,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59097,25 +59074,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。
 ・「嫌ならやめていい」
@@ -59129,25 +59106,25 @@
 快楽主義の末路はプライドだけ高いゴミ人間。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59157,25 +59134,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59183,25 +59160,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59212,25 +59189,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2008" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59243,25 +59220,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59269,25 +59246,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59299,25 +59276,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -59325,25 +59302,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -59358,25 +59335,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -59387,25 +59364,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -59422,25 +59399,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2016" t="inlineStr">
+      <c r="B2015" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -59456,6 +59433,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2015" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2016" t="n">
         <v>0</v>
       </c>
@@ -59465,45 +59471,16 @@
       <c r="E2016" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2016" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2017">
       <c r="A2017" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2017" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2018" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -59531,25 +59508,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59561,25 +59538,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59592,25 +59569,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59621,25 +59598,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -59647,25 +59624,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -59675,30 +59652,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2023" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2022" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -59709,30 +59686,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2024" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2023" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -59742,30 +59719,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2025" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2024" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -59778,30 +59755,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2026" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2025" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -59812,55 +59789,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2028" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2027" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -59873,25 +59850,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -59902,25 +59879,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -59931,25 +59908,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2031" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+      <c r="C2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -59958,19 +59935,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -59987,19 +59964,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -60012,19 +59989,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60036,19 +60013,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60057,19 +60034,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60082,19 +60059,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60105,19 +60082,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60129,19 +60106,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60150,19 +60127,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60181,24 +60158,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2041" t="inlineStr">
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2040" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60210,19 +60187,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60237,19 +60214,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60263,19 +60240,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60286,19 +60263,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60308,38 +60285,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60348,19 +60325,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60372,19 +60349,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60402,24 +60379,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2050" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2049" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60430,24 +60407,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2051" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2050" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60457,24 +60434,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2052" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2051" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60483,19 +60460,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60509,19 +60486,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60534,19 +60511,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60559,19 +60536,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60585,19 +60562,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60618,19 +60595,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -60638,19 +60615,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -60658,19 +60635,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -60680,19 +60657,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -60701,19 +60678,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -60727,25 +60704,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -60759,30 +60736,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2064" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2063" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -60795,25 +60772,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -60828,25 +60805,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -60859,25 +60836,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="C2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -60887,25 +60864,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="C2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -60919,25 +60896,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="C2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -60960,25 +60937,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="C2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -60987,25 +60964,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="C2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61020,25 +60997,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="C2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61055,25 +61032,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="C2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61084,25 +61061,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="C2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61120,25 +61097,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="C2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61151,25 +61128,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="C2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61180,6 +61157,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2077" t="n">
         <v>0</v>
       </c>
@@ -61199,29 +61199,6 @@
         </is>
       </c>
       <c r="B2078" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2079" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61240,25 +61217,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61274,25 +61251,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61304,25 +61281,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61332,25 +61309,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61362,25 +61339,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61390,25 +61367,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61430,25 +61407,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61462,30 +61439,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2086" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2085" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61497,25 +61474,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61526,25 +61503,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61580,25 +61557,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61610,25 +61587,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -61644,25 +61621,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -61674,25 +61651,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -61721,50 +61698,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -61779,25 +61756,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -61808,25 +61785,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2096" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -61844,19 +61821,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -61877,19 +61854,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -61901,19 +61878,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -61925,19 +61902,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -61948,19 +61925,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -61974,19 +61951,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -61998,19 +61975,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62023,19 +62000,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62051,19 +62028,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62081,19 +62058,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62107,19 +62084,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62131,19 +62108,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62156,19 +62133,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62179,19 +62156,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62200,19 +62177,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62222,19 +62199,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62246,19 +62223,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62273,19 +62250,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62298,19 +62275,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62323,19 +62300,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62351,19 +62328,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62380,19 +62357,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62405,19 +62382,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62427,19 +62404,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62450,19 +62427,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62475,19 +62452,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62503,19 +62480,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62530,19 +62507,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62559,19 +62536,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62588,25 +62565,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -62636,25 +62613,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -62667,25 +62644,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="C2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -62694,30 +62671,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2129" t="inlineStr">
+      <c r="C2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2128" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -62728,19 +62705,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -62752,19 +62729,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -62775,19 +62752,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -62801,17 +62778,17 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" s="2" t="n">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -62821,17 +62798,17 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
+      <c r="E2133" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2135">
-      <c r="A2135" s="2" t="n">
+    <row r="2134">
+      <c r="A2134" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>モテ攻略に大学はターニングポイントになる。
 ・サークル、ゼミ、バイト
@@ -62844,7 +62821,7 @@
 私文は特にチャンスが多い。</t>
         </is>
       </c>
-      <c r="E2135" t="inlineStr">
+      <c r="E2134" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -58884,6 +58884,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="G1996" t="inlineStr">
+        <is>
+          <t>x_posts/images/HLK5N9OaIAAbhKs.jpg,x_posts/images/HLK5NyebcAETOtl.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="1997">
       <c r="A1997" t="inlineStr">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2134"/>
+  <dimension ref="A1:G2135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62832,6 +62832,36 @@
         </is>
       </c>
     </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>彼女持ちがモテるのは、
+「社会性」と「モテ」の証明になるから。
+まずまともな人、認定を簡単に受けることが出来る。
+そして、セスクができるということは
+性的価値の証明になる。
+大半のフツメンはこの2つのお墨付きを貰うのに、多大な労力を必要とする。
+しかし、彼女持ちor既婚者というだけでこの障壁をすっ飛ばすことが出来る。
+童貞がモテない理由はこの逆です。</t>
+        </is>
+      </c>
+      <c r="C2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2135"/>
+  <dimension ref="A1:G2136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62862,6 +62862,37 @@
         </is>
       </c>
     </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>ヒョロガリでもデカくなる男の特徴は
+・ベルト使う
+・減量＜増量
+・フリーウェイをやり込む
+・トレ前にカーボ、カフェイン
+・ささみブロッコリー＜米
+・記録をつけている
+・soundcloud聴いている
+絶対、デカくなります👍</t>
+        </is>
+      </c>
+      <c r="C2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2136"/>
+  <dimension ref="A1:G2137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62893,6 +62893,36 @@
         </is>
       </c>
     </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>童貞がまず目指すべきは量産型。
+・前髪をつくる
+・服は無地
+・キモさを減らす
+・健康体になる
+量産型には相応の再現性がある。
+フツメンでもそれなりにモテることができる。
+差別化を語るのは、その後でいい。</t>
+        </is>
+      </c>
+      <c r="C2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2137"/>
+  <dimension ref="A1:G2138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62923,6 +62923,37 @@
         </is>
       </c>
     </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>気弱な男は究極、
+「自分の損得」のみ考えて生きればいい。
+・安易にノリに合わせない
+・頼み事を断る
+・相手が不機嫌になったら逆ギレ
+もっと傲慢に図々しく生きろ。
+他人に冷たくなれという話ではない。
+優しくしてもいいし、他人を助けてもいい。
+ただし、判断基準は自分の利益に置こう。</t>
+        </is>
+      </c>
+      <c r="C2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2138"/>
+  <dimension ref="A1:G2137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58841,12 +58841,13 @@
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>2026-06-20 16:03:13</t>
+          <t>2026-06-19 19:34:04</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr">
         <is>
-          <t>発達障害だとこれが神経学的に難しいことは百も承知。</t>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
         </is>
       </c>
       <c r="C1995" t="n">
@@ -58858,45 +58859,21 @@
       <c r="E1995" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr">
+        <is>
+          <t>x_posts/images/HLK5N9OaIAAbhKs.jpg,x_posts/images/HLK5NyebcAETOtl.jpg</t>
         </is>
       </c>
     </row>
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B1996" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1996" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G1996" t="inlineStr">
-        <is>
-          <t>x_posts/images/HLK5N9OaIAAbhKs.jpg,x_posts/images/HLK5NyebcAETOtl.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B1997" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -58904,50 +58881,50 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1997" t="inlineStr">
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-16 06:56:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -58962,25 +58939,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -58991,25 +58968,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -59017,25 +58994,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59050,25 +59027,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59079,25 +59056,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。
 ・「嫌ならやめていい」
@@ -59111,25 +59088,25 @@
 快楽主義の末路はプライドだけ高いゴミ人間。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59139,25 +59116,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59165,25 +59142,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59194,25 +59171,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59225,25 +59202,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2008" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59251,25 +59228,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59281,25 +59258,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -59307,25 +59284,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -59340,25 +59317,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -59369,25 +59346,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -59404,25 +59381,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2014" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2014" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2015">
-      <c r="A2015" t="inlineStr">
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2015" t="inlineStr">
+      <c r="B2014" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -59438,6 +59415,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2014" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2015" t="n">
         <v>0</v>
       </c>
@@ -59447,45 +59453,16 @@
       <c r="E2015" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2015" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2016">
       <c r="A2016" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2016" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2017" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -59513,25 +59490,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59543,25 +59520,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59574,25 +59551,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59603,25 +59580,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -59629,25 +59606,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -59657,30 +59634,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2022" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2021" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -59691,30 +59668,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2023" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2022" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -59724,30 +59701,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2024" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2023" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -59760,30 +59737,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2025" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2024" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -59794,55 +59771,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2027" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2026" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -59855,25 +59832,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -59884,25 +59861,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -59913,25 +59890,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2030" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="C2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -59940,19 +59917,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -59969,19 +59946,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -59994,19 +59971,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -60018,19 +59995,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60039,19 +60016,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60064,19 +60041,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60087,19 +60064,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60111,19 +60088,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60132,19 +60109,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60163,24 +60140,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2040" t="inlineStr">
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2039" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60192,19 +60169,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60219,19 +60196,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60245,19 +60222,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60268,19 +60245,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60290,38 +60267,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60330,19 +60307,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60354,19 +60331,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60384,24 +60361,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2049" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2048" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60412,24 +60389,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2050" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2049" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60439,24 +60416,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2051" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2050" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60465,19 +60442,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60491,19 +60468,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60516,19 +60493,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60541,19 +60518,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60567,19 +60544,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60600,19 +60577,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -60620,19 +60597,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -60640,19 +60617,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -60662,19 +60639,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -60683,19 +60660,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -60709,25 +60686,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -60741,30 +60718,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2063" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2062" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -60777,25 +60754,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -60810,25 +60787,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -60841,25 +60818,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -60869,25 +60846,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="C2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -60901,25 +60878,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="C2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -60942,25 +60919,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="C2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -60969,25 +60946,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="C2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -61002,25 +60979,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="C2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61037,25 +61014,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="C2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61066,25 +61043,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="C2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61102,25 +61079,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="C2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61133,25 +61110,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
+      <c r="C2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2076" t="inlineStr">
+      <c r="B2075" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61162,6 +61139,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2076" t="n">
         <v>0</v>
       </c>
@@ -61181,29 +61181,6 @@
         </is>
       </c>
       <c r="B2077" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2078" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61222,25 +61199,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="C2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61256,25 +61233,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61286,25 +61263,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61314,25 +61291,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61344,25 +61321,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61372,25 +61349,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61412,25 +61389,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61444,30 +61421,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2085" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2084" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61479,25 +61456,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61508,25 +61485,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61562,25 +61539,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61592,25 +61569,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -61626,25 +61603,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -61656,25 +61633,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -61703,50 +61680,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -61761,25 +61738,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -61790,25 +61767,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -61826,19 +61803,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -61859,19 +61836,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -61883,19 +61860,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -61907,19 +61884,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -61930,19 +61907,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -61956,19 +61933,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -61980,19 +61957,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -62005,19 +61982,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62033,19 +62010,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62063,19 +62040,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62089,19 +62066,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62113,19 +62090,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62138,19 +62115,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62161,19 +62138,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62182,19 +62159,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62204,19 +62181,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62228,19 +62205,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62255,19 +62232,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62280,19 +62257,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62305,19 +62282,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62333,19 +62310,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62362,19 +62339,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62387,19 +62364,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62409,19 +62386,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62432,19 +62409,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62457,19 +62434,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62485,19 +62462,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62512,19 +62489,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62541,19 +62518,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62570,25 +62547,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -62618,25 +62595,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -62649,25 +62626,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -62676,30 +62653,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2128" t="inlineStr">
+      <c r="C2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2127" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -62710,19 +62687,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -62734,19 +62711,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -62757,19 +62734,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" t="inlineStr">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -62783,17 +62760,17 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" s="2" t="n">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -62803,17 +62780,17 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
+      <c r="E2132" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2134">
-      <c r="A2134" s="2" t="n">
+    <row r="2133">
+      <c r="A2133" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>モテ攻略に大学はターニングポイントになる。
 ・サークル、ゼミ、バイト
@@ -62826,19 +62803,19 @@
 私文は特にチャンスが多い。</t>
         </is>
       </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>彼女持ちがモテるのは、
 「社会性」と「モテ」の証明になるから。
@@ -62850,25 +62827,25 @@
 童貞がモテない理由はこの逆です。</t>
         </is>
       </c>
-      <c r="C2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="C2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>ヒョロガリでもデカくなる男の特徴は
 ・ベルト使う
@@ -62881,25 +62858,25 @@
 絶対、デカくなります👍</t>
         </is>
       </c>
-      <c r="C2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="C2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>童貞がまず目指すべきは量産型。
 ・前髪をつくる
@@ -62911,25 +62888,25 @@
 差別化を語るのは、その後でいい。</t>
         </is>
       </c>
-      <c r="C2137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="C2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>気弱な男は究極、
 「自分の損得」のみ考えて生きればいい。
@@ -62942,13 +62919,13 @@
 ただし、判断基準は自分の利益に置こう。</t>
         </is>
       </c>
-      <c r="C2138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2138" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2138" t="inlineStr">
+      <c r="C2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2137" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2137"/>
+  <dimension ref="A1:G2136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58594,34 +58594,6 @@
       </c>
       <c r="B1986" t="inlineStr">
         <is>
-          <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。
-別に金持ちになる必要はない。
-・外見
-・デート代
-ここに躊躇なく投資できる経済力を持て。
-これをクリアできなければ遊ぶ資格はない。</t>
-        </is>
-      </c>
-      <c r="C1986" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1986" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1986" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1987">
-      <c r="A1987" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="B1987" t="inlineStr">
-        <is>
           <t>「努力の過大評価」をやめると生きやすくなる。
 ・才能ないことに消耗しない
 ・得意を伸ばせる
@@ -58631,25 +58603,25 @@
 才能ないことに時間を費やせるほど、人生は長くない。</t>
         </is>
       </c>
-      <c r="C1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1987" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1988">
-      <c r="A1988" t="inlineStr">
+      <c r="C1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1988" t="inlineStr">
+      <c r="B1987" t="inlineStr">
         <is>
           <t>モテる男は精神設計から違う。
 非モテ：「これ実現できるかな」と考える
@@ -58662,25 +58634,25 @@
 だからモテる男は他のことも大体うまくいく。</t>
         </is>
       </c>
-      <c r="C1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1988" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1988" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1989">
-      <c r="A1989" t="inlineStr">
+      <c r="C1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="B1989" t="inlineStr">
+      <c r="B1988" t="inlineStr">
         <is>
           <t>睡眠のゴールデンタイムなどない。
 「22時〜2時が成長ホルモンの分泌ピーク」は都市伝説。
@@ -58690,25 +58662,25 @@
 固定観念を疑う習慣が、正しい知識につながる。</t>
         </is>
       </c>
-      <c r="C1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1989" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1989" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1990">
-      <c r="A1990" t="inlineStr">
+      <c r="C1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:15</t>
         </is>
       </c>
-      <c r="B1990" t="inlineStr">
+      <c r="B1989" t="inlineStr">
         <is>
           <t>「朝散歩」をやるだけで人生変わる。
 ・眠りの質が上がる
@@ -58717,25 +58689,25 @@
 曇りの日でもやった方がいい。</t>
         </is>
       </c>
-      <c r="C1990" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1990" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1990" t="inlineStr">
+      <c r="C1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1989" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1991">
-      <c r="A1991" t="inlineStr">
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
         <is>
           <t>2026-06-21 09:26:46</t>
         </is>
       </c>
-      <c r="B1991" t="inlineStr">
+      <c r="B1990" t="inlineStr">
         <is>
           <t>朝スマホをやめる方法
 "ベッドの横に歯磨きセットを置く。"
@@ -58743,6 +58715,30 @@
 地味なライフハック。</t>
         </is>
       </c>
+      <c r="C1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:41:41</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>起床3秒後のEAA❌
+起床3秒後の歯磨き⭕</t>
+        </is>
+      </c>
       <c r="C1991" t="n">
         <v>0</v>
       </c>
@@ -58758,34 +58754,10 @@
     <row r="1992">
       <c r="A1992" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-21 07:01:00</t>
         </is>
       </c>
       <c r="B1992" t="inlineStr">
-        <is>
-          <t>起床3秒後のEAA❌
-起床3秒後の歯磨き⭕</t>
-        </is>
-      </c>
-      <c r="C1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1992" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1992" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="1993">
-      <c r="A1993" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:01:00</t>
-        </is>
-      </c>
-      <c r="B1993" t="inlineStr">
         <is>
           <t>休日の鉄則 
 ①平日と同じ時間に起きる 
@@ -58798,25 +58770,25 @@
 他人から「つまんなそう」と言われる生活を続けられる奴が勝つ。</t>
         </is>
       </c>
-      <c r="C1993" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1993" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1993" t="inlineStr">
+      <c r="C1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1992" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1994">
-      <c r="A1994" t="inlineStr">
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
         <is>
           <t>2026-06-20 18:08:17</t>
         </is>
       </c>
-      <c r="B1994" t="inlineStr">
+      <c r="B1993" t="inlineStr">
         <is>
           <t>「非モテ＋貧乏」はまずは貧乏克服から取り掛かれ。  
 別に金持ちになる必要はない。  
@@ -58826,6 +58798,30 @@
 1年後にもアプリやクラブに女はいるから焦る必要ない。</t>
         </is>
       </c>
+      <c r="C1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-06-19 19:34:04</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
+失うものがない人たちには100%勝てません。</t>
+        </is>
+      </c>
       <c r="C1994" t="n">
         <v>0</v>
       </c>
@@ -58835,45 +58831,21 @@
       <c r="E1994" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+      <c r="G1994" t="inlineStr">
+        <is>
+          <t>x_posts/images/HLK5N9OaIAAbhKs.jpg,x_posts/images/HLK5NyebcAETOtl.jpg</t>
         </is>
       </c>
     </row>
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>2026-06-19 19:34:04</t>
+          <t>2026-06-17 18:00:28</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr">
-        <is>
-          <t>筋トレや格闘技で強くなったとしても、謙虚に生きましょう。
-失うものがない人たちには100%勝てません。</t>
-        </is>
-      </c>
-      <c r="C1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1995" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1995" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G1995" t="inlineStr">
-        <is>
-          <t>x_posts/images/HLK5N9OaIAAbhKs.jpg,x_posts/images/HLK5NyebcAETOtl.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="1996">
-      <c r="A1996" t="inlineStr">
-        <is>
-          <t>2026-06-17 18:00:28</t>
-        </is>
-      </c>
-      <c r="B1996" t="inlineStr">
         <is>
           <t>一番のストレス対策は“後回しをやめる”こと。
 「そろそろやらなきゃヤバい」というタスクが頭にある時は目の前のことを100%楽しむことはできない。
@@ -58881,50 +58853,50 @@
 もちろん、睡眠食事運動も言うまでもないがそれと同等に強力なストレス対策。</t>
         </is>
       </c>
-      <c r="C1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1996" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1996" t="inlineStr">
+      <c r="C1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1995" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="1997">
-      <c r="A1997" t="inlineStr">
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
         <is>
           <t>2026-06-16 19:36:50</t>
         </is>
       </c>
-      <c r="B1997" t="inlineStr">
+      <c r="B1996" t="inlineStr">
         <is>
           <t>他人の挑戦を馬鹿にしてはいけない理由は、
 あなたが挑戦する時に過去の自分が牙を向くから。
 倫理とモラルの問題ではなく自分が損します。</t>
         </is>
       </c>
-      <c r="C1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1997" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1997" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="1998">
-      <c r="A1998" t="inlineStr">
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
         <is>
           <t>2026-06-16 06:56:00</t>
         </is>
       </c>
-      <c r="B1998" t="inlineStr">
+      <c r="B1997" t="inlineStr">
         <is>
           <t>朝イチにおすすめのタスク 
 ・最重要タスク 
@@ -58939,25 +58911,25 @@
 頭が冴えてる時間にやりたくないタスクを置けば先延ばしは回避できる。</t>
         </is>
       </c>
-      <c r="C1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1998" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1998" t="inlineStr">
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="1999">
-      <c r="A1999" t="inlineStr">
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
         <is>
           <t>2026-06-15 20:57:00</t>
         </is>
       </c>
-      <c r="B1999" t="inlineStr">
+      <c r="B1998" t="inlineStr">
         <is>
           <t>夜のブルーライトが翌日を破壊する。 
 ・入眠の遅さ 
@@ -58968,25 +58940,25 @@
 デジタルデバイスを見ないことがベスト。</t>
         </is>
       </c>
-      <c r="C1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1999" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1999" t="inlineStr">
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
     </row>
-    <row r="2000">
-      <c r="A2000" t="inlineStr">
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
         <is>
           <t>2026-06-15 19:14:00</t>
         </is>
       </c>
-      <c r="B2000" t="inlineStr">
+      <c r="B1999" t="inlineStr">
         <is>
           <t>”モテる男がモテる” 
 小泉構文っぽいが本質が詰まっている。 
@@ -58994,25 +58966,25 @@
 この自信が余裕を生み、さらなるモテを生む。</t>
         </is>
       </c>
-      <c r="C2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2000" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2000" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2001">
-      <c r="A2001" t="inlineStr">
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
         <is>
           <t>2026-06-15 18:29:00</t>
         </is>
       </c>
-      <c r="B2001" t="inlineStr">
+      <c r="B2000" t="inlineStr">
         <is>
           <t>強者男性の特徴 
 ・陽キャ 
@@ -59027,25 +58999,25 @@
 身長以外はどうにでもなることも事実。</t>
         </is>
       </c>
-      <c r="C2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2001" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2001" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2002">
-      <c r="A2002" t="inlineStr">
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
         <is>
           <t>2026-06-15 18:01:00</t>
         </is>
       </c>
-      <c r="B2002" t="inlineStr">
+      <c r="B2001" t="inlineStr">
         <is>
           <t>「好きな人だけにモテたい」 
 これは絶対に叶わない願望。 
@@ -59056,25 +59028,25 @@
 ギャルゲーと現実は全く違う。</t>
         </is>
       </c>
-      <c r="C2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2002" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2002" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2003">
-      <c r="A2003" t="inlineStr">
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
         <is>
           <t>2026-06-15 17:21:00</t>
         </is>
       </c>
-      <c r="B2003" t="inlineStr">
+      <c r="B2002" t="inlineStr">
         <is>
           <t>甘い言葉に耳を傾けたら人生詰み。
 ・「嫌ならやめていい」
@@ -59088,25 +59060,25 @@
 快楽主義の末路はプライドだけ高いゴミ人間。</t>
         </is>
       </c>
-      <c r="C2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2003" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2003" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2004">
-      <c r="A2004" t="inlineStr">
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
         <is>
           <t>2026-06-15 15:58:14</t>
         </is>
       </c>
-      <c r="B2004" t="inlineStr">
+      <c r="B2003" t="inlineStr">
         <is>
           <t>脚トレがあなたにもたらすもの 
 ・根性 
@@ -59116,25 +59088,25 @@
 行ってまいります。</t>
         </is>
       </c>
-      <c r="C2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2004" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2004" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2005">
-      <c r="A2005" t="inlineStr">
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
         <is>
           <t>2026-06-14 20:00:01</t>
         </is>
       </c>
-      <c r="B2005" t="inlineStr">
+      <c r="B2004" t="inlineStr">
         <is>
           <t>非モテは競争から逃げた成れの果て。
 戦略的撤退は大事。
@@ -59142,25 +59114,25 @@
 恋愛はイス取りゲームです。</t>
         </is>
       </c>
-      <c r="C2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2005" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2005" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2006">
-      <c r="A2006" t="inlineStr">
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
         <is>
           <t>2026-06-14 19:40:00</t>
         </is>
       </c>
-      <c r="B2006" t="inlineStr">
+      <c r="B2005" t="inlineStr">
         <is>
           <t>ヒョロガリが摂るべきコスパ最強タンパク源
 ・サバ缶
@@ -59171,25 +59143,25 @@
 俺はここ3ヶ月プロテインは一切飲んでない。</t>
         </is>
       </c>
-      <c r="C2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2006" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2006" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2007">
-      <c r="A2007" t="inlineStr">
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
         <is>
           <t>2026-06-14 19:04:00</t>
         </is>
       </c>
-      <c r="B2007" t="inlineStr">
+      <c r="B2006" t="inlineStr">
         <is>
           <t>貧乏から立て直したかったら、
 ・スキル習得
@@ -59202,25 +59174,25 @@
 これでも無理なら実家や女の家に転がり込むか生活保護です。</t>
         </is>
       </c>
-      <c r="C2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2007" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2007" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2008">
-      <c r="A2008" t="inlineStr">
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
         <is>
           <t>2026-06-22 19:29:49</t>
         </is>
       </c>
-      <c r="B2008" t="inlineStr">
+      <c r="B2007" t="inlineStr">
         <is>
           <t>ジムの民度は会費に比例します。
 月2,000円と月10,000円で会員の本気度は違います。
@@ -59228,25 +59200,25 @@
 ジムの会費はマシンへの投資ではなく環境への投資です。</t>
         </is>
       </c>
-      <c r="C2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2008" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2008" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2009">
-      <c r="A2009" t="inlineStr">
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
         <is>
           <t>2026-06-22 20:20:50</t>
         </is>
       </c>
-      <c r="B2009" t="inlineStr">
+      <c r="B2008" t="inlineStr">
         <is>
           <t>底辺＝無敵。
 失うものがない奴はどう動いても
@@ -59258,25 +59230,25 @@
 あなたが底辺なら、それはスタート地点として最強です。</t>
         </is>
       </c>
-      <c r="C2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2009" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2009" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2010">
-      <c r="A2010" t="inlineStr">
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
         <is>
           <t>2026-06-23 14:44:27</t>
         </is>
       </c>
-      <c r="B2010" t="inlineStr">
+      <c r="B2009" t="inlineStr">
         <is>
           <t>人生がつまらなかったら、
 ギラギラしたコンテンツを見るといい。
@@ -59284,25 +59256,25 @@
 TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
         </is>
       </c>
-      <c r="C2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2010" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2010" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2011">
-      <c r="A2011" t="inlineStr">
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
         <is>
           <t>2026-06-23 15:18:14</t>
         </is>
       </c>
-      <c r="B2011" t="inlineStr">
+      <c r="B2010" t="inlineStr">
         <is>
           <t>弱男は誰も助けてくれないことを自覚しろ。
 ・親は老いる
@@ -59317,25 +59289,25 @@
 男で生まれた以上は自力で這い上がる他ない。</t>
         </is>
       </c>
-      <c r="C2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2011" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2011" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2012">
-      <c r="A2012" t="inlineStr">
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
         <is>
           <t>2026-06-23 10:00:00</t>
         </is>
       </c>
-      <c r="B2012" t="inlineStr">
+      <c r="B2011" t="inlineStr">
         <is>
           <t>不潔系非モテがやりがちなこと
 ・爪に垢
@@ -59346,25 +59318,25 @@
 これをやる男は清潔感どころか清潔度が低い。</t>
         </is>
       </c>
-      <c r="C2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2012" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2012" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2013">
-      <c r="A2013" t="inlineStr">
+      <c r="C2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
         <is>
           <t>2026-06-25 18:11:29</t>
         </is>
       </c>
-      <c r="B2013" t="inlineStr">
+      <c r="B2012" t="inlineStr">
         <is>
           <t>モテ発信でよく見る嘘
 ・処女なんていない
@@ -59381,25 +59353,25 @@
 インプ稼ぎの絶望情報を真に受けるな。</t>
         </is>
       </c>
-      <c r="C2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2013" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2013" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2014">
-      <c r="A2014" t="inlineStr">
+      <c r="C2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
         <is>
           <t>2026-06-25 18:43:04</t>
         </is>
       </c>
-      <c r="B2014" t="inlineStr">
+      <c r="B2013" t="inlineStr">
         <is>
           <t>3日坊主も、素晴らしい。
 男磨き界隈では「継続」が全てみたいな空気があるが、問題は何を継続するか。
@@ -59415,6 +59387,35 @@
 だから3日坊主も、素晴らしい。</t>
         </is>
       </c>
+      <c r="C2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2013" t="inlineStr">
+        <is>
+          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:07:20</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
+すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
+        </is>
+      </c>
       <c r="C2014" t="n">
         <v>0</v>
       </c>
@@ -59424,45 +59425,16 @@
       <c r="E2014" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="F2014" t="inlineStr">
-        <is>
-          <t>https://note.com/fuji_evisjap/n/n347107b0ebbe</t>
         </is>
       </c>
     </row>
     <row r="2015">
       <c r="A2015" t="inlineStr">
         <is>
-          <t>2026-06-25 19:07:20</t>
+          <t>2026-06-25 19:26:49</t>
         </is>
       </c>
       <c r="B2015" t="inlineStr">
-        <is>
-          <t>ドーパミン中毒が辛いのは「ゲーム、ポルノに充てていた時間を自己投資に使っていれば...」と後悔すること。
-すでにしているなら、数年後にまた同じ後悔をすることになる。これはゲームポルノにハマりすぎて睡眠障害で高校中退した俺だから言える。</t>
-        </is>
-      </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:26:49</t>
-        </is>
-      </c>
-      <c r="B2016" t="inlineStr">
         <is>
           <t>アメリカの理不尽なゲイ判定
 ・スタバ＝ゲイ
@@ -59490,25 +59462,25 @@
 今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-25 20:24:19</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59520,25 +59492,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59551,25 +59523,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59580,25 +59552,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -59606,25 +59578,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -59634,30 +59606,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2021" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2020" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -59668,30 +59640,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2022" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2021" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -59701,30 +59673,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2023" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2022" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -59737,30 +59709,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2024" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2023" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -59771,55 +59743,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2026" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2025" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -59832,25 +59804,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -59861,25 +59833,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -59890,25 +59862,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2029" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -59917,19 +59889,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -59946,19 +59918,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -59971,19 +59943,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -59995,19 +59967,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -60016,19 +59988,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60041,19 +60013,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60064,19 +60036,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60088,19 +60060,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60109,19 +60081,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60140,24 +60112,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2039" t="inlineStr">
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2038" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60169,19 +60141,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60196,19 +60168,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60222,19 +60194,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60245,19 +60217,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60267,38 +60239,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60307,19 +60279,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60331,19 +60303,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60361,24 +60333,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2048" t="inlineStr">
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2047" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60389,24 +60361,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2049" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2048" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60416,24 +60388,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2050" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2049" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60442,19 +60414,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60468,19 +60440,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60493,19 +60465,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60518,19 +60490,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60544,19 +60516,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60577,19 +60549,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -60597,19 +60569,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -60617,19 +60589,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -60639,19 +60611,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -60660,19 +60632,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -60686,25 +60658,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+      <c r="C2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -60718,30 +60690,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2062" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2061" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -60754,25 +60726,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -60787,25 +60759,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -60818,25 +60790,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -60846,25 +60818,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -60878,25 +60850,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="C2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -60919,25 +60891,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="C2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -60946,25 +60918,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="C2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -60979,25 +60951,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="C2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -61014,25 +60986,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="C2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61043,25 +61015,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="C2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61079,25 +61051,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="C2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61110,25 +61082,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2074" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2074" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2075">
-      <c r="A2075" t="inlineStr">
+      <c r="C2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2075" t="inlineStr">
+      <c r="B2074" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61139,6 +61111,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2075" t="n">
         <v>0</v>
       </c>
@@ -61158,29 +61153,6 @@
         </is>
       </c>
       <c r="B2076" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2077" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61199,25 +61171,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="C2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61233,25 +61205,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="C2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61263,25 +61235,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61291,25 +61263,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61321,25 +61293,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61349,25 +61321,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61389,25 +61361,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61421,30 +61393,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2084" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2083" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61456,25 +61428,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61485,25 +61457,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61539,25 +61511,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61569,25 +61541,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -61603,25 +61575,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -61633,25 +61605,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -61680,50 +61652,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -61738,25 +61710,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -61767,25 +61739,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -61803,19 +61775,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -61836,19 +61808,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -61860,19 +61832,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -61884,19 +61856,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -61907,19 +61879,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -61933,19 +61905,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -61957,19 +61929,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -61982,19 +61954,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -62010,19 +61982,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62040,19 +62012,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62066,19 +62038,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62090,19 +62062,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62115,19 +62087,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62138,19 +62110,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62159,19 +62131,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62181,19 +62153,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62205,19 +62177,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62232,19 +62204,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62257,19 +62229,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62282,19 +62254,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62310,19 +62282,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62339,19 +62311,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62364,19 +62336,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62386,19 +62358,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62409,19 +62381,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62434,19 +62406,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62462,19 +62434,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62489,19 +62461,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62518,19 +62490,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62547,25 +62519,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -62595,25 +62567,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -62626,25 +62598,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -62653,30 +62625,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2127" t="inlineStr">
+      <c r="C2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2126" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -62687,19 +62659,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -62711,19 +62683,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -62734,19 +62706,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" t="inlineStr">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -62760,17 +62732,17 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="A2132" s="2" t="n">
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -62780,17 +62752,17 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
+      <c r="E2131" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2133">
-      <c r="A2133" s="2" t="n">
+    <row r="2132">
+      <c r="A2132" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>モテ攻略に大学はターニングポイントになる。
 ・サークル、ゼミ、バイト
@@ -62803,19 +62775,19 @@
 私文は特にチャンスが多い。</t>
         </is>
       </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>彼女持ちがモテるのは、
 「社会性」と「モテ」の証明になるから。
@@ -62827,25 +62799,25 @@
 童貞がモテない理由はこの逆です。</t>
         </is>
       </c>
-      <c r="C2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="C2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>ヒョロガリでもデカくなる男の特徴は
 ・ベルト使う
@@ -62858,25 +62830,25 @@
 絶対、デカくなります👍</t>
         </is>
       </c>
-      <c r="C2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="C2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>童貞がまず目指すべきは量産型。
 ・前髪をつくる
@@ -62888,25 +62860,25 @@
 差別化を語るのは、その後でいい。</t>
         </is>
       </c>
-      <c r="C2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="C2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>気弱な男は究極、
 「自分の損得」のみ考えて生きればいい。
@@ -62919,13 +62891,13 @@
 ただし、判断基準は自分の利益に置こう。</t>
         </is>
       </c>
-      <c r="C2137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2137" t="inlineStr">
+      <c r="C2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2136" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2136"/>
+  <dimension ref="A1:G2137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62903,6 +62903,29 @@
         </is>
       </c>
     </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>童貞がモテ攻略すると消えるもの
+・ルッキズム
+・女への焦り
+・異性への幻想
+・チン騎士マインド
+容姿は大事だが、多少チー牛臭くても積極性が合った方がモテることが分かる。　
+また媚びることでしか女と関われない奴と一線を画すことができる。</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2137"/>
+  <dimension ref="A1:G2138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62926,6 +62926,32 @@
         </is>
       </c>
     </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>テストステロンは不調を凌駕する。
+・寝不足
+・ストレス
+・3発の射精
+・二日酔い
+テストステロンが高ければ、
+数日で回復する。
+俺はここ数年、禁欲が失敗しても、
+筋トレしまくってステーキと卵食べて、
+何とかなっている。</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2138"/>
+  <dimension ref="A1:G2139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62952,6 +62952,31 @@
         </is>
       </c>
     </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>「筋トレは風邪ひきやすくなる」は嘘。
+確かに
+・ささみブロッコリー
+・間食にバナナプロテイン
+・体脂肪は10％以下をキープ
+みたいな事やってたら、当然免疫は下がる。
+俺は幼少期は病弱だったけど、
+ここ2年風邪ひいてない。
+筋トレに出会って良かったです。</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2139"/>
+  <dimension ref="A1:G2138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59431,56 +59431,10 @@
     <row r="2015">
       <c r="A2015" t="inlineStr">
         <is>
-          <t>2026-06-25 19:26:49</t>
+          <t>2026-06-25 20:24:19</t>
         </is>
       </c>
       <c r="B2015" t="inlineStr">
-        <is>
-          <t>アメリカの理不尽なゲイ判定
-・スタバ＝ゲイ
-・スキニージーンズ＝ゲイ
-・ドアを丁寧に閉めたらゲイ
-・右ピアス＆タトゥー＝ゲイ
-・信号を守ったらゲイ
-・シートベルト閉めたらゲイ
-・ウィンカー出したらゲイ
-・おしゃれしたらゲイ
-・Kポップ＝ゲイポップ
-・スクワットパッド＝ゲイ
-・カクテル＝ゲイ
-逆にマッチョ認定される人の特徴
-・信号無視
-・謝らない
-・BIG3をやる
-・葉巻を吸う
-・バーボンを飲む
-・病院に行かない
-・女の名前を覚えてない
-・Googleマップを使わない
-・寒くても上着を着ない
-・ステーキを素手で食う
-今日の朝、椎名林檎聴きながら眉毛整えてた俺はゲイ。</t>
-        </is>
-      </c>
-      <c r="C2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2015" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2015" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
-        <is>
-          <t>2026-06-25 20:24:19</t>
-        </is>
-      </c>
-      <c r="B2016" t="inlineStr">
         <is>
           <t>怠惰な弱者男性の悪習慣
 ・独り呑み
@@ -59492,25 +59446,25 @@
 「今日はいいでしょ」が未来を壊す。</t>
         </is>
       </c>
-      <c r="C2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2017">
-      <c r="A2017" t="inlineStr">
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
         <is>
           <t>2026-06-26 18:33:21</t>
         </is>
       </c>
-      <c r="B2017" t="inlineStr">
+      <c r="B2016" t="inlineStr">
         <is>
           <t>結局、自分を救えるのは自分しかいない。
 メンヘラ女はドシハナやチン騎士が助けてくれます。
@@ -59523,25 +59477,25 @@
 誰かに助けてもらおうとしている時間が、傷を深くする。</t>
         </is>
       </c>
-      <c r="C2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2017" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2017" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2018">
-      <c r="A2018" t="inlineStr">
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
         <is>
           <t>2026-06-26 18:54:29</t>
         </is>
       </c>
-      <c r="B2018" t="inlineStr">
+      <c r="B2017" t="inlineStr">
         <is>
           <t>フツメンは底辺。
 「平均的な容姿の男は平均的にモテる」と思われがちだが、実は違う。
@@ -59552,25 +59506,25 @@
 ここを一定以上にしてから戦場に立て。</t>
         </is>
       </c>
-      <c r="C2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2018" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2018" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2019">
-      <c r="A2019" t="inlineStr">
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
         <is>
           <t>2026-06-26 19:25:29</t>
         </is>
       </c>
-      <c r="B2019" t="inlineStr">
+      <c r="B2018" t="inlineStr">
         <is>
           <t>舐められる男は相手に尽くす。
 「言われた以上の事をやるべき」のマインドの男は、
@@ -59578,25 +59532,25 @@
 そうじゃなくて「契約に書かれたことはやる。それ以外は知らん。」このイギリス警備員のマインドを持つべきやね。</t>
         </is>
       </c>
-      <c r="C2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2019" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2019" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2020">
-      <c r="A2020" t="inlineStr">
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
         <is>
           <t>2026-06-27 15:13:25</t>
         </is>
       </c>
-      <c r="B2020" t="inlineStr">
+      <c r="B2019" t="inlineStr">
         <is>
           <t>貧乏人なら自己投資一択。
 資産1億あれば年利4%で寝てても400万。
@@ -59606,30 +59560,30 @@
 貧乏人が投資で得られる利益なんてたかが知れている。</t>
         </is>
       </c>
-      <c r="C2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2020" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2020" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2020" t="inlineStr">
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2019" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2021">
-      <c r="A2021" t="inlineStr">
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
         <is>
           <t>2026-06-29 18:43:45</t>
         </is>
       </c>
-      <c r="B2021" t="inlineStr">
+      <c r="B2020" t="inlineStr">
         <is>
           <t>「努力できる環境」は作れます。
 やり方は毎日○○を見ること。
@@ -59640,30 +59594,30 @@
 これなら仲間がいなくても余裕で出来る。</t>
         </is>
       </c>
-      <c r="C2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2021" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2021" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2021" t="inlineStr">
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2020" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2022">
-      <c r="A2022" t="inlineStr">
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
         <is>
           <t>2026-06-29 19:32:05</t>
         </is>
       </c>
-      <c r="B2022" t="inlineStr">
+      <c r="B2021" t="inlineStr">
         <is>
           <t>女との会話で面白いことは言わなくていい。
 女に人気な芸人やYouTuber見てみ？
@@ -59673,30 +59627,30 @@
 普通の事を1.2倍のテンションで言っておけばいいだけ。</t>
         </is>
       </c>
-      <c r="C2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2022" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2022" t="inlineStr">
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2021" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2023">
-      <c r="A2023" t="inlineStr">
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
         <is>
           <t>2026-06-29 20:42:13</t>
         </is>
       </c>
-      <c r="B2023" t="inlineStr">
+      <c r="B2022" t="inlineStr">
         <is>
           <t>弱者男性には「人に迷惑かけるな」の教育が施されすぎている。
 だから、
@@ -59709,30 +59663,30 @@
 そのかわり恩を倍で返しましょう。</t>
         </is>
       </c>
-      <c r="C2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2023" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2023" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2023" t="inlineStr">
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2022" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2024">
-      <c r="A2024" t="inlineStr">
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2024" t="inlineStr">
+      <c r="B2023" t="inlineStr">
         <is>
           <t>「20代の半分はパパ活してる」
 「女の方が浮気する」
@@ -59743,55 +59697,55 @@
 でもモテてからもなおゴミ捕まえてたら何かがおかしい。</t>
         </is>
       </c>
-      <c r="C2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2024" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2024" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2025">
-      <c r="A2025" t="inlineStr">
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
         <is>
           <t>2026-06-30 00:00:01</t>
         </is>
       </c>
-      <c r="B2025" t="inlineStr">
+      <c r="B2024" t="inlineStr">
         <is>
           <t>「コンビニ飯800円は高い」とか舐めんな。
 ヒョロガリと貧乏人は800円使って、
 スーパーで全卵40個買え。</t>
         </is>
       </c>
-      <c r="C2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2025" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2025" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2025" t="inlineStr">
+      <c r="C2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2024" t="inlineStr">
         <is>
           <t>images/conbini_egg.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2026">
-      <c r="A2026" t="inlineStr">
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:00</t>
         </is>
       </c>
-      <c r="B2026" t="inlineStr">
+      <c r="B2025" t="inlineStr">
         <is>
           <t>外見レベルを下げる習慣
 ・口呼吸
@@ -59804,25 +59758,25 @@
 大分、良くなりました。　保存</t>
         </is>
       </c>
-      <c r="C2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2026" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2026" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2027">
-      <c r="A2027" t="inlineStr">
+      <c r="C2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:01</t>
         </is>
       </c>
-      <c r="B2027" t="inlineStr">
+      <c r="B2026" t="inlineStr">
         <is>
           <t>「努力は遺伝で決まる」
 ↑
@@ -59833,25 +59787,25 @@
 これ自体も遺伝で決まるのかな？</t>
         </is>
       </c>
-      <c r="C2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2027" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2027" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" t="inlineStr">
+      <c r="C2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
         <is>
           <t>2026-07-04 00:00:02</t>
         </is>
       </c>
-      <c r="B2028" t="inlineStr">
+      <c r="B2027" t="inlineStr">
         <is>
           <t>スマホ中毒は生産性ゼロ
 ・芸能人のスキャンダル
@@ -59862,25 +59816,25 @@
 安心して自分の人生に集中しましょう。</t>
         </is>
       </c>
-      <c r="C2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2028" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2029">
-      <c r="A2029" t="inlineStr">
+      <c r="C2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="B2029" t="inlineStr">
+      <c r="B2028" t="inlineStr">
         <is>
           <t>20歳前後の非モテは単に運が悪かっただけ。
 この時期のモテは遺伝・家庭環境・コミュニティで決まる。だから引け目を感じる必要はない。
@@ -59889,19 +59843,19 @@
 努力で埋まる差はあなたが思っているほど多い。</t>
         </is>
       </c>
-      <c r="E2029" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2030">
-      <c r="A2030" t="inlineStr">
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
         <is>
           <t>2026-07-07 00:00:01</t>
         </is>
       </c>
-      <c r="B2030" t="inlineStr">
+      <c r="B2029" t="inlineStr">
         <is>
           <t>非モテほどオナ禁すべきじゃない。
 セ〇クスできない非モテがシコらずにどう発散するんだって話。
@@ -59918,19 +59872,19 @@
 テストステロンは筋トレ・睡眠・食事で上げろ。</t>
         </is>
       </c>
-      <c r="E2030" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2031">
-      <c r="A2031" t="inlineStr">
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="B2031" t="inlineStr">
+      <c r="B2030" t="inlineStr">
         <is>
           <t>非モテは筋トレに救いを求め過ぎない方がいい。
 「怠けててもジムに行けば、
@@ -59943,19 +59897,19 @@
 ジムの王様は外では通用しない。</t>
         </is>
       </c>
-      <c r="E2031" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2032">
-      <c r="A2032" t="inlineStr">
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:01</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr">
+      <c r="B2031" t="inlineStr">
         <is>
           <t>スマホ中毒者はオフラインの時間を設けよう。
 ・読書習慣
@@ -59967,19 +59921,19 @@
 習慣化して意識を自分の人生に戻せ。</t>
         </is>
       </c>
-      <c r="E2032" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2033">
-      <c r="A2033" t="inlineStr">
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:02</t>
         </is>
       </c>
-      <c r="B2033" t="inlineStr">
+      <c r="B2032" t="inlineStr">
         <is>
           <t>ヒョロガリは単に食べていないだけ。
 消費カロリー以下の食事量なら、筋肉を作る材料がないから筋トレしてもデカくならない。
@@ -59988,19 +59942,19 @@
 ヒョロガリは筋トレの前に「食事量」にこだわれ。</t>
         </is>
       </c>
-      <c r="E2033" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2034">
-      <c r="A2034" t="inlineStr">
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:03</t>
         </is>
       </c>
-      <c r="B2034" t="inlineStr">
+      <c r="B2033" t="inlineStr">
         <is>
           <t>筋トレから逃げている童貞の特徴
 ・病的ヒョロガリ
@@ -60013,19 +59967,19 @@
 ヒョロガリが筋トレをやればプラスにしかならない。</t>
         </is>
       </c>
-      <c r="E2034" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2035">
-      <c r="A2035" t="inlineStr">
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:04</t>
         </is>
       </c>
-      <c r="B2035" t="inlineStr">
+      <c r="B2034" t="inlineStr">
         <is>
           <t>筋トレに逃げている童貞の特徴
 ・モテボディより上の追求
@@ -60036,19 +59990,19 @@
 ジムの王様は恋愛市場で通用しない。</t>
         </is>
       </c>
-      <c r="E2035" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2036">
-      <c r="A2036" t="inlineStr">
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:05</t>
         </is>
       </c>
-      <c r="B2036" t="inlineStr">
+      <c r="B2035" t="inlineStr">
         <is>
           <t>ストレートネックの治し方
 ・視力の矯正
@@ -60060,19 +60014,19 @@
 大事になる前に、治すに越したことはない。</t>
         </is>
       </c>
-      <c r="E2036" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" t="inlineStr">
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:06</t>
         </is>
       </c>
-      <c r="B2037" t="inlineStr">
+      <c r="B2036" t="inlineStr">
         <is>
           <t>凡人は何かを捨てるしかない。
 ・モテたいなら、恥を捨ててアプローチ
@@ -60081,19 +60035,19 @@
 削ぎ落した時にしか最大出力は生まれない。</t>
         </is>
       </c>
-      <c r="E2037" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2038">
-      <c r="A2038" t="inlineStr">
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:07</t>
         </is>
       </c>
-      <c r="B2038" t="inlineStr">
+      <c r="B2037" t="inlineStr">
         <is>
           <t>左手の人差し指よりも、薬指の方が長い男はテストステロン値が高い。
 これ、スピではなくガチです。 
@@ -60112,24 +60066,24 @@
 0.95よりも低いとテストステロンが高い傾向。</t>
         </is>
       </c>
-      <c r="E2038" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2038" t="inlineStr">
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2037" t="inlineStr">
         <is>
           <t>x_posts/images/GymWeYeakAAvdDQ.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2039">
-      <c r="A2039" t="inlineStr">
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
         <is>
           <t>2026-07-09 00:00:08</t>
         </is>
       </c>
-      <c r="B2039" t="inlineStr">
+      <c r="B2038" t="inlineStr">
         <is>
           <t>「積み上げ」に勝るモノなし。
 底辺高の奴が、幼少期から積み上げている受験エリートに勝てるわけがない。
@@ -60141,19 +60095,19 @@
 奇跡による逆転ではなく、積み上げによる必然的勝利を狙え。</t>
         </is>
       </c>
-      <c r="E2039" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2040">
-      <c r="A2040" t="inlineStr">
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:09</t>
         </is>
       </c>
-      <c r="B2040" t="inlineStr">
+      <c r="B2039" t="inlineStr">
         <is>
           <t>カフェインは毒にも薬にもなる。
 薬になる使い方
@@ -60168,19 +60122,19 @@
 神が与えた薬になる。</t>
         </is>
       </c>
-      <c r="E2040" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2041">
-      <c r="A2041" t="inlineStr">
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:00</t>
         </is>
       </c>
-      <c r="B2041" t="inlineStr">
+      <c r="B2040" t="inlineStr">
         <is>
           <t>スマホ中毒が人生の足枷になる。
 Xでノウハウだけ集め、
@@ -60194,19 +60148,19 @@
 自分の人生を創造する側に回れ。</t>
         </is>
       </c>
-      <c r="E2041" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042">
-      <c r="A2042" t="inlineStr">
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:01</t>
         </is>
       </c>
-      <c r="B2042" t="inlineStr">
+      <c r="B2041" t="inlineStr">
         <is>
           <t>メンタル強者は「人生が無価値」だと分かっている。
 地球の歴史が1日なら、
@@ -60217,19 +60171,19 @@
 どうせ無価値なら、好きに生きた方がいい。</t>
         </is>
       </c>
-      <c r="E2042" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2043">
-      <c r="A2043" t="inlineStr">
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:02</t>
         </is>
       </c>
-      <c r="B2043" t="inlineStr">
+      <c r="B2042" t="inlineStr">
         <is>
           <t>頭に投資しろ。
 金は盗まれるが、頭脳が盗まれることはない。
@@ -60239,38 +60193,38 @@
 IQ90以上あれば、誰でも知力は伸ばせる。</t>
         </is>
       </c>
-      <c r="E2043" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2044">
-      <c r="A2044" t="inlineStr">
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:03</t>
         </is>
       </c>
-      <c r="B2044" t="inlineStr">
+      <c r="B2043" t="inlineStr">
         <is>
           <t>人生がつまらない奴は、楽しいことを探していないだけ。
 だから、ポジティブ日記を習慣にするといい。見返すためではなく「今日の良かったこと」を書く義務を課すことで、楽しいことを無意識に作り、探すようになる。
 スピではなく、行動が変わるという話。</t>
         </is>
       </c>
-      <c r="E2044" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2045">
-      <c r="A2045" t="inlineStr">
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
         <is>
           <t>2026-07-11 00:00:04</t>
         </is>
       </c>
-      <c r="B2045" t="inlineStr">
+      <c r="B2044" t="inlineStr">
         <is>
           <t>習慣化のコツは小さく始めること。
 「やる気の自然発生」に期待するのが間違い。
@@ -60279,19 +60233,19 @@
 腕立て1回、ベッドメイク、散歩1分。それだけでいい。始めてしまえば、中途半端でやめることが出来なくなる。</t>
         </is>
       </c>
-      <c r="E2045" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2046">
-      <c r="A2046" t="inlineStr">
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
         <is>
           <t>2026-07-16 00:00:00</t>
         </is>
       </c>
-      <c r="B2046" t="inlineStr">
+      <c r="B2045" t="inlineStr">
         <is>
           <t>スマホ中毒には”外出”が有効。
 とりあえず、仕事道具だけ持ってカフェや図書館に行け。
@@ -60303,19 +60257,19 @@
 繰り返すことで、執着が薄れてゆく。</t>
         </is>
       </c>
-      <c r="E2046" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2047">
-      <c r="A2047" t="inlineStr">
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2047" t="inlineStr">
+      <c r="B2046" t="inlineStr">
         <is>
           <t>肌を綺麗にしたい男へ。
 意外と重要じゃなかったもの
@@ -60333,24 +60287,24 @@
 身体の内側からケアすれば、かなり変わる。</t>
         </is>
       </c>
-      <c r="E2047" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2047" t="inlineStr">
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2046" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2048">
-      <c r="A2048" t="inlineStr">
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2048" t="inlineStr">
+      <c r="B2047" t="inlineStr">
         <is>
           <t>スマホ廃人時代の私
 ・朝スマホで1時間浪費
@@ -60361,24 +60315,24 @@
 今考えたら「出来るわけないだろ」と思う。</t>
         </is>
       </c>
-      <c r="E2048" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2048" t="inlineStr">
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2047" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2049">
-      <c r="A2049" t="inlineStr">
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
         <is>
           <t>2026-07-27 00:00:00</t>
         </is>
       </c>
-      <c r="B2049" t="inlineStr">
+      <c r="B2048" t="inlineStr">
         <is>
           <t>弱者はやらない理由を探し始める。
 非モテほど「モテても意味ない」と言い出す。
@@ -60388,24 +60342,24 @@
 手にしてない者が語る資格はない。</t>
         </is>
       </c>
-      <c r="E2049" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2049" t="inlineStr">
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2048" t="inlineStr">
         <is>
           <t>https://x.com/puregrinding23/status/2058145954361123021</t>
         </is>
       </c>
     </row>
-    <row r="2050">
-      <c r="A2050" t="inlineStr">
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2050" t="inlineStr">
+      <c r="B2049" t="inlineStr">
         <is>
           <t>ポルノ中毒≒SNS中毒
 ポルノ中毒者は、SNSのソフトポルノ（エロ広告、TikTokなどの微エロ）がトリガーとなり、ポルノを見たい欲に駆られることが多い。
@@ -60414,19 +60368,19 @@
 そうすれば、ポルノ中毒も自然と改善していく。</t>
         </is>
       </c>
-      <c r="E2050" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2051">
-      <c r="A2051" t="inlineStr">
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2051" t="inlineStr">
+      <c r="B2050" t="inlineStr">
         <is>
           <t>𝕏はゴミの掃き溜め。
 収益性が高まってから、
@@ -60440,19 +60394,19 @@
 おすすめは見れない設定にし、本当に見たい発信者だけフォローしています。</t>
         </is>
       </c>
-      <c r="E2051" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2052">
-      <c r="A2052" t="inlineStr">
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="B2052" t="inlineStr">
+      <c r="B2051" t="inlineStr">
         <is>
           <t>人生を変えたいなら、新しいものを探すな。
 ・BIG3
@@ -60465,19 +60419,19 @@
 最近は「古い＝悪い」と飛躍しているアホが多すぎる。</t>
         </is>
       </c>
-      <c r="E2052" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2053">
-      <c r="A2053" t="inlineStr">
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2053" t="inlineStr">
+      <c r="B2052" t="inlineStr">
         <is>
           <t>情弱ほど「新しいもの」が大好き。
 ・民間療法
@@ -60490,19 +60444,19 @@
 何十年、何百年と生き残っているのには、それなりの理由がある。https://x.com/puregrinding23/status/2082031054207226208</t>
         </is>
       </c>
-      <c r="E2053" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2054">
-      <c r="A2054" t="inlineStr">
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2054" t="inlineStr">
+      <c r="B2053" t="inlineStr">
         <is>
           <t>習慣化には「体内時計」がかなり重要。
 整えるには、
@@ -60516,19 +60470,19 @@
 習慣は、意志力よりも生活リズムで決まる。</t>
         </is>
       </c>
-      <c r="E2054" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2055">
-      <c r="A2055" t="inlineStr">
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
         <is>
           <t>2026-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="B2055" t="inlineStr">
+      <c r="B2054" t="inlineStr">
         <is>
           <t>ドパガキが取り入れるべきマインドフルネス
 🟠 Bティア
@@ -60549,19 +60503,19 @@
 小さな「無の時間」を増やすことで、徐々にスマホへの依存は減っていく。</t>
         </is>
       </c>
-      <c r="E2055" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2056">
-      <c r="A2056" t="inlineStr">
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2056" t="inlineStr">
+      <c r="B2055" t="inlineStr">
         <is>
           <t>チー牛が女に少し優しくされて、すぐ好きになってしまうのは自然現象。
 他に選択肢がないから当たり前。
@@ -60569,19 +60523,19 @@
 そんなチー牛に「余裕を持て」「女の前でキョドるな」と言っても無駄で、もっと根本的に非モテを解決しなくてはいけない。</t>
         </is>
       </c>
-      <c r="E2056" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2057">
-      <c r="A2057" t="inlineStr">
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2057" t="inlineStr">
+      <c r="B2056" t="inlineStr">
         <is>
           <t>ゲーム中毒が奪うのは「時間」だけじゃない。
 ゲーム内のレベル上げでドーパミンを得ることにより「自己成長欲求」までも奪う。
@@ -60589,19 +60543,19 @@
 ゲーム中毒のまま10年たった未来を想像して絶望した方がいい。否が応でもやめたくなるから。</t>
         </is>
       </c>
-      <c r="E2057" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2058">
-      <c r="A2058" t="inlineStr">
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
         <is>
           <t>2026-07-30 00:00:00</t>
         </is>
       </c>
-      <c r="B2058" t="inlineStr">
+      <c r="B2057" t="inlineStr">
         <is>
           <t>筋トレを「自己規律」だと思っているうちは、ジムに通わない方がいい。
 まずは自重トレで筋トレを好きになれ。
@@ -60611,19 +60565,19 @@
 私にとってジムはモテや自己規律ではなく完全に趣味。怪我と忙殺以外で休んだことはない。</t>
         </is>
       </c>
-      <c r="E2058" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2059">
-      <c r="A2059" t="inlineStr">
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
-      <c r="B2059" t="inlineStr">
+      <c r="B2058" t="inlineStr">
         <is>
           <t>非モテほど「金」「筋肉」があればモテると思っているが実際は、"もともとモテる男"が筋肉をつけ、金を稼いでさらにモテているだけ。
 イケオジも同じ。
@@ -60632,19 +60586,19 @@
 一芸特化はその後で良い。</t>
         </is>
       </c>
-      <c r="E2059" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2060">
-      <c r="A2060" t="inlineStr">
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2060" t="inlineStr">
+      <c r="B2059" t="inlineStr">
         <is>
           <t>筋トレしてもモテない人は、
 ・顔
@@ -60658,25 +60612,25 @@
 筋トレで体重39kgから倍近く増やしたけど、やってきたのはそれだけじゃない。</t>
         </is>
       </c>
-      <c r="C2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2060" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2060" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2061">
-      <c r="A2061" t="inlineStr">
+      <c r="C2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2061" t="inlineStr">
+      <c r="B2060" t="inlineStr">
         <is>
           <t>今、スマホ中毒による「ブレイン・ロット（脳疲労）」がやばい。
 ショートを何気なくスクロールするだけで、あなたの知能は低下します。
@@ -60690,30 +60644,30 @@
 TikTokは見ない方がいいです。</t>
         </is>
       </c>
-      <c r="C2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2061" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2061" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2061" t="inlineStr">
+      <c r="C2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2060" t="inlineStr">
         <is>
           <t>x_posts/images/HP_-d-tbAAAn4ui.jpg</t>
         </is>
       </c>
     </row>
-    <row r="2062">
-      <c r="A2062" t="inlineStr">
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2062" t="inlineStr">
+      <c r="B2061" t="inlineStr">
         <is>
           <t>都合が悪くなったら、 
 「真の○○は..」と言って勝手に言葉の定義狭めてくる奴、マジで嫌い。  
@@ -60726,25 +60680,25 @@
 認めたくないのは分かるけども。</t>
         </is>
       </c>
-      <c r="C2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2062" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2063">
-      <c r="A2063" t="inlineStr">
+      <c r="C2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2063" t="inlineStr">
+      <c r="B2062" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 習慣化は「距離」が命。
@@ -60759,25 +60713,25 @@
 環境を変えれば、習慣は勝手に変わる。</t>
         </is>
       </c>
-      <c r="C2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2063" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2063" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2064">
-      <c r="A2064" t="inlineStr">
+      <c r="C2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2064" t="inlineStr">
+      <c r="B2063" t="inlineStr">
         <is>
           <t>成長している時は常にダサい。
 ・男磨き全般
@@ -60790,25 +60744,25 @@
 まずダサい時期を乗り越えろ。</t>
         </is>
       </c>
-      <c r="C2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2064" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2064" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2065">
-      <c r="A2065" t="inlineStr">
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2065" t="inlineStr">
+      <c r="B2064" t="inlineStr">
         <is>
           <t>モテにおいて先天性は残酷です。
 髪型を変えただけでモテる人もいれば、
@@ -60818,25 +60772,25 @@
 諦めて撤退することが幸福度を上げる場合もあります。</t>
         </is>
       </c>
-      <c r="C2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2065" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066" t="inlineStr">
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2066" t="inlineStr">
+      <c r="B2065" t="inlineStr">
         <is>
           <t>本命にならない女性一覧
 ・店員に態度悪い
@@ -60850,25 +60804,25 @@
 お断り😤✋</t>
         </is>
       </c>
-      <c r="C2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2066" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" t="inlineStr">
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2067" t="inlineStr">
+      <c r="B2066" t="inlineStr">
         <is>
           <t>あなたの夢や野望が叶わないのは、
 スマホのせい。
@@ -60891,25 +60845,25 @@
 自分が一番理解している。</t>
         </is>
       </c>
-      <c r="C2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2067" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2068">
-      <c r="A2068" t="inlineStr">
+      <c r="C2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B2068" t="inlineStr">
+      <c r="B2067" t="inlineStr">
         <is>
           <t>自己満男磨きと呼ばれる「コールドシャワー」「オナ禁」「ジャーナル」etc.は別にモテる習慣ではない。
 これらはあくまで怠惰を治し、自己規律を作る目的で有効な習慣。　
@@ -60918,25 +60872,25 @@
 俺もここから始めた。</t>
         </is>
       </c>
-      <c r="C2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2068" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2068" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2069">
-      <c r="A2069" t="inlineStr">
+      <c r="C2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2069" t="inlineStr">
+      <c r="B2068" t="inlineStr">
         <is>
           <t>努力はブルーオーシャン。
 まず50%は「どうせ無理だから..」
@@ -60951,25 +60905,25 @@
 勝手に競争相手はいなくなる。</t>
         </is>
       </c>
-      <c r="C2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2069" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2069" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2070">
-      <c r="A2070" t="inlineStr">
+      <c r="C2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2070" t="inlineStr">
+      <c r="B2069" t="inlineStr">
         <is>
           <t>一日で鬱っぽさを晴らす方法
 ・朝散歩
@@ -60986,25 +60940,25 @@
 そしたら翌日には余裕で回復している。</t>
         </is>
       </c>
-      <c r="C2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2070" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2070" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2071">
-      <c r="A2071" t="inlineStr">
+      <c r="C2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2071" t="inlineStr">
+      <c r="B2070" t="inlineStr">
         <is>
           <t>弱者男性は"自分の要求を通す"ことに抵抗がある。
 店員に「水ください」すら言えない。
@@ -61015,25 +60969,25 @@
 自分の要求すら口に出せない奴が女を口説くなんて無理。</t>
         </is>
       </c>
-      <c r="C2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2071" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2071" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2072">
-      <c r="A2072" t="inlineStr">
+      <c r="C2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B2072" t="inlineStr">
+      <c r="B2071" t="inlineStr">
         <is>
           <t>筋トレしてもデカくならない人は高重量から逃げている。
 ・反動を使ってはいけない
@@ -61051,25 +61005,25 @@
 その上で、初心者こそ高重量にチャレンジするセットを設けることで、ストリクトセットの重量も上がり、結果デカくなる。</t>
         </is>
       </c>
-      <c r="C2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2072" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2072" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2073">
-      <c r="A2073" t="inlineStr">
+      <c r="C2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2073" t="inlineStr">
+      <c r="B2072" t="inlineStr">
         <is>
           <t>童貞が「美女攻略」を考えない方がいい。
 むしろブス、BBA、ニューハーフを片っ端から当たれ。
@@ -61082,25 +61036,25 @@
 経験を積めば脳死で動けるようになる。</t>
         </is>
       </c>
-      <c r="C2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2073" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2073" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2074">
-      <c r="A2074" t="inlineStr">
+      <c r="C2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B2074" t="inlineStr">
+      <c r="B2073" t="inlineStr">
         <is>
           <t>「女を追うな」という助言は一長一短。
 確かに、童貞チー牛や理想の女を抱けない層は、まずステータスを上げることに注力した方がいい。
@@ -61111,6 +61065,29 @@
 実戦を繰り返せば、自分だけのノウハウを作れる。</t>
         </is>
       </c>
+      <c r="C2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
+        </is>
+      </c>
       <c r="C2074" t="n">
         <v>0</v>
       </c>
@@ -61130,29 +61107,6 @@
         </is>
       </c>
       <c r="B2075" t="inlineStr">
-        <is>
-          <t>BMI＝筋トレ知らない奴がこだわる数字。</t>
-        </is>
-      </c>
-      <c r="C2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2075" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2075" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2076">
-      <c r="A2076" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B2076" t="inlineStr">
         <is>
           <t>男磨きには2種類ある。
 ① 自己規律を作る男磨き
@@ -61171,25 +61125,25 @@
 この2つを網羅して、あとは現場に出れば余裕で戦える。</t>
         </is>
       </c>
-      <c r="C2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2076" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2076" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077">
-      <c r="A2077" t="inlineStr">
+      <c r="C2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2077" t="inlineStr">
+      <c r="B2076" t="inlineStr">
         <is>
           <t>非モテ・貧乏・堕落している男は、
 まず"自分を好きになること"が先。
@@ -61205,25 +61159,25 @@
 ニートでスマホ廃人だった俺もここからスタートした。</t>
         </is>
       </c>
-      <c r="C2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2077" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2077" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2078">
-      <c r="A2078" t="inlineStr">
+      <c r="C2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2078" t="inlineStr">
+      <c r="B2077" t="inlineStr">
         <is>
           <t>モテテクで個人的に効果的だったもの
 ・ピークエンド
@@ -61235,25 +61189,25 @@
 「LINEの返信をわざと遅らせてマインドシェアを...」は、結果論だと思ってる。</t>
         </is>
       </c>
-      <c r="C2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2078" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2078" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2079">
-      <c r="A2079" t="inlineStr">
+      <c r="C2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2079" t="inlineStr">
+      <c r="B2078" t="inlineStr">
         <is>
           <t>モテテクにおける単純接触効果は、
 本体が魅力的であることが前提。
@@ -61263,25 +61217,25 @@
 女を追う前に己を磨け。</t>
         </is>
       </c>
-      <c r="C2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2079" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2080">
-      <c r="A2080" t="inlineStr">
+      <c r="C2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B2080" t="inlineStr">
+      <c r="B2079" t="inlineStr">
         <is>
           <t>奢り奢られ論争の、
 「奢りたくない女と飯屋に行かない」
@@ -61293,25 +61247,25 @@
 関係性に合わせて、どちらかに振り切れ。</t>
         </is>
       </c>
-      <c r="C2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2080" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2080" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2081">
-      <c r="A2081" t="inlineStr">
+      <c r="C2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2081" t="inlineStr">
+      <c r="B2080" t="inlineStr">
         <is>
           <t>筋トレ中の飲み物は水で良い。
 理由はトレ前の食事を摂っていればエネルギー枯渇する事なんてないから。
@@ -61321,25 +61275,25 @@
 あとは強度確保のためにまともなプレ買った方がいい。</t>
         </is>
       </c>
-      <c r="C2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2081" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2081" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2082">
-      <c r="A2082" t="inlineStr">
+      <c r="C2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2082" t="inlineStr">
+      <c r="B2081" t="inlineStr">
         <is>
           <t>スマホ中毒者は情報を「点」でしか見られない。
 ゆえにノウハウコレクターや器用貧乏になりがち。
@@ -61361,25 +61315,25 @@
 そして、その目的を達成するために必要な情報だけ取りに行け。</t>
         </is>
       </c>
-      <c r="C2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2082" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2082" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2083">
-      <c r="A2083" t="inlineStr">
+      <c r="C2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B2083" t="inlineStr">
+      <c r="B2082" t="inlineStr">
         <is>
           <t>マッチングアプリは少子化の救世主ではない。
 むしろ、少子化を促進する。
@@ -61393,30 +61347,30 @@
 マッチングアプリは男女を結びつけるどころか、むしろ「選ばれる男」と「選ばれない男」の分断を強めている。</t>
         </is>
       </c>
-      <c r="C2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2083" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2083" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2083" t="inlineStr">
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2082" t="inlineStr">
         <is>
           <t>x_posts/images/tinder_like_rate.jpg,x_posts/images/mote_kakusa.webp</t>
         </is>
       </c>
     </row>
-    <row r="2084">
-      <c r="A2084" t="inlineStr">
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2084" t="inlineStr">
+      <c r="B2083" t="inlineStr">
         <is>
           <t>1日3時間を作り出す方法
 ・ショート動画をやめる（＋60分）
@@ -61428,25 +61382,25 @@
 副業・筋トレ・読書、何でもできる。</t>
         </is>
       </c>
-      <c r="C2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2084" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2084" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2085">
-      <c r="A2085" t="inlineStr">
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2085" t="inlineStr">
+      <c r="B2084" t="inlineStr">
         <is>
           <t>テストステロンが低い男の特徴
 ・慢性的な睡眠不足
@@ -61457,25 +61411,25 @@
 これ全部2年前の俺。食事・睡眠・筋トレを変えただけで体が別物になった。</t>
         </is>
       </c>
-      <c r="C2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2085" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2085" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2086">
-      <c r="A2086" t="inlineStr">
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2086" t="inlineStr">
+      <c r="B2085" t="inlineStr">
         <is>
           <t>童貞には4種類ある。
 それぞれの特徴＆対策を自分に当てはめてみて。
@@ -61511,25 +61465,25 @@
 まずは理想を壊す。</t>
         </is>
       </c>
-      <c r="C2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2086" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2086" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2087">
-      <c r="A2087" t="inlineStr">
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2087" t="inlineStr">
+      <c r="B2086" t="inlineStr">
         <is>
           <t>20歳過ぎた童貞はソープに行け。
 「童貞バレしたくない」
@@ -61541,25 +61495,25 @@
 経験すれば、セックスを必要以上に神格化しなくなる。</t>
         </is>
       </c>
-      <c r="C2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2087" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2087" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2088">
-      <c r="A2088" t="inlineStr">
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B2088" t="inlineStr">
+      <c r="B2087" t="inlineStr">
         <is>
           <t>チー牛の自信の無さは筋トレで解決できる。
 舐められる
@@ -61575,25 +61529,25 @@
 俺の脱チー牛は家で腕立て伏せする事から始まった。</t>
         </is>
       </c>
-      <c r="C2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2088" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2088" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2089">
-      <c r="A2089" t="inlineStr">
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2089" t="inlineStr">
+      <c r="B2088" t="inlineStr">
         <is>
           <t>童貞は、
 「ナンパは社会悪」
@@ -61605,25 +61559,25 @@
 まずプライド捨てて青春を取り戻そうな。</t>
         </is>
       </c>
-      <c r="C2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2089" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2089" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2090">
-      <c r="A2090" t="inlineStr">
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2090" t="inlineStr">
+      <c r="B2089" t="inlineStr">
         <is>
           <t>内向型への差別はエグい。
 俺はクラスで一言も喋らない発達だったけど、相手は初手から舐めてくる。
@@ -61652,50 +61606,50 @@
 ただし、舐められる内向型になる必要はない。</t>
         </is>
       </c>
-      <c r="C2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2090" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2090" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2091">
-      <c r="A2091" t="inlineStr">
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B2091" t="inlineStr">
+      <c r="B2090" t="inlineStr">
         <is>
           <t>「ジムに行く時間がない」
 ↑
 Xでしょうもないコンテンツ見てる時間があるのに？</t>
         </is>
       </c>
-      <c r="C2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2091" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2091" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2092">
-      <c r="A2092" t="inlineStr">
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2092" t="inlineStr">
+      <c r="B2091" t="inlineStr">
         <is>
           <t>非モテは整形の前にやることが山積み。
 ・体脂肪を減らす
@@ -61710,25 +61664,25 @@
 やらずに整形は金ドブだからね。</t>
         </is>
       </c>
-      <c r="C2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2092" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2093">
-      <c r="A2093" t="inlineStr">
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B2093" t="inlineStr">
+      <c r="B2092" t="inlineStr">
         <is>
           <t>「女はセックスした男に惚れる」は真実。
 理由は行動の正当化。
@@ -61739,25 +61693,25 @@
 特に学生時代モテなかったモブであればなおさら。</t>
         </is>
       </c>
-      <c r="C2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2093" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2093" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2094">
-      <c r="A2094" t="inlineStr">
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2094" t="inlineStr">
+      <c r="B2093" t="inlineStr">
         <is>
           <t>男磨きにハマりすぎると、
 努力がズレる。
@@ -61775,19 +61729,19 @@
 フィードバックが得られる環境がないと努力がズレるという話。</t>
         </is>
       </c>
-      <c r="E2094" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2095">
-      <c r="A2095" t="inlineStr">
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2095" t="inlineStr">
+      <c r="B2094" t="inlineStr">
         <is>
           <t>"むくみ"を取りたいなら、
 塩分を減らすより、カリウムを摂れ。
@@ -61808,19 +61762,19 @@
 これが理想的。</t>
         </is>
       </c>
-      <c r="E2095" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2096">
-      <c r="A2096" t="inlineStr">
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2096" t="inlineStr">
+      <c r="B2095" t="inlineStr">
         <is>
           <t>ゲイっぽくなればモテることが出来ます。
 ・カフェ巡り 
@@ -61832,19 +61786,19 @@
 通過儀礼なので。</t>
         </is>
       </c>
-      <c r="E2096" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2097">
-      <c r="A2097" t="inlineStr">
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B2097" t="inlineStr">
+      <c r="B2096" t="inlineStr">
         <is>
           <t>スマホ中毒は価値観が変わると治る。　
 ・ゴシップは無意味
@@ -61856,19 +61810,19 @@
 極地は「悟ること」だった。</t>
         </is>
       </c>
-      <c r="E2097" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2098">
-      <c r="A2098" t="inlineStr">
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2098" t="inlineStr">
+      <c r="B2097" t="inlineStr">
         <is>
           <t>ネット依存症やめると脳が覚醒する。
 集中力が戻り、時間が増え、
@@ -61879,19 +61833,19 @@
 IQ20くらい上がった体感があった。</t>
         </is>
       </c>
-      <c r="E2098" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2099">
-      <c r="A2099" t="inlineStr">
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B2099" t="inlineStr">
+      <c r="B2098" t="inlineStr">
         <is>
           <t>スマホで鬱になる人の特徴
 ・見る専
@@ -61905,19 +61859,19 @@
 使い方を変えれば、スマホ鬱は治る。</t>
         </is>
       </c>
-      <c r="E2099" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2100">
-      <c r="A2100" t="inlineStr">
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2100" t="inlineStr">
+      <c r="B2099" t="inlineStr">
         <is>
           <t>弱者男性はモテるモテない以前の問題。
 まず自己嫌悪を治すべき。
@@ -61929,19 +61883,19 @@
 自閉チー牛だった俺も人並には幸せになれた。</t>
         </is>
       </c>
-      <c r="E2100" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="A2101" t="inlineStr">
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2101" t="inlineStr">
+      <c r="B2100" t="inlineStr">
         <is>
           <t>スマホでドーパミンを浴び続けると、
 風呂に入る事すらダルくなる。
@@ -61954,19 +61908,19 @@
 10分散歩することから始めよう。</t>
         </is>
       </c>
-      <c r="E2101" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="A2102" t="inlineStr">
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2102" t="inlineStr">
+      <c r="B2101" t="inlineStr">
         <is>
           <t>デジタルデトックスで脳を再起動する方法
 ・機内モード
@@ -61982,19 +61936,19 @@
 ドーパミン中毒を治せます。</t>
         </is>
       </c>
-      <c r="E2102" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" t="inlineStr">
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2103" t="inlineStr">
+      <c r="B2102" t="inlineStr">
         <is>
           <t>脱スマホ中毒 Before/After
 Before
@@ -62012,19 +61966,19 @@
 脳は奇跡を起こす。</t>
         </is>
       </c>
-      <c r="E2103" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" t="inlineStr">
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B2104" t="inlineStr">
+      <c r="B2103" t="inlineStr">
         <is>
           <t>チー牛がメガネをする理由には、
 「チー牛がチー牛たる理由」が詰まっている。
@@ -62038,19 +61992,19 @@
 という考えは捨てろ。</t>
         </is>
       </c>
-      <c r="E2104" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" t="inlineStr">
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2105" t="inlineStr">
+      <c r="B2104" t="inlineStr">
         <is>
           <t>スマホが吸い取るのは時間だけではない。
 あなたの大切な意志力を削ぐ。
@@ -62062,19 +62016,19 @@
 これだけでも良い方向に向かう。</t>
         </is>
       </c>
-      <c r="E2105" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" t="inlineStr">
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2106" t="inlineStr">
+      <c r="B2105" t="inlineStr">
         <is>
           <t>非モテであることは精神に悪い。
 非モテは、
@@ -62087,19 +62041,19 @@
 セックスできるようになること。</t>
         </is>
       </c>
-      <c r="E2106" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" t="inlineStr">
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2107" t="inlineStr">
+      <c r="B2106" t="inlineStr">
         <is>
           <t>テストステロンは勝利する事で得られる。
 ・誘惑に勝つ
@@ -62110,19 +62064,19 @@
 小さな勝利が大きな勝利を導く。</t>
         </is>
       </c>
-      <c r="E2107" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" t="inlineStr">
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2108" t="inlineStr">
+      <c r="B2107" t="inlineStr">
         <is>
           <t>非モテは女からすれば透明人間。
 「男は外見＜中身」
@@ -62131,19 +62085,19 @@
 その話の土俵にすら上がっていない。</t>
         </is>
       </c>
-      <c r="E2108" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" t="inlineStr">
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2109" t="inlineStr">
+      <c r="B2108" t="inlineStr">
         <is>
           <t>筋トレがモテるかは本人のスペック次第。
 元々スポーツガチ勢がさらに筋肉付けても変わらない。逆に「マッチョなるとモテなくなる」なんてこともない。
@@ -62153,19 +62107,19 @@
 どっちにしろ損はない。</t>
         </is>
       </c>
-      <c r="E2109" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" t="inlineStr">
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2110" t="inlineStr">
+      <c r="B2109" t="inlineStr">
         <is>
           <t>筋トレを大学生から取り組んでいる人は賢い。
 テストステロンが高く成長しやすいから、
@@ -62177,19 +62131,19 @@
 半端に夜遊びするよりは道が開ける。</t>
         </is>
       </c>
-      <c r="E2110" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" t="inlineStr">
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B2111" t="inlineStr">
+      <c r="B2110" t="inlineStr">
         <is>
           <t>モテにおいて顔が大事なのは情報量にある。
 顔から人となりを察知できる。
@@ -62204,19 +62158,19 @@
 モテることにおいて合理的戦略。</t>
         </is>
       </c>
-      <c r="E2111" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" t="inlineStr">
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2112" t="inlineStr">
+      <c r="B2111" t="inlineStr">
         <is>
           <t>スマホ中毒者は「面倒」を味方に付けろ。
 ・アプリを一回一回消す
@@ -62229,19 +62183,19 @@
 スクリーンタイム1時間を実現した。</t>
         </is>
       </c>
-      <c r="E2112" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" t="inlineStr">
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2113" t="inlineStr">
+      <c r="B2112" t="inlineStr">
         <is>
           <t>スマホ中毒者は「完全オフライン時間」を設けよう。
 ルーターを切るか機内モード。
@@ -62254,19 +62208,19 @@
 トレーダーでもなければチャートを見る必要もない。</t>
         </is>
       </c>
-      <c r="E2113" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" t="inlineStr">
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2114" t="inlineStr">
+      <c r="B2113" t="inlineStr">
         <is>
           <t>経験人数を稼ぐことは、
 ハメ技でしかない。
@@ -62282,19 +62236,19 @@
 妥協した女に時間を使うな。</t>
         </is>
       </c>
-      <c r="E2114" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" t="inlineStr">
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B2115" t="inlineStr">
+      <c r="B2114" t="inlineStr">
         <is>
           <t>筋トレにおいて"体重比"という考えは捨てろ。
 なぜなら、体重を増やすのも努力だから。
@@ -62311,19 +62265,19 @@
 そのくらい成長に邪魔な考えだと思ってる。</t>
         </is>
       </c>
-      <c r="E2115" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" t="inlineStr">
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2116" t="inlineStr">
+      <c r="B2115" t="inlineStr">
         <is>
           <t>ネット中毒は荒療治しかない。
 ・ルーターを切る
@@ -62336,19 +62290,19 @@
 繰り返すことで、前頭前野はドーパミン漬けから回復していく。</t>
         </is>
       </c>
-      <c r="E2116" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" t="inlineStr">
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B2117" t="inlineStr">
+      <c r="B2116" t="inlineStr">
         <is>
           <t>女の本能は非常にシビア。
 魅力的な男（アルファ）には性的な関係を求め、
@@ -62358,19 +62312,19 @@
 「選ばれる男」ではなく「選ぶ側の男」に回ること。</t>
         </is>
       </c>
-      <c r="E2117" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" t="inlineStr">
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2118" t="inlineStr">
+      <c r="B2117" t="inlineStr">
         <is>
           <t>増量期に食べてたジャンクフード
 ・ごつ盛り（800kcal）
@@ -62381,19 +62335,19 @@
 ヒョロガリは黙って食え。</t>
         </is>
       </c>
-      <c r="E2118" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" t="inlineStr">
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B2119" t="inlineStr">
+      <c r="B2118" t="inlineStr">
         <is>
           <t>筋トレがモテるのは、身体が変わるからだけではない。
 ・テストステロン
@@ -62406,19 +62360,19 @@
 「男としての総合力」が上がる。</t>
         </is>
       </c>
-      <c r="E2119" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" t="inlineStr">
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2120" t="inlineStr">
+      <c r="B2119" t="inlineStr">
         <is>
           <t>自閉チー牛の私がコミュ障を治したステップ
 ① 独り言
@@ -62434,19 +62388,19 @@
 私は鏡の前での独り言から始めた。</t>
         </is>
       </c>
-      <c r="E2120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" t="inlineStr">
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B2121" t="inlineStr">
+      <c r="B2120" t="inlineStr">
         <is>
           <t>童貞チー牛にはヤリチン擬態が有効。
 ハッタリで0→1を作れ。
@@ -62461,19 +62415,19 @@
 0→1は力技で作れる。</t>
         </is>
       </c>
-      <c r="E2121" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" t="inlineStr">
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2122" t="inlineStr">
+      <c r="B2121" t="inlineStr">
         <is>
           <t>テストステロンを上げる食事
 ・赤肉
@@ -62490,19 +62444,19 @@
 これが男の食事。</t>
         </is>
       </c>
-      <c r="E2122" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" t="inlineStr">
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2123" t="inlineStr">
+      <c r="B2122" t="inlineStr">
         <is>
           <t>環境のせいにしろ。
 あなたが努力できないのは「意志力」ではなく明らかに「環境」のせい。
@@ -62519,25 +62473,25 @@
 いい加減、努力の過大評価はやめて、環境を変える事を意識しよう。</t>
         </is>
       </c>
-      <c r="C2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2123" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" t="inlineStr">
+      <c r="C2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2124" t="inlineStr">
+      <c r="B2123" t="inlineStr">
         <is>
           <t>ポルノ中毒には2種類ある。
 ① 精液過多型
@@ -62567,25 +62521,25 @@
 同じ自慰行為でも、原因が違えば対策も違う</t>
         </is>
       </c>
-      <c r="C2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" t="inlineStr">
+      <c r="C2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2125" t="inlineStr">
+      <c r="B2124" t="inlineStr">
         <is>
           <t>筋トレでスマホやめると、
 セットの質が上がった。
@@ -62598,25 +62552,25 @@
 そりゃインターバルで猫の動画見てたら力抜けるよな笑</t>
         </is>
       </c>
-      <c r="C2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2125" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" t="inlineStr">
+      <c r="C2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
         <is>
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="B2126" t="inlineStr">
+      <c r="B2125" t="inlineStr">
         <is>
           <t>鬱は予防できる。
 カフェインを体重×3mg摂って、
@@ -62625,30 +62579,30 @@
 週1でやってたら鬱になる方が難しい。</t>
         </is>
       </c>
-      <c r="C2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2126" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G2126" t="inlineStr">
+      <c r="C2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G2125" t="inlineStr">
         <is>
           <t>/mnt/c/Users/81808/OneDrive - 横浜商科大学/デスクトップ/スクリーンショット/スクリーンショット 2026-10-01 201118.png</t>
         </is>
       </c>
     </row>
-    <row r="2127">
-      <c r="A2127" t="inlineStr">
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2127" t="inlineStr">
+      <c r="B2126" t="inlineStr">
         <is>
           <t>「使えない筋肉」こそが至高。
 結局、人間はただの動物。
@@ -62659,19 +62613,19 @@
 身体のデカさ＝自己防衛</t>
         </is>
       </c>
-      <c r="E2127" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="A2128" t="inlineStr">
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2128" t="inlineStr">
+      <c r="B2127" t="inlineStr">
         <is>
           <t>メンズコーチにハマる男は、
 「父親に甘やかされてきた系」の弱男。
@@ -62683,19 +62637,19 @@
 精神的な父は違っていい。</t>
         </is>
       </c>
-      <c r="E2128" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="A2129" t="inlineStr">
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="B2129" t="inlineStr">
+      <c r="B2128" t="inlineStr">
         <is>
           <t>ポルノ中毒って「金玉パンパンで毎回、精液が正常に出る人」は割と健全。
 5回シコっても翌日には、
@@ -62706,19 +62660,19 @@
 行為依存になってしまっている人は真の中毒者。https://x.com/puregrinding23/status/2105598928477700478</t>
         </is>
       </c>
-      <c r="E2129" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="A2130" t="inlineStr">
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="B2130" t="inlineStr">
+      <c r="B2129" t="inlineStr">
         <is>
           <t>テストステロンは原始的な生活で上がる。
 ・1日1万歩歩く
@@ -62732,17 +62686,17 @@
 私は毎朝ベランダでパンイチで日光浴びることにハマっています。</t>
         </is>
       </c>
-      <c r="E2130" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="A2131" s="2" t="n">
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="2" t="n">
         <v>46303</v>
       </c>
-      <c r="B2131" t="inlineStr">
+      <c r="B2130" t="inlineStr">
         <is>
           <t>堕落を治すには起床3秒が勝負。
 スマホに手を伸ばすか、
@@ -62752,17 +62706,17 @@
 あとは流れで上手くいきやすい。</t>
         </is>
       </c>
-      <c r="E2131" t="inlineStr">
+      <c r="E2130" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
     </row>
-    <row r="2132">
-      <c r="A2132" s="2" t="n">
+    <row r="2131">
+      <c r="A2131" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B2132" t="inlineStr">
+      <c r="B2131" t="inlineStr">
         <is>
           <t>モテ攻略に大学はターニングポイントになる。
 ・サークル、ゼミ、バイト
@@ -62775,19 +62729,19 @@
 私文は特にチャンスが多い。</t>
         </is>
       </c>
-      <c r="E2132" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="A2133" t="inlineStr">
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2133" t="inlineStr">
+      <c r="B2132" t="inlineStr">
         <is>
           <t>彼女持ちがモテるのは、
 「社会性」と「モテ」の証明になるから。
@@ -62799,25 +62753,25 @@
 童貞がモテない理由はこの逆です。</t>
         </is>
       </c>
-      <c r="C2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2133" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="A2134" t="inlineStr">
+      <c r="C2132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="B2134" t="inlineStr">
+      <c r="B2133" t="inlineStr">
         <is>
           <t>ヒョロガリでもデカくなる男の特徴は
 ・ベルト使う
@@ -62830,25 +62784,25 @@
 絶対、デカくなります👍</t>
         </is>
       </c>
-      <c r="C2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2134" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="A2135" t="inlineStr">
+      <c r="C2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2135" t="inlineStr">
+      <c r="B2134" t="inlineStr">
         <is>
           <t>童貞がまず目指すべきは量産型。
 ・前髪をつくる
@@ -62860,25 +62814,25 @@
 差別化を語るのは、その後でいい。</t>
         </is>
       </c>
-      <c r="C2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2135" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="A2136" t="inlineStr">
+      <c r="C2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
         <is>
           <t>2026-10-13 00:00:00</t>
         </is>
       </c>
-      <c r="B2136" t="inlineStr">
+      <c r="B2135" t="inlineStr">
         <is>
           <t>気弱な男は究極、
 「自分の損得」のみ考えて生きればいい。
@@ -62891,25 +62845,25 @@
 ただし、判断基準は自分の利益に置こう。</t>
         </is>
       </c>
-      <c r="C2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2136" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="A2137" t="inlineStr">
+      <c r="C2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2136" t="inlineStr">
         <is>
           <t>童貞がモテ攻略すると消えるもの
 ・ルッキズム
@@ -62920,19 +62874,19 @@
 また媚びることでしか女と関われない奴と一線を画すことができる。</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B2138" t="inlineStr">
+      <c r="B2137" t="inlineStr">
         <is>
           <t>テストステロンは不調を凌駕する。
 ・寝不足
@@ -62946,19 +62900,19 @@
 何とかなっている。</t>
         </is>
       </c>
-      <c r="E2138" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="A2139" t="inlineStr">
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B2139" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>「筋トレは風邪ひきやすくなる」は嘘。
 確かに
@@ -62971,7 +62925,7 @@
 筋トレに出会って良かったです。</t>
         </is>
       </c>
-      <c r="E2139" t="inlineStr">
+      <c r="E2138" t="inlineStr">
         <is>
           <t>normal</t>
         </is>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2138"/>
+  <dimension ref="A1:G2139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62931,6 +62931,32 @@
         </is>
       </c>
     </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>非モテが男磨きに逃げる言い訳
+・整形が済んでない
+・もっと痩せてから
+・筋トレしてから
+・金がない
+スペックは無関係という話ではない。
+童貞なのに自己完結の努力だけして、
+年を重ねるなという話。
+小綺麗なチー牛になったら外に出ろ。
+最初は理想の女なんて抱けなくていい。</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -59543,6 +59543,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="G2018" t="inlineStr">
+        <is>
+          <t>images/british_guard.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="2019">
       <c r="A2019" t="inlineStr">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2139"/>
+  <dimension ref="A1:G2140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62962,6 +62962,43 @@
         </is>
       </c>
     </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:38:37</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>ヒョロガリが増量しない言い訳
+・体質的に太れない
+・食べるのが苦手
+・太ったらモテない
+・食費が高い
+モテボディを目指していても、
+太りつつ筋肉を増やす期間は必要。
+今から始めれば、来年に良い思いが出来る。
+俺はこのマインドで去年14kg増やした。</t>
+        </is>
+      </c>
+      <c r="C2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2140" t="inlineStr">
+        <is>
+          <t>【ヒョロガリ向け】最短で「モテボディ」を獲得するための食事プログラム｜by元体重39kgのヒョロガリが解説。
+https://note.com/puregrinding1/n/na60936ff3ad1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2140"/>
+  <dimension ref="A1:G2141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62999,6 +62999,45 @@
         </is>
       </c>
     </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:46:54</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>スマホ中毒者は、
+・1日3時間
+・1ヶ月で 90時間
+・1年で 1,095時間
+・10年で 10,950時間
+を失っています。
+中毒を治し、
+「モテ」「金」「筋トレ」「スキル」
+に時間を投じましょう。
+どんなに怠惰な人間でも3時間は減らせる。
+ニートで1日10時間のスクロールガイガイの僕でも出来ました。</t>
+        </is>
+      </c>
+      <c r="C2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2141" t="inlineStr">
+        <is>
+          <t>【スマホ中毒者向け】デジタル・ドーパミン廃人だった私がスクリーンタイム10時間→1時間で人生を奪還した思考法
+https://note.com/puregrinding1/n/n75b3881b4678</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2141"/>
+  <dimension ref="A1:G2142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63038,6 +63038,42 @@
         </is>
       </c>
     </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-10-22 20:02:31</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>ポルノ中毒で射精障害になる人の特徴は
+・過激なものにシフトしている
+・脚ピン、握力MAX、床でやる
+・三人称視点のポルノを好む
+俺も童卒した頃に実感した。
+EDまではいかないが、寝バックで強い刺激を与えないとイケなかった。
+童貞は初セスクで恥をかかないためにも、
+気を付けた方がいい。</t>
+        </is>
+      </c>
+      <c r="C2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2142" t="inlineStr">
+        <is>
+          <t>「爆速でモテる男磨きのやり方」非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説
+https://note.com/puregrinding1/n/n4eabc4c9b556</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2142"/>
+  <dimension ref="A1:G2143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63074,6 +63074,42 @@
         </is>
       </c>
     </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-10-24 19:21:13</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>「コンビニ飯850円は高い」とか舐めんな。
+ヒョロガリと貧乏人は850円使って、
+スーパーで全卵40個買え。</t>
+        </is>
+      </c>
+      <c r="C2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2143" t="inlineStr">
+        <is>
+          <t>【ヒョロガリ向け】最短で「モテボディ」を獲得するための食事プログラム｜by元体重39kgのヒョロガリが解説。
+https://note.com/puregrinding1/n/na60936ff3ad1</t>
+        </is>
+      </c>
+      <c r="G2143" t="inlineStr">
+        <is>
+          <t>images/convenience_store_850.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2143"/>
+  <dimension ref="A1:G2144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63110,6 +63110,37 @@
         </is>
       </c>
     </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-10-24 19:23:55</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>人生がつまらなかったら、
+ギラギラしたコンテンツを見るといい。
+女、金、自由という「男のシンプルな欲望」を刺激してみてください。
+TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2144" t="inlineStr">
+        <is>
+          <t>https://x.com/puregrinding23/status/2058145954361123021</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2144"/>
+  <dimension ref="A1:G2143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63110,37 +63110,6 @@
         </is>
       </c>
     </row>
-    <row r="2144">
-      <c r="A2144" t="inlineStr">
-        <is>
-          <t>2026-10-24 19:23:55</t>
-        </is>
-      </c>
-      <c r="B2144" t="inlineStr">
-        <is>
-          <t>人生がつまらなかったら、
-ギラギラしたコンテンツを見るといい。
-女、金、自由という「男のシンプルな欲望」を刺激してみてください。
-TikTok等で「wolfofwallstreetedit」「Billionaire motivation」と検索するとピッタリな動画が出てきます。</t>
-        </is>
-      </c>
-      <c r="C2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2144" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F2144" t="inlineStr">
-        <is>
-          <t>https://x.com/puregrinding23/status/2058145954361123021</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2143"/>
+  <dimension ref="A1:G2145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63110,6 +63110,78 @@
         </is>
       </c>
     </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-10-24 23:47:16</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>チー牛を卒業する男
+・自分から話しかける
+・断られても次に行く
+・遺伝的限界までベストを尽くす
+チー牛のままの奴
+・顔のせいにする
+・男磨き陰キャのまま
+・モテテクだけ集める
+容姿は大事。
+でも、分かれ目は自己完結に逃げないこと。
+自閉チー牛の私も男磨き陰キャやめて、対人関係と向き合ってから彼女ができました。</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2144" t="inlineStr">
+        <is>
+          <t>「爆速でモテる男磨きのやり方」非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説
+https://note.com/puregrinding1/n/n4eabc4c9b556</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-10-24 23:47:16</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>弱者男性は「報酬を先送りにする能力」に欠けている。
+スマホ中毒しかり、貧困層にフードデリバリーの利用率が高いのも領ける。(確かイギリスのuberのデータ)
+今を犠牲にして、将来に報酬を先送りにする。
+これだけ覚えておくだけで、人生は変わる。
+スマホ廃人の私もそうでした。</t>
+        </is>
+      </c>
+      <c r="C2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2145" t="inlineStr">
+        <is>
+          <t>【スマホ中毒者向け】"デジタル・ドーパミン廃人"だった私がスクリーンタイム10時間→1時間で人生を奪還した思考法
+https://note.com/puregrinding1/n/n75b3881b4678</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -59760,7 +59760,7 @@
 ・巻き肩
 私はストレートネックがひどかったのですが、
 スマホ中毒をやめてモニターを高くすることで
-大分、良くなりました。　保存</t>
+大分、良くなりました。</t>
         </is>
       </c>
       <c r="C2025" t="n">

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2145"/>
+  <dimension ref="A1:G2146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63182,6 +63182,39 @@
         </is>
       </c>
     </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:30:01</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>弱男はスマホをやめて、運動習慣取り入れる。
+そして支出は最大限カットして、
+空き時間で出来る月5万のビジネスを作る。
+それをさらに自己投資して稼ぐ。
+そしたら、逆転への道が切り開ける。
+20代だったらモテ攻略も遅くはない。</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2146" t="inlineStr">
+        <is>
+          <t>https://x.com/puregrinding23/status/2058145954361123021</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2146"/>
+  <dimension ref="A1:G2147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63215,6 +63215,44 @@
         </is>
       </c>
     </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:54:15</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>成長している時は常にダサい。
+習慣化は「距離」が命。
+・徒歩で行けるジムを選ぶ
+・作業専用の書斎を作る
+・目標を壁紙にする
+逆に悪習慣は遠ざける。
+・スマホを別室に置く
+・アプリを遠ざけるor消す
+・衝動買い
+→クレカを財布から抜く
+環境を変えれば、習慣は勝手に変わる。</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2147" t="inlineStr">
+        <is>
+          <t>https://x.com/puregrinding23/status/2058145954361123021</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2147"/>
+  <dimension ref="A1:G2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63253,6 +63253,43 @@
         </is>
       </c>
     </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:54:44</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>成長している時は常にダサい。
+・男磨き全般
+・童貞のキモアプローチ
+・ヒョロガリがジムに行く時
+ここで「冷笑対象になるならやめるわ」となる奴は
+メンタル的に向いていない。
+逆にダサいと思われても「だからなんや？」と
+なれる人はそのまま成長できる。
+まずダサい時期を乗り越えろ。</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2148" t="inlineStr">
+        <is>
+          <t>「爆速でモテる男磨きのやり方」非モテが恋愛の土台を築き上げる男磨きby元自閉症チー牛が解説
+https://note.com/puregrinding1/n/n4eabc4c9b556</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/x_posts/posts_categorized.xlsx
+++ b/x_posts/posts_categorized.xlsx
@@ -62965,7 +62965,7 @@
     <row r="2140">
       <c r="A2140" t="inlineStr">
         <is>
-          <t>2026-10-22 18:38:37</t>
+          <t>2026-08-10 00:00:00</t>
         </is>
       </c>
       <c r="B2140" t="inlineStr">
@@ -63002,7 +63002,7 @@
     <row r="2141">
       <c r="A2141" t="inlineStr">
         <is>
-          <t>2026-10-22 18:46:54</t>
+          <t>2026-08-11 00:00:00</t>
         </is>
       </c>
       <c r="B2141" t="inlineStr">
@@ -63041,7 +63041,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>2026-10-22 20:02:31</t>
+          <t>2026-08-12 00:00:00</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
@@ -63077,7 +63077,7 @@
     <row r="2143">
       <c r="A2143" t="inlineStr">
         <is>
-          <t>2026-10-24 19:21:13</t>
+          <t>2026-08-13 00:00:00</t>
         </is>
       </c>
       <c r="B2143" t="inlineStr">
@@ -63113,7 +63113,7 @@
     <row r="2144">
       <c r="A2144" t="inlineStr">
         <is>
-          <t>2026-10-24 23:47:16</t>
+          <t>2026-08-14 00:00:00</t>
         </is>
       </c>
       <c r="B2144" t="inlineStr">
@@ -63152,7 +63152,7 @@
     <row r="2145">
       <c r="A2145" t="inlineStr">
         <is>
-          <t>2026-10-24 23:47:16</t>
+          <t>2026-08-15 00:00:00</t>
         </is>
       </c>
       <c r="B2145" t="inlineStr">
@@ -63185,7 +63185,7 @@
     <row r="2146">
       <c r="A2146" t="inlineStr">
         <is>
-          <t>2026-10-25 20:30:01</t>
+          <t>2026-08-16 00:00:00</t>
         </is>
       </c>
       <c r="B2146" t="inlineStr">
@@ -63218,7 +63218,7 @@
     <row r="2147">
       <c r="A2147" t="inlineStr">
         <is>
-          <t>2026-10-27 10:54:15</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="B2147" t="inlineStr">
@@ -63256,7 +63256,7 @@
     <row r="2148">
       <c r="A2148" t="inlineStr">
         <is>
-          <t>2026-10-27 10:54:44</t>
+          <t>2026-08-18 00:00:00</t>
         </is>
       </c>
       <c r="B2148" t="inlineStr">
